--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1620,13 +1620,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.62817967593</v>
+        <v>46073.79484634259</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55022653935</v>
+        <v>46092.716893206016</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.547676111106</v>
+        <v>46129.71434277778</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1669,13 +1669,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.62818002315</v>
+        <v>46073.794846689816</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.550201342594</v>
+        <v>46092.71686800926</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71108753472</v>
+        <v>46133.877754201385</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1734,13 +1734,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.62818039352</v>
+        <v>46073.794847060184</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55020189815</v>
+        <v>46092.716868564814</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.47894534722</v>
+        <v>46134.64561201389</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1799,13 +1799,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.628180694446</v>
+        <v>46073.79484736111</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55020238426</v>
+        <v>46092.71686905093</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.478941203706</v>
+        <v>46134.64560787037</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1864,13 +1864,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.628180960644</v>
+        <v>46073.794847627316</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.5502027662</v>
+        <v>46092.71686943287</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.478936851854</v>
+        <v>46134.64560351852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1929,13 +1929,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.628181238426</v>
+        <v>46073.7948479051</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55020334491</v>
+        <v>46092.71687001157</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.478931087964</v>
+        <v>46134.64559775463</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -1994,13 +1994,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.628182002314</v>
+        <v>46073.794848668986</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.434622615736</v>
+        <v>46129.60128928241</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.547719375</v>
+        <v>46129.71438604167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2043,13 +2043,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.628182291664</v>
+        <v>46073.794848958336</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.382770868055</v>
+        <v>46097.54943753472</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38278583333</v>
+        <v>46097.549452499996</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2108,13 +2108,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.628182569446</v>
+        <v>46073.79484923611</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.43460976852</v>
+        <v>46129.60127643518</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.00499202547</v>
+        <v>46154.171658692125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2173,13 +2173,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.62818284723</v>
+        <v>46073.794849513884</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.380507800925</v>
+        <v>46097.54717446759</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.547774074075</v>
+        <v>46129.71444074074</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2222,13 +2222,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.628180370375</v>
+        <v>46073.79484703703</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.380070625004</v>
+        <v>46097.54673729167</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.38826939814</v>
+        <v>46104.554936064815</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2287,13 +2287,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.62818092592</v>
+        <v>46073.794847592595</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.38044920139</v>
+        <v>46097.54711586806</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.388864293986</v>
+        <v>46104.55553096065</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2352,13 +2352,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.628181168984</v>
+        <v>46073.79484783565</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38026064815</v>
+        <v>46097.54692731482</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.4023097801</v>
+        <v>46104.56897644676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2417,13 +2417,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.62818142361</v>
+        <v>46073.79484809028</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.38048609954</v>
+        <v>46097.5471527662</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.612236898145</v>
+        <v>46100.77890356482</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2482,13 +2482,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.62818166667</v>
+        <v>46073.79484833333</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.33702034722</v>
+        <v>46114.50368701389</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.33703412037</v>
+        <v>46114.50370078704</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2535,13 +2535,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.64645108796</v>
+        <v>46101.81311775463</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.40283936342</v>
+        <v>46104.56950603009</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2600,13 +2600,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3809314699</v>
+        <v>46097.547598136574</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.40305519676</v>
+        <v>46104.56972186343</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2665,13 +2665,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.62818238426</v>
+        <v>46073.79484905093</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38286118055</v>
+        <v>46097.54952784722</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.40372770833</v>
+        <v>46104.570394375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2730,13 +2730,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.62818262732</v>
+        <v>46073.79484929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.647509710645</v>
+        <v>46101.81417637732</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.64752646991</v>
+        <v>46101.814193136575</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2795,13 +2795,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.41547559028</v>
+        <v>46076.58214225694</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.33700079861</v>
+        <v>46114.50366746528</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.337126388884</v>
+        <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2860,13 +2860,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.62817975694</v>
+        <v>46073.79484642361</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38118626157</v>
+        <v>46097.54785292824</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.6113996412</v>
+        <v>46100.778066307874</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2925,13 +2925,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.62818008102</v>
+        <v>46073.79484674768</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.54803983796</v>
+        <v>46129.71470650463</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.548054328705</v>
+        <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2978,13 +2978,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.380689363425</v>
+        <v>46097.54735603009</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.03892021991</v>
+        <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3043,13 +3043,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.62818060185</v>
+        <v>46073.794847268524</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.380632326385</v>
+        <v>46097.54729899306</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.64645784722</v>
+        <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3108,13 +3108,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.62818085648</v>
+        <v>46073.79484752315</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38067305555</v>
+        <v>46097.54733972222</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.3806743287</v>
+        <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3173,13 +3173,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.62818109954</v>
+        <v>46073.7948477662</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.420903715276</v>
+        <v>46104.58757038195</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.03892015046</v>
+        <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3238,13 +3238,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.62818136574</v>
+        <v>46073.79484803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.42083481481</v>
+        <v>46104.58750148148</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.42083644676</v>
+        <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3299,13 +3299,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.62818162037</v>
+        <v>46073.79484828704</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.42088792824</v>
+        <v>46104.58755459491</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42088951389</v>
+        <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3360,13 +3360,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.62818186343</v>
+        <v>46073.79484853009</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.41699271991</v>
+        <v>46104.583659386575</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.41700664352</v>
+        <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3425,13 +3425,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.62818211806</v>
+        <v>46073.79484878472</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.416909374995</v>
+        <v>46104.58357604167</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.416911215274</v>
+        <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3486,13 +3486,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.41697875</v>
+        <v>46104.58364541667</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.41698019676</v>
+        <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3547,13 +3547,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.62818072917</v>
+        <v>46073.79484739584</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.41762032408</v>
+        <v>46104.584286990736</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.039385833334</v>
+        <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3612,13 +3612,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.62818103009</v>
+        <v>46073.79484769676</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.417508425926</v>
+        <v>46104.58417509259</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.41751008102</v>
+        <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3673,13 +3673,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.628181319444</v>
+        <v>46073.79484798611</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.41755533565</v>
+        <v>46104.58422200232</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.41755704861</v>
+        <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3734,13 +3734,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.62818159722</v>
+        <v>46073.79484826389</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.41760486111</v>
+        <v>46104.58427152778</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.417606539355</v>
+        <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3795,13 +3795,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.62818189815</v>
+        <v>46073.794848564816</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.63444692129</v>
+        <v>46114.801113587964</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.63445758102</v>
+        <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3860,13 +3860,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.62818216435</v>
+        <v>46073.79484883102</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.42476375</v>
+        <v>46112.591430416665</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.424765902775</v>
+        <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3921,13 +3921,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.628182465276</v>
+        <v>46073.79484913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.63443313657</v>
+        <v>46114.80109980324</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.63443443287</v>
+        <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3982,13 +3982,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.415997523145</v>
+        <v>46076.58266418982</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.331283182866</v>
+        <v>46112.49794984954</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.02542255787</v>
+        <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4047,13 +4047,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.41613828704</v>
+        <v>46076.58280495371</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.547919675926</v>
+        <v>46129.7145863426</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.54792074074</v>
+        <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4108,13 +4108,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.41635584491</v>
+        <v>46076.58302251158</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.54796578704</v>
+        <v>46129.7146324537</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.547966886574</v>
+        <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4169,11 +4169,11 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.62818280092</v>
+        <v>46073.794849467595</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46114.632145219904</v>
+        <v>46114.798811886576</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4218,13 +4218,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.62818306713</v>
+        <v>46073.79484973379</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.63182189815</v>
+        <v>46114.79848856482</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.63184163194</v>
+        <v>46114.79850829861</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4283,13 +4283,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.62817972222</v>
+        <v>46073.79484638889</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.63205997685</v>
+        <v>46114.79872664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.63207577546</v>
+        <v>46114.79874244213</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4348,13 +4348,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.6432952662</v>
+        <v>46087.80996193287</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.63212616898</v>
+        <v>46114.798792835645</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.63214876158</v>
+        <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4411,11 +4411,11 @@
         <v>188</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.64335503472</v>
+        <v>46087.810021701385</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46172.01372217592</v>
+        <v>46172.18038884259</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>189</v>
@@ -4472,13 +4472,13 @@
         <v>194</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.6281800463</v>
+        <v>46073.79484671296</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.50667412037</v>
+        <v>46121.673340787034</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.50668688657</v>
+        <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>195</v>
@@ -4525,13 +4525,13 @@
         <v>197</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.628180300926</v>
+        <v>46073.79484696759</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.63278359953</v>
+        <v>46120.799450266204</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.63280086806</v>
+        <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>198</v>
@@ -4590,13 +4590,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.62818056713</v>
+        <v>46073.794847233796</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.50665810185</v>
+        <v>46121.67332476852</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.50689269676</v>
+        <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4655,13 +4655,13 @@
         <v>207</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.62818082176</v>
+        <v>46073.794847488425</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.60070484954</v>
+        <v>46132.76737151621</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.60071787037</v>
+        <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>208</v>
@@ -4708,13 +4708,13 @@
         <v>210</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.62818108796</v>
+        <v>46073.79484775463</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.632385439814</v>
+        <v>46120.79905210648</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.757545243054</v>
+        <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>211</v>
@@ -4773,13 +4773,13 @@
         <v>215</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.62818134259</v>
+        <v>46073.79484800926</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.394725266204</v>
+        <v>46132.561391932875</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.39474199074</v>
+        <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>216</v>
@@ -4838,13 +4838,13 @@
         <v>219</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.60068640046</v>
+        <v>46132.76735306713</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.60070510417</v>
+        <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>220</v>
@@ -4903,13 +4903,13 @@
         <v>223</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.54959740741</v>
+        <v>46129.71626407407</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.54968293982</v>
+        <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -4952,13 +4952,13 @@
         <v>225</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.450968784724</v>
+        <v>46122.61763545139</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.450987118056</v>
+        <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>226</v>
@@ -5017,13 +5017,13 @@
         <v>228</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.62817998843</v>
+        <v>46073.79484665509</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.49241293981</v>
+        <v>46122.659079606485</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.00931273148</v>
+        <v>46147.17597939815</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5082,13 +5082,13 @@
         <v>230</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.62818046296</v>
+        <v>46073.794847129626</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.50250782407</v>
+        <v>46127.669174490744</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.00931284722</v>
+        <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>231</v>
@@ -5147,13 +5147,13 @@
         <v>233</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.62818075232</v>
+        <v>46073.794847418976</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.50256168982</v>
+        <v>46127.66922835648</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.00809422454</v>
+        <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>234</v>
@@ -5212,13 +5212,13 @@
         <v>236</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.41694188658</v>
+        <v>46076.583608553236</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.549582754626</v>
+        <v>46129.7162494213</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.0342689699</v>
+        <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>237</v>
@@ -5277,11 +5277,11 @@
         <v>239</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.62818101852</v>
+        <v>46073.79484768519</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.64890082176</v>
+        <v>46087.815567488426</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>240</v>
@@ -5324,11 +5324,11 @@
         <v>242</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46143.51689972222</v>
+        <v>46143.68356638889</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>243</v>
@@ -5387,11 +5387,11 @@
         <v>245</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46171.007393252316</v>
+        <v>46171.17405991898</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>246</v>
@@ -5450,11 +5450,11 @@
         <v>249</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46160.38170990741</v>
+        <v>46160.54837657408</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>250</v>
@@ -5513,11 +5513,11 @@
         <v>252</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.628182175926</v>
+        <v>46073.79484884259</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46160.37949565973</v>
+        <v>46160.54616232638</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>253</v>
@@ -5576,11 +5576,11 @@
         <v>255</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.45626391204</v>
+        <v>46076.6229305787</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46140.001457164355</v>
+        <v>46140.16812383102</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>256</v>
@@ -5639,11 +5639,11 @@
         <v>258</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.6281824537</v>
+        <v>46073.79484912037</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46171.00739363426</v>
+        <v>46171.174060300924</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>192</v>
@@ -5700,11 +5700,11 @@
         <v>261</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.6281827662</v>
+        <v>46073.794849432874</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46173.02446645833</v>
+        <v>46173.191133125</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>193</v>
@@ -5761,11 +5761,11 @@
         <v>263</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.6281803125</v>
+        <v>46073.794846979166</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.50283079861</v>
+        <v>46090.66949746528</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>264</v>
@@ -5808,11 +5808,11 @@
         <v>266</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.62818071759</v>
+        <v>46073.794847384255</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46176.03782940972</v>
+        <v>46176.20449607639</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>267</v>
@@ -5869,11 +5869,11 @@
         <v>271</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.62818100695</v>
+        <v>46073.79484767361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.00153725695</v>
+        <v>46179.16820392361</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>272</v>
@@ -5932,11 +5932,11 @@
         <v>275</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46182.01569325231</v>
+        <v>46182.18235991898</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>276</v>
@@ -5993,11 +5993,11 @@
         <v>278</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.62818158565</v>
+        <v>46073.79484825231</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46183.02135520833</v>
+        <v>46183.188021875</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>279</v>
@@ -6054,11 +6054,11 @@
         <v>281</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.50286570602</v>
+        <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>282</v>
@@ -6101,11 +6101,11 @@
         <v>284</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.62818219907</v>
+        <v>46073.79484886574</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46184.02798275463</v>
+        <v>46184.1946494213</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>285</v>
@@ -6164,11 +6164,11 @@
         <v>289</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.62818248842</v>
+        <v>46073.79484915509</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.02798273148</v>
+        <v>46184.19464939815</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>290</v>
@@ -6227,11 +6227,11 @@
         <v>291</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.47971854167</v>
+        <v>46090.64638520833</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.50289863426</v>
+        <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>292</v>
@@ -6274,11 +6274,11 @@
         <v>294</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.47982414352</v>
+        <v>46090.646490810184</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46183.00311795139</v>
+        <v>46183.169784618054</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>295</v>
@@ -6337,11 +6337,11 @@
         <v>297</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.48022813657</v>
+        <v>46090.64689480324</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.656672060184</v>
+        <v>46090.823338726856</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>298</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46184.1946494213</v>
+        <v>46190.12544563657</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>285</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.19464939815</v>
+        <v>46190.12544762732</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>290</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -6278,7 +6278,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46183.169784618054</v>
+        <v>46190.250327291666</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>295</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -6278,7 +6278,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.250327291666</v>
+        <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>295</v>
@@ -6328,8 +6328,8 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="12" t="s">
-        <v>81</v>
+      <c r="U80" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.12544563657</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>285</v>
@@ -6155,8 +6155,8 @@
       <c r="T77" s="9">
         <v>0</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>81</v>
+      <c r="U77" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.12544762732</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>290</v>
@@ -6218,8 +6218,8 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>81</v>
+      <c r="U78" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.823338726856</v>
+        <v>46192.17605807871</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>298</v>
@@ -6391,8 +6391,8 @@
       <c r="T81" s="9">
         <v>0</v>
       </c>
-      <c r="U81" s="10" t="s">
-        <v>61</v>
+      <c r="U81" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5281,7 +5281,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46087.815567488426</v>
+        <v>46195.6882462963</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>240</v>
@@ -5326,9 +5326,11 @@
       <c r="B64" s="5">
         <v>46073.79484796296</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46195.68823886574</v>
+      </c>
       <c r="D64" s="5">
-        <v>46143.68356638889</v>
+        <v>46195.688256319445</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>243</v>
@@ -5376,10 +5378,10 @@
         <v>60</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5391,7 +5393,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46171.17405991898</v>
+        <v>46195.68826325232</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>246</v>
@@ -5441,8 +5443,8 @@
       <c r="T65" s="9">
         <v>0</v>
       </c>
-      <c r="U65" s="10" t="s">
-        <v>61</v>
+      <c r="U65" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5454,7 +5456,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46160.54837657408</v>
+        <v>46195.68826268519</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>250</v>
@@ -5504,8 +5506,8 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="10" t="s">
-        <v>61</v>
+      <c r="U66" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5517,7 +5519,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46160.54616232638</v>
+        <v>46195.68826314815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>253</v>
@@ -5567,8 +5569,8 @@
       <c r="T67" s="9">
         <v>0</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>61</v>
+      <c r="U67" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5580,7 +5582,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46140.16812383102</v>
+        <v>46195.688253761575</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>256</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="299">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46172.18038884259</v>
+        <v>46197.50927037037</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>189</v>
@@ -4463,8 +4463,8 @@
       <c r="T49" s="9">
         <v>0</v>
       </c>
-      <c r="U49" s="10" t="s">
-        <v>61</v>
+      <c r="U49" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5279,9 +5279,11 @@
       <c r="B63" s="8">
         <v>46073.79484768519</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46197.50932107639</v>
+      </c>
       <c r="D63" s="8">
-        <v>46195.6882462963</v>
+        <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>240</v>
@@ -5316,8 +5318,12 @@
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="T63" s="9">
+        <v>1</v>
+      </c>
+      <c r="U63" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5391,9 +5397,11 @@
       <c r="B65" s="8">
         <v>46073.79484829861</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46197.50917609954</v>
+      </c>
       <c r="D65" s="8">
-        <v>46195.68826325232</v>
+        <v>46197.50919467593</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>246</v>
@@ -5441,10 +5449,10 @@
         <v>60</v>
       </c>
       <c r="T65" s="9">
-        <v>0</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U65" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5454,9 +5462,11 @@
       <c r="B66" s="5">
         <v>46073.79484857639</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46197.50918461806</v>
+      </c>
       <c r="D66" s="5">
-        <v>46195.68826268519</v>
+        <v>46197.50920605324</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>250</v>
@@ -5504,10 +5514,10 @@
         <v>60</v>
       </c>
       <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U66" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5517,9 +5527,11 @@
       <c r="B67" s="8">
         <v>46073.79484884259</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46197.50919322917</v>
+      </c>
       <c r="D67" s="8">
-        <v>46195.68826314815</v>
+        <v>46197.509207361116</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>253</v>
@@ -5567,10 +5579,10 @@
         <v>60</v>
       </c>
       <c r="T67" s="9">
-        <v>0</v>
-      </c>
-      <c r="U67" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5580,9 +5592,11 @@
       <c r="B68" s="5">
         <v>46076.6229305787</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46197.50920206019</v>
+      </c>
       <c r="D68" s="5">
-        <v>46195.688253761575</v>
+        <v>46197.50921739583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>256</v>
@@ -5630,10 +5644,10 @@
         <v>60</v>
       </c>
       <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U68" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5643,9 +5657,11 @@
       <c r="B69" s="8">
         <v>46073.79484912037</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46197.5092531713</v>
+      </c>
       <c r="D69" s="8">
-        <v>46171.174060300924</v>
+        <v>46197.50926989583</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>192</v>
@@ -5691,10 +5707,10 @@
         <v>60</v>
       </c>
       <c r="T69" s="9">
-        <v>0</v>
-      </c>
-      <c r="U69" s="10" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U69" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5704,9 +5720,11 @@
       <c r="B70" s="5">
         <v>46073.794849432874</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46197.50929818287</v>
+      </c>
       <c r="D70" s="5">
-        <v>46173.191133125</v>
+        <v>46197.50932179399</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>193</v>
@@ -5752,10 +5770,10 @@
         <v>60</v>
       </c>
       <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="10" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U70" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5814,7 +5832,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46176.20449607639</v>
+        <v>46197.50931729167</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>267</v>
@@ -5862,8 +5880,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="10" t="s">
-        <v>61</v>
+      <c r="U72" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1620,13 +1620,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.79484634259</v>
+        <v>46073.62817967593</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.716893206016</v>
+        <v>46092.55022653935</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.71434277778</v>
+        <v>46129.547676111106</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1669,13 +1669,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.794846689816</v>
+        <v>46073.62818002315</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71686800926</v>
+        <v>46092.550201342594</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877754201385</v>
+        <v>46133.71108753472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1734,13 +1734,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.794847060184</v>
+        <v>46073.62818039352</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.716868564814</v>
+        <v>46092.55020189815</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.64561201389</v>
+        <v>46134.47894534722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1799,13 +1799,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.79484736111</v>
+        <v>46073.628180694446</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71686905093</v>
+        <v>46092.55020238426</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.64560787037</v>
+        <v>46134.478941203706</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1864,13 +1864,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.794847627316</v>
+        <v>46073.628180960644</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71686943287</v>
+        <v>46092.5502027662</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.64560351852</v>
+        <v>46134.478936851854</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1929,13 +1929,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.7948479051</v>
+        <v>46073.628181238426</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71687001157</v>
+        <v>46092.55020334491</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.64559775463</v>
+        <v>46134.478931087964</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -1994,13 +1994,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.794848668986</v>
+        <v>46073.628182002314</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.60128928241</v>
+        <v>46129.434622615736</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.71438604167</v>
+        <v>46129.547719375</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2043,13 +2043,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.794848958336</v>
+        <v>46073.628182291664</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54943753472</v>
+        <v>46097.382770868055</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.549452499996</v>
+        <v>46097.38278583333</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2108,13 +2108,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.79484923611</v>
+        <v>46073.628182569446</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.60127643518</v>
+        <v>46129.43460976852</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.171658692125</v>
+        <v>46154.00499202547</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2173,13 +2173,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.794849513884</v>
+        <v>46073.62818284723</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.54717446759</v>
+        <v>46097.380507800925</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.71444074074</v>
+        <v>46129.547774074075</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2222,13 +2222,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.79484703703</v>
+        <v>46073.628180370375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54673729167</v>
+        <v>46097.380070625004</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.554936064815</v>
+        <v>46104.38826939814</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2287,13 +2287,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.794847592595</v>
+        <v>46073.62818092592</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54711586806</v>
+        <v>46097.38044920139</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.55553096065</v>
+        <v>46104.388864293986</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2352,13 +2352,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.79484783565</v>
+        <v>46073.628181168984</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.54692731482</v>
+        <v>46097.38026064815</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.56897644676</v>
+        <v>46104.4023097801</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2417,13 +2417,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.79484809028</v>
+        <v>46073.62818142361</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.5471527662</v>
+        <v>46097.38048609954</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.77890356482</v>
+        <v>46100.612236898145</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2482,13 +2482,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.79484833333</v>
+        <v>46073.62818166667</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.50368701389</v>
+        <v>46114.33702034722</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.50370078704</v>
+        <v>46114.33703412037</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2535,13 +2535,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.81311775463</v>
+        <v>46101.64645108796</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.56950603009</v>
+        <v>46104.40283936342</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2600,13 +2600,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.547598136574</v>
+        <v>46097.3809314699</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.56972186343</v>
+        <v>46104.40305519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2665,13 +2665,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.79484905093</v>
+        <v>46073.62818238426</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54952784722</v>
+        <v>46097.38286118055</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.570394375</v>
+        <v>46104.40372770833</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2730,13 +2730,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.79484929398</v>
+        <v>46073.62818262732</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.81417637732</v>
+        <v>46101.647509710645</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.814193136575</v>
+        <v>46101.64752646991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2795,13 +2795,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.58214225694</v>
+        <v>46076.41547559028</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.50366746528</v>
+        <v>46114.33700079861</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.503793055555</v>
+        <v>46114.337126388884</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2860,13 +2860,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.79484642361</v>
+        <v>46073.62817975694</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.54785292824</v>
+        <v>46097.38118626157</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.778066307874</v>
+        <v>46100.6113996412</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2925,13 +2925,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.79484674768</v>
+        <v>46073.62818008102</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.71470650463</v>
+        <v>46129.54803983796</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.71472099537</v>
+        <v>46129.548054328705</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2978,13 +2978,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.54735603009</v>
+        <v>46097.380689363425</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.20558688657</v>
+        <v>46134.03892021991</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3043,13 +3043,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.794847268524</v>
+        <v>46073.62818060185</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.54729899306</v>
+        <v>46097.380632326385</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.813124513894</v>
+        <v>46101.64645784722</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3108,13 +3108,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.79484752315</v>
+        <v>46073.62818085648</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54733972222</v>
+        <v>46097.38067305555</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.54734099537</v>
+        <v>46097.3806743287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3173,13 +3173,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.7948477662</v>
+        <v>46073.62818109954</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.58757038195</v>
+        <v>46104.420903715276</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.20558681713</v>
+        <v>46134.03892015046</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3238,13 +3238,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.79484803241</v>
+        <v>46073.62818136574</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.58750148148</v>
+        <v>46104.42083481481</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.58750311343</v>
+        <v>46104.42083644676</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3299,13 +3299,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.79484828704</v>
+        <v>46073.62818162037</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.58755459491</v>
+        <v>46104.42088792824</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.58755618056</v>
+        <v>46104.42088951389</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3360,13 +3360,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.79484853009</v>
+        <v>46073.62818186343</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.583659386575</v>
+        <v>46104.41699271991</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.58367331019</v>
+        <v>46104.41700664352</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3425,13 +3425,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.79484878472</v>
+        <v>46073.62818211806</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.58357604167</v>
+        <v>46104.416909374995</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.583577881946</v>
+        <v>46104.416911215274</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3486,13 +3486,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.58364541667</v>
+        <v>46104.41697875</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.58364686342</v>
+        <v>46104.41698019676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3547,13 +3547,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.79484739584</v>
+        <v>46073.62818072917</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.584286990736</v>
+        <v>46104.41762032408</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.2060525</v>
+        <v>46165.039385833334</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3612,13 +3612,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.79484769676</v>
+        <v>46073.62818103009</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.58417509259</v>
+        <v>46104.417508425926</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.58417674768</v>
+        <v>46104.41751008102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3673,13 +3673,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.79484798611</v>
+        <v>46073.628181319444</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.58422200232</v>
+        <v>46104.41755533565</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.58422371528</v>
+        <v>46104.41755704861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3734,13 +3734,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.79484826389</v>
+        <v>46073.62818159722</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.58427152778</v>
+        <v>46104.41760486111</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.58427320602</v>
+        <v>46104.417606539355</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3795,13 +3795,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.794848564816</v>
+        <v>46073.62818189815</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.801113587964</v>
+        <v>46114.63444692129</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.801124247686</v>
+        <v>46114.63445758102</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3860,13 +3860,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.79484883102</v>
+        <v>46073.62818216435</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.591430416665</v>
+        <v>46112.42476375</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.59143256945</v>
+        <v>46112.424765902775</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3921,13 +3921,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.79484913194</v>
+        <v>46073.628182465276</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.80109980324</v>
+        <v>46114.63443313657</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.80110109954</v>
+        <v>46114.63443443287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3982,13 +3982,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.58266418982</v>
+        <v>46076.415997523145</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.49794984954</v>
+        <v>46112.331283182866</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.19208922454</v>
+        <v>46134.02542255787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4047,13 +4047,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.58280495371</v>
+        <v>46076.41613828704</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.7145863426</v>
+        <v>46129.547919675926</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.714587407405</v>
+        <v>46129.54792074074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4108,13 +4108,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.58302251158</v>
+        <v>46076.41635584491</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.7146324537</v>
+        <v>46129.54796578704</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.714633553245</v>
+        <v>46129.547966886574</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4169,11 +4169,11 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.794849467595</v>
+        <v>46073.62818280092</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46114.798811886576</v>
+        <v>46114.632145219904</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4218,13 +4218,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.79484973379</v>
+        <v>46073.62818306713</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.79848856482</v>
+        <v>46114.63182189815</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.79850829861</v>
+        <v>46114.63184163194</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4283,13 +4283,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.79484638889</v>
+        <v>46073.62817972222</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.79872664352</v>
+        <v>46114.63205997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.79874244213</v>
+        <v>46114.63207577546</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4348,13 +4348,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.80996193287</v>
+        <v>46087.6432952662</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.798792835645</v>
+        <v>46114.63212616898</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.798815428236</v>
+        <v>46114.63214876158</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4411,11 +4411,11 @@
         <v>188</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.810021701385</v>
+        <v>46087.64335503472</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46197.50927037037</v>
+        <v>46197.3426037037</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>189</v>
@@ -4472,13 +4472,13 @@
         <v>194</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.79484671296</v>
+        <v>46073.6281800463</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.673340787034</v>
+        <v>46121.50667412037</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.67335355324</v>
+        <v>46121.50668688657</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>195</v>
@@ -4525,13 +4525,13 @@
         <v>197</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.79484696759</v>
+        <v>46073.628180300926</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.799450266204</v>
+        <v>46120.63278359953</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.79946753472</v>
+        <v>46120.63280086806</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>198</v>
@@ -4590,13 +4590,13 @@
         <v>202</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.794847233796</v>
+        <v>46073.62818056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.67332476852</v>
+        <v>46121.50665810185</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.67355936342</v>
+        <v>46121.50689269676</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>203</v>
@@ -4655,13 +4655,13 @@
         <v>207</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.794847488425</v>
+        <v>46073.62818082176</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76737151621</v>
+        <v>46132.60070484954</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.76738453704</v>
+        <v>46132.60071787037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>208</v>
@@ -4708,13 +4708,13 @@
         <v>210</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.79484775463</v>
+        <v>46073.62818108796</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.79905210648</v>
+        <v>46120.632385439814</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.92421190972</v>
+        <v>46132.757545243054</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>211</v>
@@ -4773,13 +4773,13 @@
         <v>215</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.79484800926</v>
+        <v>46073.62818134259</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.561391932875</v>
+        <v>46132.394725266204</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.561408657406</v>
+        <v>46132.39474199074</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>216</v>
@@ -4838,13 +4838,13 @@
         <v>219</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76735306713</v>
+        <v>46132.60068640046</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.76737177084</v>
+        <v>46132.60070510417</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>220</v>
@@ -4903,13 +4903,13 @@
         <v>223</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.71626407407</v>
+        <v>46129.54959740741</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.71634960648</v>
+        <v>46129.54968293982</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -4952,13 +4952,13 @@
         <v>225</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.61763545139</v>
+        <v>46122.450968784724</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.61765378472</v>
+        <v>46122.450987118056</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>226</v>
@@ -5017,13 +5017,13 @@
         <v>228</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.79484665509</v>
+        <v>46073.62817998843</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.659079606485</v>
+        <v>46122.49241293981</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.17597939815</v>
+        <v>46147.00931273148</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5082,13 +5082,13 @@
         <v>230</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.794847129626</v>
+        <v>46073.62818046296</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.669174490744</v>
+        <v>46127.50250782407</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.17597951389</v>
+        <v>46147.00931284722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>231</v>
@@ -5147,13 +5147,13 @@
         <v>233</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.794847418976</v>
+        <v>46073.62818075232</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.66922835648</v>
+        <v>46127.50256168982</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.174760891205</v>
+        <v>46169.00809422454</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>234</v>
@@ -5212,13 +5212,13 @@
         <v>236</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.583608553236</v>
+        <v>46076.41694188658</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.7162494213</v>
+        <v>46129.549582754626</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.200935636574</v>
+        <v>46136.0342689699</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>237</v>
@@ -5277,13 +5277,13 @@
         <v>239</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.79484768519</v>
+        <v>46073.62818101852</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.50932107639</v>
+        <v>46197.342654409724</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.50933475695</v>
+        <v>46197.34266809028</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>240</v>
@@ -5330,13 +5330,13 @@
         <v>242</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.68823886574</v>
+        <v>46195.521572199075</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.688256319445</v>
+        <v>46195.52158965278</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>243</v>
@@ -5395,13 +5395,13 @@
         <v>245</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50917609954</v>
+        <v>46197.34250943287</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50919467593</v>
+        <v>46197.34252800926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>246</v>
@@ -5460,13 +5460,13 @@
         <v>249</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50918461806</v>
+        <v>46197.34251795139</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50920605324</v>
+        <v>46197.34253938658</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>250</v>
@@ -5525,13 +5525,13 @@
         <v>252</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.79484884259</v>
+        <v>46073.628182175926</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.50919322917</v>
+        <v>46197.3425265625</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.509207361116</v>
+        <v>46197.342540694444</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>253</v>
@@ -5590,13 +5590,13 @@
         <v>255</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.6229305787</v>
+        <v>46076.45626391204</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.50920206019</v>
+        <v>46197.342535393516</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.50921739583</v>
+        <v>46197.34255072917</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>256</v>
@@ -5655,13 +5655,13 @@
         <v>258</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.79484912037</v>
+        <v>46073.6281824537</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.5092531713</v>
+        <v>46197.34258650463</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.50926989583</v>
+        <v>46197.34260322917</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>192</v>
@@ -5718,13 +5718,13 @@
         <v>261</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.794849432874</v>
+        <v>46073.6281827662</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.50929818287</v>
+        <v>46197.34263151621</v>
       </c>
       <c r="D70" s="5">
-        <v>46197.50932179399</v>
+        <v>46197.342655127315</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>193</v>
@@ -5781,11 +5781,11 @@
         <v>263</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.794846979166</v>
+        <v>46073.6281803125</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.66949746528</v>
+        <v>46090.50283079861</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>264</v>
@@ -5828,11 +5828,11 @@
         <v>266</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.794847384255</v>
+        <v>46073.62818071759</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.50931729167</v>
+        <v>46197.342650624996</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>267</v>
@@ -5889,11 +5889,11 @@
         <v>271</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.79484767361</v>
+        <v>46073.62818100695</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.16820392361</v>
+        <v>46179.00153725695</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>272</v>
@@ -5952,11 +5952,11 @@
         <v>275</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46182.18235991898</v>
+        <v>46182.01569325231</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>276</v>
@@ -6013,11 +6013,11 @@
         <v>278</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.79484825231</v>
+        <v>46073.62818158565</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46183.188021875</v>
+        <v>46183.02135520833</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>279</v>
@@ -6074,11 +6074,11 @@
         <v>281</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.66953237269</v>
+        <v>46090.50286570602</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>282</v>
@@ -6121,11 +6121,11 @@
         <v>284</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.79484886574</v>
+        <v>46073.62818219907</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>285</v>
@@ -6184,11 +6184,11 @@
         <v>289</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.79484915509</v>
+        <v>46073.62818248842</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>290</v>
@@ -6247,11 +6247,11 @@
         <v>291</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.64638520833</v>
+        <v>46090.47971854167</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.66956530092</v>
+        <v>46090.50289863426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>292</v>
@@ -6294,11 +6294,11 @@
         <v>294</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.646490810184</v>
+        <v>46090.47982414352</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.18765634259</v>
+        <v>46191.020989675926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>295</v>
@@ -6357,11 +6357,11 @@
         <v>297</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.64689480324</v>
+        <v>46090.48022813657</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46192.17605807871</v>
+        <v>46192.00939141204</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>298</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="301">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -633,31 +633,37 @@
     <t>Planos Preliminares</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213381527095358</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor,Planos Preliminares</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213561126963620</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213381527095358</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor,Planos Preliminares</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213561126963620</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
   </si>
   <si>
     <t>Montaje Alabe,Montaje Rodete,Ingenieria y diseño:,Armado,Control de calidad Armado,Montaje sensores,Montaje motor</t>
@@ -1620,13 +1626,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.62817967593</v>
+        <v>46073.79484634259</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55022653935</v>
+        <v>46092.716893206016</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.547676111106</v>
+        <v>46129.71434277778</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1669,13 +1675,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.62818002315</v>
+        <v>46073.794846689816</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.550201342594</v>
+        <v>46092.71686800926</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71108753472</v>
+        <v>46133.877754201385</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1734,13 +1740,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.62818039352</v>
+        <v>46073.794847060184</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55020189815</v>
+        <v>46092.716868564814</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.47894534722</v>
+        <v>46134.64561201389</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1799,13 +1805,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.628180694446</v>
+        <v>46073.79484736111</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55020238426</v>
+        <v>46092.71686905093</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.478941203706</v>
+        <v>46134.64560787037</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1864,13 +1870,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.628180960644</v>
+        <v>46073.794847627316</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.5502027662</v>
+        <v>46092.71686943287</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.478936851854</v>
+        <v>46134.64560351852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1929,13 +1935,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.628181238426</v>
+        <v>46073.7948479051</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55020334491</v>
+        <v>46092.71687001157</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.478931087964</v>
+        <v>46134.64559775463</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -1994,13 +2000,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.628182002314</v>
+        <v>46073.794848668986</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.434622615736</v>
+        <v>46129.60128928241</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.547719375</v>
+        <v>46129.71438604167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2043,13 +2049,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.628182291664</v>
+        <v>46073.794848958336</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.382770868055</v>
+        <v>46097.54943753472</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38278583333</v>
+        <v>46097.549452499996</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2108,13 +2114,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.628182569446</v>
+        <v>46073.79484923611</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.43460976852</v>
+        <v>46129.60127643518</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.00499202547</v>
+        <v>46154.171658692125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2173,13 +2179,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.62818284723</v>
+        <v>46073.794849513884</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.380507800925</v>
+        <v>46097.54717446759</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.547774074075</v>
+        <v>46129.71444074074</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2222,13 +2228,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.628180370375</v>
+        <v>46073.79484703703</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.380070625004</v>
+        <v>46097.54673729167</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.38826939814</v>
+        <v>46104.554936064815</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2287,13 +2293,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.62818092592</v>
+        <v>46073.794847592595</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.38044920139</v>
+        <v>46097.54711586806</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.388864293986</v>
+        <v>46104.55553096065</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2352,13 +2358,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.628181168984</v>
+        <v>46073.79484783565</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38026064815</v>
+        <v>46097.54692731482</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.4023097801</v>
+        <v>46104.56897644676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2417,13 +2423,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.62818142361</v>
+        <v>46073.79484809028</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.38048609954</v>
+        <v>46097.5471527662</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.612236898145</v>
+        <v>46100.77890356482</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2482,13 +2488,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.62818166667</v>
+        <v>46073.79484833333</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.33702034722</v>
+        <v>46114.50368701389</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.33703412037</v>
+        <v>46114.50370078704</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2535,13 +2541,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.64645108796</v>
+        <v>46101.81311775463</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.40283936342</v>
+        <v>46104.56950603009</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2600,13 +2606,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3809314699</v>
+        <v>46097.547598136574</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.40305519676</v>
+        <v>46104.56972186343</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2665,13 +2671,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.62818238426</v>
+        <v>46073.79484905093</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38286118055</v>
+        <v>46097.54952784722</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.40372770833</v>
+        <v>46104.570394375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2730,13 +2736,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.62818262732</v>
+        <v>46073.79484929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.647509710645</v>
+        <v>46101.81417637732</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.64752646991</v>
+        <v>46101.814193136575</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2795,13 +2801,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.41547559028</v>
+        <v>46076.58214225694</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.33700079861</v>
+        <v>46114.50366746528</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.337126388884</v>
+        <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2860,13 +2866,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.62817975694</v>
+        <v>46073.79484642361</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38118626157</v>
+        <v>46097.54785292824</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.6113996412</v>
+        <v>46100.778066307874</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2925,13 +2931,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.62818008102</v>
+        <v>46073.79484674768</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.54803983796</v>
+        <v>46129.71470650463</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.548054328705</v>
+        <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2978,13 +2984,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.380689363425</v>
+        <v>46097.54735603009</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.03892021991</v>
+        <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3043,13 +3049,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.62818060185</v>
+        <v>46073.794847268524</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.380632326385</v>
+        <v>46097.54729899306</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.64645784722</v>
+        <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3108,13 +3114,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.62818085648</v>
+        <v>46073.79484752315</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38067305555</v>
+        <v>46097.54733972222</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.3806743287</v>
+        <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3173,13 +3179,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.62818109954</v>
+        <v>46073.7948477662</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.420903715276</v>
+        <v>46104.58757038195</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.03892015046</v>
+        <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3238,13 +3244,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.62818136574</v>
+        <v>46073.79484803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.42083481481</v>
+        <v>46104.58750148148</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.42083644676</v>
+        <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3299,13 +3305,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.62818162037</v>
+        <v>46073.79484828704</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.42088792824</v>
+        <v>46104.58755459491</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42088951389</v>
+        <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3360,13 +3366,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.62818186343</v>
+        <v>46073.79484853009</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.41699271991</v>
+        <v>46104.583659386575</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.41700664352</v>
+        <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3425,13 +3431,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.62818211806</v>
+        <v>46073.79484878472</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.416909374995</v>
+        <v>46104.58357604167</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.416911215274</v>
+        <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3486,13 +3492,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.41697875</v>
+        <v>46104.58364541667</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.41698019676</v>
+        <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3547,13 +3553,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.62818072917</v>
+        <v>46073.79484739584</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.41762032408</v>
+        <v>46104.584286990736</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.039385833334</v>
+        <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3612,13 +3618,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.62818103009</v>
+        <v>46073.79484769676</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.417508425926</v>
+        <v>46104.58417509259</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.41751008102</v>
+        <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3673,13 +3679,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.628181319444</v>
+        <v>46073.79484798611</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.41755533565</v>
+        <v>46104.58422200232</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.41755704861</v>
+        <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3734,13 +3740,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.62818159722</v>
+        <v>46073.79484826389</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.41760486111</v>
+        <v>46104.58427152778</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.417606539355</v>
+        <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3795,13 +3801,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.62818189815</v>
+        <v>46073.794848564816</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.63444692129</v>
+        <v>46114.801113587964</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.63445758102</v>
+        <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3860,13 +3866,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.62818216435</v>
+        <v>46073.79484883102</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.42476375</v>
+        <v>46112.591430416665</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.424765902775</v>
+        <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3921,13 +3927,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.628182465276</v>
+        <v>46073.79484913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.63443313657</v>
+        <v>46114.80109980324</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.63443443287</v>
+        <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3982,13 +3988,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.415997523145</v>
+        <v>46076.58266418982</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.331283182866</v>
+        <v>46112.49794984954</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.02542255787</v>
+        <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4047,13 +4053,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.41613828704</v>
+        <v>46076.58280495371</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.547919675926</v>
+        <v>46129.7145863426</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.54792074074</v>
+        <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4108,13 +4114,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.41635584491</v>
+        <v>46076.58302251158</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.54796578704</v>
+        <v>46129.7146324537</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.547966886574</v>
+        <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4169,11 +4175,11 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.62818280092</v>
+        <v>46073.794849467595</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46114.632145219904</v>
+        <v>46114.798811886576</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4218,13 +4224,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.62818306713</v>
+        <v>46073.79484973379</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.63182189815</v>
+        <v>46114.79848856482</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.63184163194</v>
+        <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4283,13 +4289,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.62817972222</v>
+        <v>46073.79484638889</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.63205997685</v>
+        <v>46114.79872664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.63207577546</v>
+        <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4348,13 +4354,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.6432952662</v>
+        <v>46087.80996193287</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.63212616898</v>
+        <v>46114.798792835645</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.63214876158</v>
+        <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4363,10 +4369,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4388,7 +4394,7 @@
         <v>182</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q48" s="5">
         <v>46085</v>
@@ -4408,26 +4414,26 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.64335503472</v>
+        <v>46087.810021701385</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46197.3426037037</v>
+        <v>46197.50927037037</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4446,10 +4452,10 @@
         <v>174</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q49" s="8">
         <v>46171</v>
@@ -4469,19 +4475,19 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.6281800463</v>
+        <v>46073.79484671296</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.50667412037</v>
+        <v>46121.673340787034</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.50668688657</v>
+        <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4505,7 +4511,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4522,28 +4528,28 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.628180300926</v>
+        <v>46073.79484696759</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.63278359953</v>
+        <v>46120.799450266204</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.63280086806</v>
+        <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I51" s="8">
         <v>46073</v>
@@ -4561,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q51" s="8">
         <v>46073</v>
@@ -4587,28 +4593,28 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.62818056713</v>
+        <v>46073.794847233796</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.50665810185</v>
+        <v>46121.67332476852</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.50689269676</v>
+        <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I52" s="5">
         <v>46077</v>
@@ -4626,13 +4632,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q52" s="5">
         <v>46077</v>
@@ -4652,19 +4658,19 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.62818082176</v>
+        <v>46073.794847488425</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.60070484954</v>
+        <v>46132.76737151621</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.60071787037</v>
+        <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4688,7 +4694,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4705,28 +4711,28 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.62818108796</v>
+        <v>46073.79484775463</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.632385439814</v>
+        <v>46120.79905210648</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.757545243054</v>
+        <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I54" s="5">
         <v>46079</v>
@@ -4744,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q54" s="5">
         <v>46079</v>
@@ -4770,28 +4776,28 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B55" s="8">
+        <v>46073.79484800926</v>
+      </c>
+      <c r="C55" s="8">
+        <v>46132.561391932875</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46132.561408657406</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>215</v>
-      </c>
-      <c r="B55" s="8">
-        <v>46073.62818134259</v>
-      </c>
-      <c r="C55" s="8">
-        <v>46132.394725266204</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46132.39474199074</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I55" s="8">
         <v>46090</v>
@@ -4809,13 +4815,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q55" s="8">
         <v>46090</v>
@@ -4835,28 +4841,28 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.60068640046</v>
+        <v>46132.76735306713</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.60070510417</v>
+        <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I56" s="5">
         <v>46119</v>
@@ -4874,13 +4880,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q56" s="5">
         <v>46119</v>
@@ -4900,19 +4906,19 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.54959740741</v>
+        <v>46129.71626407407</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.54968293982</v>
+        <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4936,7 +4942,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4949,28 +4955,28 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.450968784724</v>
+        <v>46122.61763545139</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.450987118056</v>
+        <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46078</v>
@@ -4988,13 +4994,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q58" s="5">
         <v>46078</v>
@@ -5014,16 +5020,16 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.62817998843</v>
+        <v>46073.79484665509</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.49241293981</v>
+        <v>46122.659079606485</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.00931273148</v>
+        <v>46147.17597939815</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5032,10 +5038,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I59" s="8">
         <v>46142</v>
@@ -5053,13 +5059,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q59" s="8">
         <v>46142</v>
@@ -5079,28 +5085,28 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.62818046296</v>
+        <v>46073.794847129626</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.50250782407</v>
+        <v>46127.669174490744</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.00931284722</v>
+        <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46142</v>
@@ -5118,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q60" s="5">
         <v>46142</v>
@@ -5144,28 +5150,28 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.62818075232</v>
+        <v>46073.794847418976</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.50256168982</v>
+        <v>46127.66922835648</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.00809422454</v>
+        <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I61" s="8">
         <v>46164</v>
@@ -5183,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q61" s="8">
         <v>46167</v>
@@ -5209,28 +5215,28 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.41694188658</v>
+        <v>46076.583608553236</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.549582754626</v>
+        <v>46129.7162494213</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.0342689699</v>
+        <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I62" s="5">
         <v>46134</v>
@@ -5248,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>171</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q62" s="5">
         <v>46134</v>
@@ -5274,19 +5280,19 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.62818101852</v>
+        <v>46073.79484768519</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.342654409724</v>
+        <v>46197.50932107639</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.34266809028</v>
+        <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5310,7 +5316,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5327,19 +5333,19 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.521572199075</v>
+        <v>46195.68823886574</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.52158965278</v>
+        <v>46195.688256319445</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5366,13 +5372,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q64" s="5">
         <v>46121</v>
@@ -5392,19 +5398,19 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.34250943287</v>
+        <v>46197.50917609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.34252800926</v>
+        <v>46197.50919467593</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5431,13 +5437,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q65" s="8">
         <v>46169</v>
@@ -5457,19 +5463,19 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.34251795139</v>
+        <v>46197.50918461806</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.34253938658</v>
+        <v>46197.50920605324</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5496,13 +5502,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q66" s="5">
         <v>46147</v>
@@ -5522,19 +5528,19 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.628182175926</v>
+        <v>46073.79484884259</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.3425265625</v>
+        <v>46197.50919322917</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.342540694444</v>
+        <v>46197.509207361116</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5561,13 +5567,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q67" s="8">
         <v>46149</v>
@@ -5587,19 +5593,19 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.45626391204</v>
+        <v>46076.6229305787</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.342535393516</v>
+        <v>46197.50920206019</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.34255072917</v>
+        <v>46197.50921739583</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5626,13 +5632,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q68" s="5">
         <v>46136</v>
@@ -5652,19 +5658,19 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.6281824537</v>
+        <v>46073.79484912037</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.34258650463</v>
+        <v>46197.5092531713</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.34260322917</v>
+        <v>46197.50926989583</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5689,13 +5695,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q69" s="8">
         <v>46170</v>
@@ -5715,19 +5721,19 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.6281827662</v>
+        <v>46073.794849432874</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.34263151621</v>
+        <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46197.342655127315</v>
+        <v>46197.50932179399</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5752,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q70" s="5">
         <v>46172</v>
@@ -5778,17 +5784,17 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.6281803125</v>
+        <v>46073.794846979166</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.50283079861</v>
+        <v>46090.66949746528</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5812,7 +5818,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5825,26 +5831,26 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.62818071759</v>
+        <v>46073.794847384255</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.342650624996</v>
+        <v>46197.50931729167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5860,13 +5866,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q72" s="5">
         <v>46175</v>
@@ -5886,17 +5892,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.62818100695</v>
+        <v>46073.79484767361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.00153725695</v>
+        <v>46179.16820392361</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5923,13 +5929,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q73" s="8">
         <v>46176</v>
@@ -5949,26 +5955,26 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46182.01569325231</v>
+        <v>46182.18235991898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5984,13 +5990,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q74" s="5">
         <v>46181</v>
@@ -6010,26 +6016,26 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.62818158565</v>
+        <v>46073.79484825231</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46183.02135520833</v>
+        <v>46183.188021875</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -6045,13 +6051,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q75" s="8">
         <v>46182</v>
@@ -6071,17 +6077,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.50286570602</v>
+        <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6105,7 +6111,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6118,26 +6124,26 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.62818219907</v>
+        <v>46073.79484886574</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I77" s="8">
         <v>46182</v>
@@ -6155,13 +6161,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q77" s="8">
         <v>46183</v>
@@ -6181,26 +6187,26 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.62818248842</v>
+        <v>46073.79484915509</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I78" s="5">
         <v>46182</v>
@@ -6218,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q78" s="5">
         <v>46183</v>
@@ -6244,17 +6250,17 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.47971854167</v>
+        <v>46090.64638520833</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.50289863426</v>
+        <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6278,7 +6284,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6291,17 +6297,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.47982414352</v>
+        <v>46090.646490810184</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.020989675926</v>
+        <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6328,13 +6334,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q80" s="5">
         <v>46182</v>
@@ -6354,17 +6360,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.48022813657</v>
+        <v>46090.64689480324</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46192.00939141204</v>
+        <v>46192.17605807871</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6391,13 +6397,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q81" s="8">
         <v>46191</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1626,13 +1626,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.79484634259</v>
+        <v>46073.62817967593</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.716893206016</v>
+        <v>46092.55022653935</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.71434277778</v>
+        <v>46129.547676111106</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1675,13 +1675,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.794846689816</v>
+        <v>46073.62818002315</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71686800926</v>
+        <v>46092.550201342594</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877754201385</v>
+        <v>46133.71108753472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1740,13 +1740,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.794847060184</v>
+        <v>46073.62818039352</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.716868564814</v>
+        <v>46092.55020189815</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.64561201389</v>
+        <v>46134.47894534722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1805,13 +1805,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.79484736111</v>
+        <v>46073.628180694446</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71686905093</v>
+        <v>46092.55020238426</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.64560787037</v>
+        <v>46134.478941203706</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1870,13 +1870,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.794847627316</v>
+        <v>46073.628180960644</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71686943287</v>
+        <v>46092.5502027662</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.64560351852</v>
+        <v>46134.478936851854</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1935,13 +1935,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.7948479051</v>
+        <v>46073.628181238426</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71687001157</v>
+        <v>46092.55020334491</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.64559775463</v>
+        <v>46134.478931087964</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2000,13 +2000,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.794848668986</v>
+        <v>46073.628182002314</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.60128928241</v>
+        <v>46129.434622615736</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.71438604167</v>
+        <v>46129.547719375</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2049,13 +2049,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.794848958336</v>
+        <v>46073.628182291664</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54943753472</v>
+        <v>46097.382770868055</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.549452499996</v>
+        <v>46097.38278583333</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2114,13 +2114,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.79484923611</v>
+        <v>46073.628182569446</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.60127643518</v>
+        <v>46129.43460976852</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.171658692125</v>
+        <v>46154.00499202547</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2179,13 +2179,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.794849513884</v>
+        <v>46073.62818284723</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.54717446759</v>
+        <v>46097.380507800925</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.71444074074</v>
+        <v>46129.547774074075</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2228,13 +2228,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.79484703703</v>
+        <v>46073.628180370375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54673729167</v>
+        <v>46097.380070625004</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.554936064815</v>
+        <v>46104.38826939814</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2293,13 +2293,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.794847592595</v>
+        <v>46073.62818092592</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54711586806</v>
+        <v>46097.38044920139</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.55553096065</v>
+        <v>46104.388864293986</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2358,13 +2358,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.79484783565</v>
+        <v>46073.628181168984</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.54692731482</v>
+        <v>46097.38026064815</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.56897644676</v>
+        <v>46104.4023097801</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2423,13 +2423,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.79484809028</v>
+        <v>46073.62818142361</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.5471527662</v>
+        <v>46097.38048609954</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.77890356482</v>
+        <v>46100.612236898145</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2488,13 +2488,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.79484833333</v>
+        <v>46073.62818166667</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.50368701389</v>
+        <v>46114.33702034722</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.50370078704</v>
+        <v>46114.33703412037</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2541,13 +2541,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.81311775463</v>
+        <v>46101.64645108796</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.56950603009</v>
+        <v>46104.40283936342</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2606,13 +2606,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.547598136574</v>
+        <v>46097.3809314699</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.56972186343</v>
+        <v>46104.40305519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2671,13 +2671,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.79484905093</v>
+        <v>46073.62818238426</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54952784722</v>
+        <v>46097.38286118055</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.570394375</v>
+        <v>46104.40372770833</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2736,13 +2736,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.79484929398</v>
+        <v>46073.62818262732</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.81417637732</v>
+        <v>46101.647509710645</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.814193136575</v>
+        <v>46101.64752646991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2801,13 +2801,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.58214225694</v>
+        <v>46076.41547559028</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.50366746528</v>
+        <v>46114.33700079861</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.503793055555</v>
+        <v>46114.337126388884</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2866,13 +2866,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.79484642361</v>
+        <v>46073.62817975694</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.54785292824</v>
+        <v>46097.38118626157</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.778066307874</v>
+        <v>46100.6113996412</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2931,13 +2931,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.79484674768</v>
+        <v>46073.62818008102</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.71470650463</v>
+        <v>46129.54803983796</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.71472099537</v>
+        <v>46129.548054328705</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2984,13 +2984,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.54735603009</v>
+        <v>46097.380689363425</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.20558688657</v>
+        <v>46134.03892021991</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3049,13 +3049,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.794847268524</v>
+        <v>46073.62818060185</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.54729899306</v>
+        <v>46097.380632326385</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.813124513894</v>
+        <v>46101.64645784722</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3114,13 +3114,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.79484752315</v>
+        <v>46073.62818085648</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54733972222</v>
+        <v>46097.38067305555</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.54734099537</v>
+        <v>46097.3806743287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3179,13 +3179,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.7948477662</v>
+        <v>46073.62818109954</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.58757038195</v>
+        <v>46104.420903715276</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.20558681713</v>
+        <v>46134.03892015046</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3244,13 +3244,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.79484803241</v>
+        <v>46073.62818136574</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.58750148148</v>
+        <v>46104.42083481481</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.58750311343</v>
+        <v>46104.42083644676</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3305,13 +3305,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.79484828704</v>
+        <v>46073.62818162037</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.58755459491</v>
+        <v>46104.42088792824</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.58755618056</v>
+        <v>46104.42088951389</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3366,13 +3366,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.79484853009</v>
+        <v>46073.62818186343</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.583659386575</v>
+        <v>46104.41699271991</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.58367331019</v>
+        <v>46104.41700664352</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3431,13 +3431,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.79484878472</v>
+        <v>46073.62818211806</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.58357604167</v>
+        <v>46104.416909374995</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.583577881946</v>
+        <v>46104.416911215274</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3492,13 +3492,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.58364541667</v>
+        <v>46104.41697875</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.58364686342</v>
+        <v>46104.41698019676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3553,13 +3553,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.79484739584</v>
+        <v>46073.62818072917</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.584286990736</v>
+        <v>46104.41762032408</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.2060525</v>
+        <v>46165.039385833334</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3618,13 +3618,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.79484769676</v>
+        <v>46073.62818103009</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.58417509259</v>
+        <v>46104.417508425926</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.58417674768</v>
+        <v>46104.41751008102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3679,13 +3679,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.79484798611</v>
+        <v>46073.628181319444</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.58422200232</v>
+        <v>46104.41755533565</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.58422371528</v>
+        <v>46104.41755704861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3740,13 +3740,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.79484826389</v>
+        <v>46073.62818159722</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.58427152778</v>
+        <v>46104.41760486111</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.58427320602</v>
+        <v>46104.417606539355</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3801,13 +3801,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.794848564816</v>
+        <v>46073.62818189815</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.801113587964</v>
+        <v>46114.63444692129</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.801124247686</v>
+        <v>46114.63445758102</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3866,13 +3866,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.79484883102</v>
+        <v>46073.62818216435</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.591430416665</v>
+        <v>46112.42476375</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.59143256945</v>
+        <v>46112.424765902775</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3927,13 +3927,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.79484913194</v>
+        <v>46073.628182465276</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.80109980324</v>
+        <v>46114.63443313657</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.80110109954</v>
+        <v>46114.63443443287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3988,13 +3988,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.58266418982</v>
+        <v>46076.415997523145</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.49794984954</v>
+        <v>46112.331283182866</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.19208922454</v>
+        <v>46134.02542255787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4053,13 +4053,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.58280495371</v>
+        <v>46076.41613828704</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.7145863426</v>
+        <v>46129.547919675926</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.714587407405</v>
+        <v>46129.54792074074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4114,13 +4114,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.58302251158</v>
+        <v>46076.41635584491</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.7146324537</v>
+        <v>46129.54796578704</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.714633553245</v>
+        <v>46129.547966886574</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4175,11 +4175,11 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.794849467595</v>
+        <v>46073.62818280092</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46114.798811886576</v>
+        <v>46114.632145219904</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4224,13 +4224,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.79484973379</v>
+        <v>46073.62818306713</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.79848856482</v>
+        <v>46114.63182189815</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.70688251157</v>
+        <v>46197.54021584491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4289,13 +4289,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.79484638889</v>
+        <v>46073.62817972222</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.79872664352</v>
+        <v>46114.63205997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.70691572917</v>
+        <v>46197.5402490625</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4354,13 +4354,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.80996193287</v>
+        <v>46087.6432952662</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.798792835645</v>
+        <v>46114.63212616898</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.798815428236</v>
+        <v>46114.63214876158</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4417,11 +4417,11 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.810021701385</v>
+        <v>46087.64335503472</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46197.50927037037</v>
+        <v>46197.3426037037</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4478,13 +4478,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.79484671296</v>
+        <v>46073.6281800463</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.673340787034</v>
+        <v>46121.50667412037</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.67335355324</v>
+        <v>46121.50668688657</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4531,13 +4531,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.79484696759</v>
+        <v>46073.628180300926</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.799450266204</v>
+        <v>46120.63278359953</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.79946753472</v>
+        <v>46120.63280086806</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4596,13 +4596,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.794847233796</v>
+        <v>46073.62818056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.67332476852</v>
+        <v>46121.50665810185</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.67355936342</v>
+        <v>46121.50689269676</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4661,13 +4661,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.794847488425</v>
+        <v>46073.62818082176</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76737151621</v>
+        <v>46132.60070484954</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.76738453704</v>
+        <v>46132.60071787037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4714,13 +4714,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.79484775463</v>
+        <v>46073.62818108796</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.79905210648</v>
+        <v>46120.632385439814</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.92421190972</v>
+        <v>46132.757545243054</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4779,13 +4779,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.79484800926</v>
+        <v>46073.62818134259</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.561391932875</v>
+        <v>46132.394725266204</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.561408657406</v>
+        <v>46132.39474199074</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4844,13 +4844,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76735306713</v>
+        <v>46132.60068640046</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.76737177084</v>
+        <v>46132.60070510417</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4909,13 +4909,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.71626407407</v>
+        <v>46129.54959740741</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.71634960648</v>
+        <v>46129.54968293982</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4958,13 +4958,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.61763545139</v>
+        <v>46122.450968784724</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.61765378472</v>
+        <v>46122.450987118056</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5023,13 +5023,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.79484665509</v>
+        <v>46073.62817998843</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.659079606485</v>
+        <v>46122.49241293981</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.17597939815</v>
+        <v>46147.00931273148</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5088,13 +5088,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.794847129626</v>
+        <v>46073.62818046296</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.669174490744</v>
+        <v>46127.50250782407</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.17597951389</v>
+        <v>46147.00931284722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5153,13 +5153,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.794847418976</v>
+        <v>46073.62818075232</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.66922835648</v>
+        <v>46127.50256168982</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.174760891205</v>
+        <v>46169.00809422454</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5218,13 +5218,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.583608553236</v>
+        <v>46076.41694188658</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.7162494213</v>
+        <v>46129.549582754626</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.200935636574</v>
+        <v>46136.0342689699</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5283,13 +5283,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.79484768519</v>
+        <v>46073.62818101852</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.50932107639</v>
+        <v>46197.342654409724</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.50933475695</v>
+        <v>46197.34266809028</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5336,13 +5336,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.68823886574</v>
+        <v>46195.521572199075</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.688256319445</v>
+        <v>46195.52158965278</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5401,13 +5401,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50917609954</v>
+        <v>46197.34250943287</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50919467593</v>
+        <v>46197.34252800926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5466,13 +5466,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50918461806</v>
+        <v>46197.34251795139</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50920605324</v>
+        <v>46197.34253938658</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5531,13 +5531,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.79484884259</v>
+        <v>46073.628182175926</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.50919322917</v>
+        <v>46197.3425265625</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.509207361116</v>
+        <v>46197.342540694444</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5596,13 +5596,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.6229305787</v>
+        <v>46076.45626391204</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.50920206019</v>
+        <v>46197.342535393516</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.50921739583</v>
+        <v>46197.34255072917</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5661,13 +5661,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.79484912037</v>
+        <v>46073.6281824537</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.5092531713</v>
+        <v>46197.34258650463</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.50926989583</v>
+        <v>46197.34260322917</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5724,13 +5724,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.794849432874</v>
+        <v>46073.6281827662</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.50929818287</v>
+        <v>46197.34263151621</v>
       </c>
       <c r="D70" s="5">
-        <v>46197.50932179399</v>
+        <v>46197.342655127315</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5787,11 +5787,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.794846979166</v>
+        <v>46073.6281803125</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.66949746528</v>
+        <v>46090.50283079861</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5834,11 +5834,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.794847384255</v>
+        <v>46073.62818071759</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.50931729167</v>
+        <v>46197.342650624996</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5895,11 +5895,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.79484767361</v>
+        <v>46073.62818100695</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.16820392361</v>
+        <v>46179.00153725695</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5958,11 +5958,11 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46182.18235991898</v>
+        <v>46182.01569325231</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6019,11 +6019,11 @@
         <v>280</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.79484825231</v>
+        <v>46073.62818158565</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46183.188021875</v>
+        <v>46183.02135520833</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>281</v>
@@ -6080,11 +6080,11 @@
         <v>283</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.66953237269</v>
+        <v>46090.50286570602</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>284</v>
@@ -6127,11 +6127,11 @@
         <v>286</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.79484886574</v>
+        <v>46073.62818219907</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>287</v>
@@ -6190,11 +6190,11 @@
         <v>291</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.79484915509</v>
+        <v>46073.62818248842</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>292</v>
@@ -6253,11 +6253,11 @@
         <v>293</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.64638520833</v>
+        <v>46090.47971854167</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.66956530092</v>
+        <v>46090.50289863426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>294</v>
@@ -6300,11 +6300,11 @@
         <v>296</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.646490810184</v>
+        <v>46090.47982414352</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.18765634259</v>
+        <v>46191.020989675926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>297</v>
@@ -6363,11 +6363,11 @@
         <v>299</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.64689480324</v>
+        <v>46090.48022813657</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46192.17605807871</v>
+        <v>46192.00939141204</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>300</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1626,13 +1626,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.62817967593</v>
+        <v>46073.79484634259</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55022653935</v>
+        <v>46092.716893206016</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.547676111106</v>
+        <v>46129.71434277778</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1675,13 +1675,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.62818002315</v>
+        <v>46073.794846689816</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.550201342594</v>
+        <v>46092.71686800926</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71108753472</v>
+        <v>46133.877754201385</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1740,13 +1740,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.62818039352</v>
+        <v>46073.794847060184</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55020189815</v>
+        <v>46092.716868564814</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.47894534722</v>
+        <v>46134.64561201389</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1805,13 +1805,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.628180694446</v>
+        <v>46073.79484736111</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55020238426</v>
+        <v>46092.71686905093</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.478941203706</v>
+        <v>46134.64560787037</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1870,13 +1870,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.628180960644</v>
+        <v>46073.794847627316</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.5502027662</v>
+        <v>46092.71686943287</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.478936851854</v>
+        <v>46134.64560351852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1935,13 +1935,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.628181238426</v>
+        <v>46073.7948479051</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55020334491</v>
+        <v>46092.71687001157</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.478931087964</v>
+        <v>46134.64559775463</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2000,13 +2000,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.628182002314</v>
+        <v>46073.794848668986</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.434622615736</v>
+        <v>46129.60128928241</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.547719375</v>
+        <v>46129.71438604167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2049,13 +2049,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.628182291664</v>
+        <v>46073.794848958336</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.382770868055</v>
+        <v>46097.54943753472</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38278583333</v>
+        <v>46097.549452499996</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2114,13 +2114,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.628182569446</v>
+        <v>46073.79484923611</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.43460976852</v>
+        <v>46129.60127643518</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.00499202547</v>
+        <v>46154.171658692125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2179,13 +2179,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.62818284723</v>
+        <v>46073.794849513884</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.380507800925</v>
+        <v>46097.54717446759</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.547774074075</v>
+        <v>46129.71444074074</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2228,13 +2228,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.628180370375</v>
+        <v>46073.79484703703</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.380070625004</v>
+        <v>46097.54673729167</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.38826939814</v>
+        <v>46104.554936064815</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2293,13 +2293,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.62818092592</v>
+        <v>46073.794847592595</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.38044920139</v>
+        <v>46097.54711586806</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.388864293986</v>
+        <v>46104.55553096065</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2358,13 +2358,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.628181168984</v>
+        <v>46073.79484783565</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38026064815</v>
+        <v>46097.54692731482</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.4023097801</v>
+        <v>46104.56897644676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2423,13 +2423,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.62818142361</v>
+        <v>46073.79484809028</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.38048609954</v>
+        <v>46097.5471527662</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.612236898145</v>
+        <v>46100.77890356482</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2488,13 +2488,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.62818166667</v>
+        <v>46073.79484833333</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.33702034722</v>
+        <v>46114.50368701389</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.33703412037</v>
+        <v>46114.50370078704</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2541,13 +2541,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.64645108796</v>
+        <v>46101.81311775463</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.40283936342</v>
+        <v>46104.56950603009</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2606,13 +2606,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3809314699</v>
+        <v>46097.547598136574</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.40305519676</v>
+        <v>46104.56972186343</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2671,13 +2671,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.62818238426</v>
+        <v>46073.79484905093</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38286118055</v>
+        <v>46097.54952784722</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.40372770833</v>
+        <v>46104.570394375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2736,13 +2736,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.62818262732</v>
+        <v>46073.79484929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.647509710645</v>
+        <v>46101.81417637732</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.64752646991</v>
+        <v>46101.814193136575</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2801,13 +2801,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.41547559028</v>
+        <v>46076.58214225694</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.33700079861</v>
+        <v>46114.50366746528</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.337126388884</v>
+        <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2866,13 +2866,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.62817975694</v>
+        <v>46073.79484642361</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38118626157</v>
+        <v>46097.54785292824</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.6113996412</v>
+        <v>46100.778066307874</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2931,13 +2931,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.62818008102</v>
+        <v>46073.79484674768</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.54803983796</v>
+        <v>46129.71470650463</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.548054328705</v>
+        <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2984,13 +2984,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.380689363425</v>
+        <v>46097.54735603009</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.03892021991</v>
+        <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3049,13 +3049,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.62818060185</v>
+        <v>46073.794847268524</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.380632326385</v>
+        <v>46097.54729899306</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.64645784722</v>
+        <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3114,13 +3114,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.62818085648</v>
+        <v>46073.79484752315</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38067305555</v>
+        <v>46097.54733972222</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.3806743287</v>
+        <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3179,13 +3179,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.62818109954</v>
+        <v>46073.7948477662</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.420903715276</v>
+        <v>46104.58757038195</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.03892015046</v>
+        <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3244,13 +3244,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.62818136574</v>
+        <v>46073.79484803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.42083481481</v>
+        <v>46104.58750148148</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.42083644676</v>
+        <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3305,13 +3305,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.62818162037</v>
+        <v>46073.79484828704</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.42088792824</v>
+        <v>46104.58755459491</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42088951389</v>
+        <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3366,13 +3366,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.62818186343</v>
+        <v>46073.79484853009</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.41699271991</v>
+        <v>46104.583659386575</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.41700664352</v>
+        <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3431,13 +3431,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.62818211806</v>
+        <v>46073.79484878472</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.416909374995</v>
+        <v>46104.58357604167</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.416911215274</v>
+        <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3492,13 +3492,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.41697875</v>
+        <v>46104.58364541667</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.41698019676</v>
+        <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3553,13 +3553,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.62818072917</v>
+        <v>46073.79484739584</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.41762032408</v>
+        <v>46104.584286990736</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.039385833334</v>
+        <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3618,13 +3618,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.62818103009</v>
+        <v>46073.79484769676</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.417508425926</v>
+        <v>46104.58417509259</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.41751008102</v>
+        <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3679,13 +3679,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.628181319444</v>
+        <v>46073.79484798611</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.41755533565</v>
+        <v>46104.58422200232</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.41755704861</v>
+        <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3740,13 +3740,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.62818159722</v>
+        <v>46073.79484826389</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.41760486111</v>
+        <v>46104.58427152778</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.417606539355</v>
+        <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3801,13 +3801,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.62818189815</v>
+        <v>46073.794848564816</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.63444692129</v>
+        <v>46114.801113587964</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.63445758102</v>
+        <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3866,13 +3866,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.62818216435</v>
+        <v>46073.79484883102</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.42476375</v>
+        <v>46112.591430416665</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.424765902775</v>
+        <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3927,13 +3927,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.628182465276</v>
+        <v>46073.79484913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.63443313657</v>
+        <v>46114.80109980324</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.63443443287</v>
+        <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3988,13 +3988,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.415997523145</v>
+        <v>46076.58266418982</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.331283182866</v>
+        <v>46112.49794984954</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.02542255787</v>
+        <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4053,13 +4053,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.41613828704</v>
+        <v>46076.58280495371</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.547919675926</v>
+        <v>46129.7145863426</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.54792074074</v>
+        <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4114,13 +4114,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.41635584491</v>
+        <v>46076.58302251158</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.54796578704</v>
+        <v>46129.7146324537</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.547966886574</v>
+        <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4175,11 +4175,11 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.62818280092</v>
+        <v>46073.794849467595</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46114.632145219904</v>
+        <v>46114.798811886576</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4224,13 +4224,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.62818306713</v>
+        <v>46073.79484973379</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.63182189815</v>
+        <v>46114.79848856482</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.54021584491</v>
+        <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4289,13 +4289,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.62817972222</v>
+        <v>46073.79484638889</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.63205997685</v>
+        <v>46114.79872664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.5402490625</v>
+        <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4354,13 +4354,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.6432952662</v>
+        <v>46087.80996193287</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.63212616898</v>
+        <v>46114.798792835645</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.63214876158</v>
+        <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4417,11 +4417,11 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.64335503472</v>
+        <v>46087.810021701385</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46197.3426037037</v>
+        <v>46197.50927037037</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4478,13 +4478,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.6281800463</v>
+        <v>46073.79484671296</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.50667412037</v>
+        <v>46121.673340787034</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.50668688657</v>
+        <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4531,13 +4531,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.628180300926</v>
+        <v>46073.79484696759</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.63278359953</v>
+        <v>46120.799450266204</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.63280086806</v>
+        <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4596,13 +4596,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.62818056713</v>
+        <v>46073.794847233796</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.50665810185</v>
+        <v>46121.67332476852</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.50689269676</v>
+        <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4661,13 +4661,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.62818082176</v>
+        <v>46073.794847488425</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.60070484954</v>
+        <v>46132.76737151621</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.60071787037</v>
+        <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4714,13 +4714,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.62818108796</v>
+        <v>46073.79484775463</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.632385439814</v>
+        <v>46120.79905210648</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.757545243054</v>
+        <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4779,13 +4779,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.62818134259</v>
+        <v>46073.79484800926</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.394725266204</v>
+        <v>46132.561391932875</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.39474199074</v>
+        <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4844,13 +4844,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.60068640046</v>
+        <v>46132.76735306713</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.60070510417</v>
+        <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4909,13 +4909,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.54959740741</v>
+        <v>46129.71626407407</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.54968293982</v>
+        <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4958,13 +4958,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.450968784724</v>
+        <v>46122.61763545139</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.450987118056</v>
+        <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5023,13 +5023,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.62817998843</v>
+        <v>46073.79484665509</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.49241293981</v>
+        <v>46122.659079606485</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.00931273148</v>
+        <v>46147.17597939815</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5088,13 +5088,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.62818046296</v>
+        <v>46073.794847129626</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.50250782407</v>
+        <v>46127.669174490744</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.00931284722</v>
+        <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5153,13 +5153,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.62818075232</v>
+        <v>46073.794847418976</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.50256168982</v>
+        <v>46127.66922835648</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.00809422454</v>
+        <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5218,13 +5218,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.41694188658</v>
+        <v>46076.583608553236</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.549582754626</v>
+        <v>46129.7162494213</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.0342689699</v>
+        <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5283,13 +5283,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.62818101852</v>
+        <v>46073.79484768519</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.342654409724</v>
+        <v>46197.50932107639</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.34266809028</v>
+        <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5336,13 +5336,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.521572199075</v>
+        <v>46195.68823886574</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.52158965278</v>
+        <v>46195.688256319445</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5401,13 +5401,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.34250943287</v>
+        <v>46197.50917609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.34252800926</v>
+        <v>46197.50919467593</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5466,13 +5466,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.34251795139</v>
+        <v>46197.50918461806</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.34253938658</v>
+        <v>46197.50920605324</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5531,13 +5531,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.628182175926</v>
+        <v>46073.79484884259</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.3425265625</v>
+        <v>46197.50919322917</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.342540694444</v>
+        <v>46197.509207361116</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5596,13 +5596,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.45626391204</v>
+        <v>46076.6229305787</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.342535393516</v>
+        <v>46197.50920206019</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.34255072917</v>
+        <v>46197.50921739583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5661,13 +5661,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.6281824537</v>
+        <v>46073.79484912037</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.34258650463</v>
+        <v>46197.5092531713</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.34260322917</v>
+        <v>46197.50926989583</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5724,13 +5724,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.6281827662</v>
+        <v>46073.794849432874</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.34263151621</v>
+        <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46197.342655127315</v>
+        <v>46197.50932179399</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5787,11 +5787,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.6281803125</v>
+        <v>46073.794846979166</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.50283079861</v>
+        <v>46090.66949746528</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5834,11 +5834,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.62818071759</v>
+        <v>46073.794847384255</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.342650624996</v>
+        <v>46197.50931729167</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5895,11 +5895,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.62818100695</v>
+        <v>46073.79484767361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.00153725695</v>
+        <v>46179.16820392361</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5958,11 +5958,11 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46182.01569325231</v>
+        <v>46182.18235991898</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6019,11 +6019,11 @@
         <v>280</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.62818158565</v>
+        <v>46073.79484825231</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46183.02135520833</v>
+        <v>46183.188021875</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>281</v>
@@ -6080,11 +6080,11 @@
         <v>283</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.50286570602</v>
+        <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>284</v>
@@ -6127,11 +6127,11 @@
         <v>286</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.62818219907</v>
+        <v>46073.79484886574</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>287</v>
@@ -6190,11 +6190,11 @@
         <v>291</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.62818248842</v>
+        <v>46073.79484915509</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>292</v>
@@ -6253,11 +6253,11 @@
         <v>293</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.47971854167</v>
+        <v>46090.64638520833</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.50289863426</v>
+        <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>294</v>
@@ -6300,11 +6300,11 @@
         <v>296</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.47982414352</v>
+        <v>46090.646490810184</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.020989675926</v>
+        <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>297</v>
@@ -6363,11 +6363,11 @@
         <v>299</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.48022813657</v>
+        <v>46090.64689480324</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46192.00939141204</v>
+        <v>46192.17605807871</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>300</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="302">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -934,6 +934,10 @@
   </si>
   <si>
     <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjunto PL.
+https://app.asana.com/1/402967058777498/profile/1213576320894219 quedo atento a tus comentarios si es necesario realizar una modificación o incluir más bultos</t>
   </si>
   <si>
     <t>Despacho,Logistica:</t>
@@ -5791,7 +5795,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.66949746528</v>
+        <v>46197.90012883102</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5960,9 +5964,11 @@
       <c r="B74" s="5">
         <v>46073.79484796296</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46197.90011859954</v>
+      </c>
       <c r="D74" s="5">
-        <v>46182.18235991898</v>
+        <v>46197.90013689815</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -5984,7 +5990,7 @@
         <v>26</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>26</v>
@@ -5996,7 +6002,7 @@
         <v>274</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q74" s="5">
         <v>46181</v>
@@ -6008,25 +6014,25 @@
         <v>60</v>
       </c>
       <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="10" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U74" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B75" s="8">
         <v>46073.79484825231</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46183.188021875</v>
+        <v>46197.90013631944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6057,7 +6063,7 @@
         <v>278</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q75" s="8">
         <v>46182</v>
@@ -6071,13 +6077,13 @@
       <c r="T75" s="9">
         <v>0</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>61</v>
+      <c r="U75" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B76" s="5">
         <v>46073.79484855324</v>
@@ -6087,7 +6093,7 @@
         <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6111,7 +6117,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6124,7 +6130,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B77" s="8">
         <v>46073.79484886574</v>
@@ -6134,16 +6140,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I77" s="8">
         <v>46182</v>
@@ -6161,13 +6167,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q77" s="8">
         <v>46183</v>
@@ -6187,7 +6193,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B78" s="5">
         <v>46073.79484915509</v>
@@ -6197,16 +6203,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I78" s="5">
         <v>46182</v>
@@ -6224,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q78" s="5">
         <v>46183</v>
@@ -6250,7 +6256,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B79" s="8">
         <v>46090.64638520833</v>
@@ -6260,7 +6266,7 @@
         <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6284,7 +6290,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6297,7 +6303,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B80" s="5">
         <v>46090.646490810184</v>
@@ -6307,7 +6313,7 @@
         <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6334,13 +6340,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q80" s="5">
         <v>46182</v>
@@ -6360,7 +6366,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B81" s="8">
         <v>46090.64689480324</v>
@@ -6370,7 +6376,7 @@
         <v>46192.17605807871</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6397,13 +6403,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q81" s="8">
         <v>46191</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -4181,9 +4181,11 @@
       <c r="B45" s="8">
         <v>46073.794849467595</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46198.551042673615</v>
+      </c>
       <c r="D45" s="8">
-        <v>46114.798811886576</v>
+        <v>46198.55105587963</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4218,9 +4220,11 @@
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
-      <c r="U45" s="12" t="s">
-        <v>81</v>
+      <c r="T45" s="9">
+        <v>1</v>
+      </c>
+      <c r="U45" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4423,9 +4427,11 @@
       <c r="B49" s="8">
         <v>46087.810021701385</v>
       </c>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8">
+        <v>46198.55102407407</v>
+      </c>
       <c r="D49" s="8">
-        <v>46197.50927037037</v>
+        <v>46198.551042928244</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4471,10 +4477,10 @@
         <v>60</v>
       </c>
       <c r="T49" s="9">
-        <v>0</v>
-      </c>
-      <c r="U49" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5734,7 +5740,7 @@
         <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46197.50932179399</v>
+        <v>46198.55104168982</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5782,8 +5788,8 @@
       <c r="T70" s="6">
         <v>1</v>
       </c>
-      <c r="U70" s="11" t="s">
-        <v>33</v>
+      <c r="U70" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1630,13 +1630,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.79484634259</v>
+        <v>46073.62817967593</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.716893206016</v>
+        <v>46092.55022653935</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.71434277778</v>
+        <v>46129.547676111106</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1679,13 +1679,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.794846689816</v>
+        <v>46073.62818002315</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71686800926</v>
+        <v>46092.550201342594</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877754201385</v>
+        <v>46133.71108753472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1744,13 +1744,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.794847060184</v>
+        <v>46073.62818039352</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.716868564814</v>
+        <v>46092.55020189815</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.64561201389</v>
+        <v>46134.47894534722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1809,13 +1809,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.79484736111</v>
+        <v>46073.628180694446</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71686905093</v>
+        <v>46092.55020238426</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.64560787037</v>
+        <v>46134.478941203706</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1874,13 +1874,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.794847627316</v>
+        <v>46073.628180960644</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71686943287</v>
+        <v>46092.5502027662</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.64560351852</v>
+        <v>46134.478936851854</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1939,13 +1939,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.7948479051</v>
+        <v>46073.628181238426</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71687001157</v>
+        <v>46092.55020334491</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.64559775463</v>
+        <v>46134.478931087964</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2004,13 +2004,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.794848668986</v>
+        <v>46073.628182002314</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.60128928241</v>
+        <v>46129.434622615736</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.71438604167</v>
+        <v>46129.547719375</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2053,13 +2053,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.794848958336</v>
+        <v>46073.628182291664</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54943753472</v>
+        <v>46097.382770868055</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.549452499996</v>
+        <v>46097.38278583333</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2118,13 +2118,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.79484923611</v>
+        <v>46073.628182569446</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.60127643518</v>
+        <v>46129.43460976852</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.171658692125</v>
+        <v>46154.00499202547</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2183,13 +2183,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.794849513884</v>
+        <v>46073.62818284723</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.54717446759</v>
+        <v>46097.380507800925</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.71444074074</v>
+        <v>46129.547774074075</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2232,13 +2232,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.79484703703</v>
+        <v>46073.628180370375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54673729167</v>
+        <v>46097.380070625004</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.554936064815</v>
+        <v>46104.38826939814</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2297,13 +2297,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.794847592595</v>
+        <v>46073.62818092592</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54711586806</v>
+        <v>46097.38044920139</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.55553096065</v>
+        <v>46104.388864293986</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2362,13 +2362,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.79484783565</v>
+        <v>46073.628181168984</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.54692731482</v>
+        <v>46097.38026064815</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.56897644676</v>
+        <v>46104.4023097801</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2427,13 +2427,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.79484809028</v>
+        <v>46073.62818142361</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.5471527662</v>
+        <v>46097.38048609954</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.77890356482</v>
+        <v>46100.612236898145</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2492,13 +2492,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.79484833333</v>
+        <v>46073.62818166667</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.50368701389</v>
+        <v>46114.33702034722</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.50370078704</v>
+        <v>46114.33703412037</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2545,13 +2545,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.81311775463</v>
+        <v>46101.64645108796</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.56950603009</v>
+        <v>46104.40283936342</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2610,13 +2610,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.547598136574</v>
+        <v>46097.3809314699</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.56972186343</v>
+        <v>46104.40305519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2675,13 +2675,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.79484905093</v>
+        <v>46073.62818238426</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54952784722</v>
+        <v>46097.38286118055</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.570394375</v>
+        <v>46104.40372770833</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2740,13 +2740,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.79484929398</v>
+        <v>46073.62818262732</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.81417637732</v>
+        <v>46101.647509710645</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.814193136575</v>
+        <v>46101.64752646991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2805,13 +2805,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.58214225694</v>
+        <v>46076.41547559028</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.50366746528</v>
+        <v>46114.33700079861</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.503793055555</v>
+        <v>46114.337126388884</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2870,13 +2870,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.79484642361</v>
+        <v>46073.62817975694</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.54785292824</v>
+        <v>46097.38118626157</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.778066307874</v>
+        <v>46100.6113996412</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2935,13 +2935,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.79484674768</v>
+        <v>46073.62818008102</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.71470650463</v>
+        <v>46129.54803983796</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.71472099537</v>
+        <v>46129.548054328705</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2988,13 +2988,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.54735603009</v>
+        <v>46097.380689363425</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.20558688657</v>
+        <v>46134.03892021991</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3053,13 +3053,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.794847268524</v>
+        <v>46073.62818060185</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.54729899306</v>
+        <v>46097.380632326385</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.813124513894</v>
+        <v>46101.64645784722</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3118,13 +3118,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.79484752315</v>
+        <v>46073.62818085648</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54733972222</v>
+        <v>46097.38067305555</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.54734099537</v>
+        <v>46097.3806743287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3183,13 +3183,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.7948477662</v>
+        <v>46073.62818109954</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.58757038195</v>
+        <v>46104.420903715276</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.20558681713</v>
+        <v>46134.03892015046</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3248,13 +3248,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.79484803241</v>
+        <v>46073.62818136574</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.58750148148</v>
+        <v>46104.42083481481</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.58750311343</v>
+        <v>46104.42083644676</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3309,13 +3309,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.79484828704</v>
+        <v>46073.62818162037</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.58755459491</v>
+        <v>46104.42088792824</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.58755618056</v>
+        <v>46104.42088951389</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3370,13 +3370,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.79484853009</v>
+        <v>46073.62818186343</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.583659386575</v>
+        <v>46104.41699271991</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.58367331019</v>
+        <v>46104.41700664352</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3435,13 +3435,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.79484878472</v>
+        <v>46073.62818211806</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.58357604167</v>
+        <v>46104.416909374995</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.583577881946</v>
+        <v>46104.416911215274</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3496,13 +3496,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.58364541667</v>
+        <v>46104.41697875</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.58364686342</v>
+        <v>46104.41698019676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3557,13 +3557,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.79484739584</v>
+        <v>46073.62818072917</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.584286990736</v>
+        <v>46104.41762032408</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.2060525</v>
+        <v>46165.039385833334</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3622,13 +3622,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.79484769676</v>
+        <v>46073.62818103009</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.58417509259</v>
+        <v>46104.417508425926</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.58417674768</v>
+        <v>46104.41751008102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3683,13 +3683,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.79484798611</v>
+        <v>46073.628181319444</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.58422200232</v>
+        <v>46104.41755533565</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.58422371528</v>
+        <v>46104.41755704861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3744,13 +3744,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.79484826389</v>
+        <v>46073.62818159722</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.58427152778</v>
+        <v>46104.41760486111</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.58427320602</v>
+        <v>46104.417606539355</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3805,13 +3805,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.794848564816</v>
+        <v>46073.62818189815</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.801113587964</v>
+        <v>46114.63444692129</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.801124247686</v>
+        <v>46114.63445758102</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3870,13 +3870,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.79484883102</v>
+        <v>46073.62818216435</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.591430416665</v>
+        <v>46112.42476375</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.59143256945</v>
+        <v>46112.424765902775</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3931,13 +3931,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.79484913194</v>
+        <v>46073.628182465276</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.80109980324</v>
+        <v>46114.63443313657</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.80110109954</v>
+        <v>46114.63443443287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3992,13 +3992,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.58266418982</v>
+        <v>46076.415997523145</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.49794984954</v>
+        <v>46112.331283182866</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.19208922454</v>
+        <v>46134.02542255787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4057,13 +4057,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.58280495371</v>
+        <v>46076.41613828704</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.7145863426</v>
+        <v>46129.547919675926</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.714587407405</v>
+        <v>46129.54792074074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4118,13 +4118,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.58302251158</v>
+        <v>46076.41635584491</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.7146324537</v>
+        <v>46129.54796578704</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.714633553245</v>
+        <v>46129.547966886574</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4179,13 +4179,13 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.794849467595</v>
+        <v>46073.62818280092</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.551042673615</v>
+        <v>46198.38437600694</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.55105587963</v>
+        <v>46198.384389212966</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.79484973379</v>
+        <v>46073.62818306713</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.79848856482</v>
+        <v>46114.63182189815</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.70688251157</v>
+        <v>46197.54021584491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.79484638889</v>
+        <v>46073.62817972222</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.79872664352</v>
+        <v>46114.63205997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.70691572917</v>
+        <v>46197.5402490625</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.80996193287</v>
+        <v>46087.6432952662</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.798792835645</v>
+        <v>46114.63212616898</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.798815428236</v>
+        <v>46114.63214876158</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4425,13 +4425,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.810021701385</v>
+        <v>46087.64335503472</v>
       </c>
       <c r="C49" s="8">
-        <v>46198.55102407407</v>
+        <v>46198.38435740741</v>
       </c>
       <c r="D49" s="8">
-        <v>46198.551042928244</v>
+        <v>46198.38437626157</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4488,13 +4488,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.79484671296</v>
+        <v>46073.6281800463</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.673340787034</v>
+        <v>46121.50667412037</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.67335355324</v>
+        <v>46121.50668688657</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4541,13 +4541,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.79484696759</v>
+        <v>46073.628180300926</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.799450266204</v>
+        <v>46120.63278359953</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.79946753472</v>
+        <v>46120.63280086806</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4606,13 +4606,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.794847233796</v>
+        <v>46073.62818056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.67332476852</v>
+        <v>46121.50665810185</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.67355936342</v>
+        <v>46121.50689269676</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4671,13 +4671,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.794847488425</v>
+        <v>46073.62818082176</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76737151621</v>
+        <v>46132.60070484954</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.76738453704</v>
+        <v>46132.60071787037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4724,13 +4724,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.79484775463</v>
+        <v>46073.62818108796</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.79905210648</v>
+        <v>46120.632385439814</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.92421190972</v>
+        <v>46132.757545243054</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4789,13 +4789,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.79484800926</v>
+        <v>46073.62818134259</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.561391932875</v>
+        <v>46132.394725266204</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.561408657406</v>
+        <v>46132.39474199074</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4854,13 +4854,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76735306713</v>
+        <v>46132.60068640046</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.76737177084</v>
+        <v>46132.60070510417</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4919,13 +4919,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.71626407407</v>
+        <v>46129.54959740741</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.71634960648</v>
+        <v>46129.54968293982</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4968,13 +4968,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.61763545139</v>
+        <v>46122.450968784724</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.61765378472</v>
+        <v>46122.450987118056</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5033,13 +5033,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.79484665509</v>
+        <v>46073.62817998843</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.659079606485</v>
+        <v>46122.49241293981</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.17597939815</v>
+        <v>46147.00931273148</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5098,13 +5098,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.794847129626</v>
+        <v>46073.62818046296</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.669174490744</v>
+        <v>46127.50250782407</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.17597951389</v>
+        <v>46147.00931284722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5163,13 +5163,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.794847418976</v>
+        <v>46073.62818075232</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.66922835648</v>
+        <v>46127.50256168982</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.174760891205</v>
+        <v>46169.00809422454</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5228,13 +5228,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.583608553236</v>
+        <v>46076.41694188658</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.7162494213</v>
+        <v>46129.549582754626</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.200935636574</v>
+        <v>46136.0342689699</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5293,13 +5293,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.79484768519</v>
+        <v>46073.62818101852</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.50932107639</v>
+        <v>46197.342654409724</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.50933475695</v>
+        <v>46197.34266809028</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5346,13 +5346,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.68823886574</v>
+        <v>46195.521572199075</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.688256319445</v>
+        <v>46195.52158965278</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5411,13 +5411,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50917609954</v>
+        <v>46197.34250943287</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50919467593</v>
+        <v>46197.34252800926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5476,13 +5476,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50918461806</v>
+        <v>46197.34251795139</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50920605324</v>
+        <v>46197.34253938658</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5541,13 +5541,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.79484884259</v>
+        <v>46073.628182175926</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.50919322917</v>
+        <v>46197.3425265625</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.509207361116</v>
+        <v>46197.342540694444</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5606,13 +5606,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.6229305787</v>
+        <v>46076.45626391204</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.50920206019</v>
+        <v>46197.342535393516</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.50921739583</v>
+        <v>46197.34255072917</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5671,13 +5671,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.79484912037</v>
+        <v>46073.6281824537</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.5092531713</v>
+        <v>46197.34258650463</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.50926989583</v>
+        <v>46197.34260322917</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5734,13 +5734,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.794849432874</v>
+        <v>46073.6281827662</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.50929818287</v>
+        <v>46197.34263151621</v>
       </c>
       <c r="D70" s="5">
-        <v>46198.55104168982</v>
+        <v>46198.384375023146</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5797,11 +5797,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.794846979166</v>
+        <v>46073.6281803125</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.90012883102</v>
+        <v>46197.73346216435</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5844,11 +5844,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.794847384255</v>
+        <v>46073.62818071759</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.50931729167</v>
+        <v>46197.342650624996</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5905,11 +5905,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.79484767361</v>
+        <v>46073.62818100695</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.16820392361</v>
+        <v>46179.00153725695</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5968,13 +5968,13 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C74" s="5">
-        <v>46197.90011859954</v>
+        <v>46197.73345193287</v>
       </c>
       <c r="D74" s="5">
-        <v>46197.90013689815</v>
+        <v>46197.733470231484</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6031,11 +6031,11 @@
         <v>281</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.79484825231</v>
+        <v>46073.62818158565</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46197.90013631944</v>
+        <v>46197.733469652776</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>282</v>
@@ -6092,11 +6092,11 @@
         <v>284</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.66953237269</v>
+        <v>46090.50286570602</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>285</v>
@@ -6139,11 +6139,11 @@
         <v>287</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.79484886574</v>
+        <v>46073.62818219907</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>288</v>
@@ -6202,11 +6202,11 @@
         <v>292</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.79484915509</v>
+        <v>46073.62818248842</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>293</v>
@@ -6265,11 +6265,11 @@
         <v>294</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.64638520833</v>
+        <v>46090.47971854167</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.66956530092</v>
+        <v>46090.50289863426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>295</v>
@@ -6312,11 +6312,11 @@
         <v>297</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.646490810184</v>
+        <v>46090.47982414352</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.18765634259</v>
+        <v>46191.020989675926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>298</v>
@@ -6375,11 +6375,11 @@
         <v>300</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.64689480324</v>
+        <v>46090.48022813657</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46192.17605807871</v>
+        <v>46192.00939141204</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1630,13 +1630,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.62817967593</v>
+        <v>46073.79484634259</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55022653935</v>
+        <v>46092.716893206016</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.547676111106</v>
+        <v>46129.71434277778</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1679,13 +1679,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.62818002315</v>
+        <v>46073.794846689816</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.550201342594</v>
+        <v>46092.71686800926</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71108753472</v>
+        <v>46133.877754201385</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1744,13 +1744,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.62818039352</v>
+        <v>46073.794847060184</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55020189815</v>
+        <v>46092.716868564814</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.47894534722</v>
+        <v>46134.64561201389</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1809,13 +1809,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.628180694446</v>
+        <v>46073.79484736111</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55020238426</v>
+        <v>46092.71686905093</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.478941203706</v>
+        <v>46134.64560787037</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1874,13 +1874,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.628180960644</v>
+        <v>46073.794847627316</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.5502027662</v>
+        <v>46092.71686943287</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.478936851854</v>
+        <v>46134.64560351852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1939,13 +1939,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.628181238426</v>
+        <v>46073.7948479051</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55020334491</v>
+        <v>46092.71687001157</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.478931087964</v>
+        <v>46134.64559775463</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2004,13 +2004,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.628182002314</v>
+        <v>46073.794848668986</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.434622615736</v>
+        <v>46129.60128928241</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.547719375</v>
+        <v>46129.71438604167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2053,13 +2053,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.628182291664</v>
+        <v>46073.794848958336</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.382770868055</v>
+        <v>46097.54943753472</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38278583333</v>
+        <v>46097.549452499996</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2118,13 +2118,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.628182569446</v>
+        <v>46073.79484923611</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.43460976852</v>
+        <v>46129.60127643518</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.00499202547</v>
+        <v>46154.171658692125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2183,13 +2183,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.62818284723</v>
+        <v>46073.794849513884</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.380507800925</v>
+        <v>46097.54717446759</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.547774074075</v>
+        <v>46129.71444074074</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2232,13 +2232,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.628180370375</v>
+        <v>46073.79484703703</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.380070625004</v>
+        <v>46097.54673729167</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.38826939814</v>
+        <v>46104.554936064815</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2297,13 +2297,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.62818092592</v>
+        <v>46073.794847592595</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.38044920139</v>
+        <v>46097.54711586806</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.388864293986</v>
+        <v>46104.55553096065</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2362,13 +2362,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.628181168984</v>
+        <v>46073.79484783565</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38026064815</v>
+        <v>46097.54692731482</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.4023097801</v>
+        <v>46104.56897644676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2427,13 +2427,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.62818142361</v>
+        <v>46073.79484809028</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.38048609954</v>
+        <v>46097.5471527662</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.612236898145</v>
+        <v>46100.77890356482</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2492,13 +2492,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.62818166667</v>
+        <v>46073.79484833333</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.33702034722</v>
+        <v>46114.50368701389</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.33703412037</v>
+        <v>46114.50370078704</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2545,13 +2545,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.64645108796</v>
+        <v>46101.81311775463</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.40283936342</v>
+        <v>46104.56950603009</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2610,13 +2610,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3809314699</v>
+        <v>46097.547598136574</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.40305519676</v>
+        <v>46104.56972186343</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2675,13 +2675,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.62818238426</v>
+        <v>46073.79484905093</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38286118055</v>
+        <v>46097.54952784722</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.40372770833</v>
+        <v>46104.570394375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2740,13 +2740,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.62818262732</v>
+        <v>46073.79484929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.647509710645</v>
+        <v>46101.81417637732</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.64752646991</v>
+        <v>46101.814193136575</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2805,13 +2805,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.41547559028</v>
+        <v>46076.58214225694</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.33700079861</v>
+        <v>46114.50366746528</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.337126388884</v>
+        <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2870,13 +2870,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.62817975694</v>
+        <v>46073.79484642361</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38118626157</v>
+        <v>46097.54785292824</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.6113996412</v>
+        <v>46100.778066307874</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2935,13 +2935,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.62818008102</v>
+        <v>46073.79484674768</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.54803983796</v>
+        <v>46129.71470650463</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.548054328705</v>
+        <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2988,13 +2988,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.380689363425</v>
+        <v>46097.54735603009</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.03892021991</v>
+        <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3053,13 +3053,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.62818060185</v>
+        <v>46073.794847268524</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.380632326385</v>
+        <v>46097.54729899306</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.64645784722</v>
+        <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3118,13 +3118,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.62818085648</v>
+        <v>46073.79484752315</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38067305555</v>
+        <v>46097.54733972222</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.3806743287</v>
+        <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3183,13 +3183,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.62818109954</v>
+        <v>46073.7948477662</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.420903715276</v>
+        <v>46104.58757038195</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.03892015046</v>
+        <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3248,13 +3248,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.62818136574</v>
+        <v>46073.79484803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.42083481481</v>
+        <v>46104.58750148148</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.42083644676</v>
+        <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3309,13 +3309,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.62818162037</v>
+        <v>46073.79484828704</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.42088792824</v>
+        <v>46104.58755459491</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42088951389</v>
+        <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3370,13 +3370,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.62818186343</v>
+        <v>46073.79484853009</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.41699271991</v>
+        <v>46104.583659386575</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.41700664352</v>
+        <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3435,13 +3435,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.62818211806</v>
+        <v>46073.79484878472</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.416909374995</v>
+        <v>46104.58357604167</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.416911215274</v>
+        <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3496,13 +3496,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.41697875</v>
+        <v>46104.58364541667</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.41698019676</v>
+        <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3557,13 +3557,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.62818072917</v>
+        <v>46073.79484739584</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.41762032408</v>
+        <v>46104.584286990736</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.039385833334</v>
+        <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3622,13 +3622,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.62818103009</v>
+        <v>46073.79484769676</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.417508425926</v>
+        <v>46104.58417509259</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.41751008102</v>
+        <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3683,13 +3683,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.628181319444</v>
+        <v>46073.79484798611</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.41755533565</v>
+        <v>46104.58422200232</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.41755704861</v>
+        <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3744,13 +3744,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.62818159722</v>
+        <v>46073.79484826389</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.41760486111</v>
+        <v>46104.58427152778</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.417606539355</v>
+        <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3805,13 +3805,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.62818189815</v>
+        <v>46073.794848564816</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.63444692129</v>
+        <v>46114.801113587964</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.63445758102</v>
+        <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3870,13 +3870,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.62818216435</v>
+        <v>46073.79484883102</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.42476375</v>
+        <v>46112.591430416665</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.424765902775</v>
+        <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3931,13 +3931,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.628182465276</v>
+        <v>46073.79484913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.63443313657</v>
+        <v>46114.80109980324</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.63443443287</v>
+        <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3992,13 +3992,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.415997523145</v>
+        <v>46076.58266418982</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.331283182866</v>
+        <v>46112.49794984954</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.02542255787</v>
+        <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4057,13 +4057,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.41613828704</v>
+        <v>46076.58280495371</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.547919675926</v>
+        <v>46129.7145863426</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.54792074074</v>
+        <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4118,13 +4118,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.41635584491</v>
+        <v>46076.58302251158</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.54796578704</v>
+        <v>46129.7146324537</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.547966886574</v>
+        <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4179,13 +4179,13 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.62818280092</v>
+        <v>46073.794849467595</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.38437600694</v>
+        <v>46198.551042673615</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.384389212966</v>
+        <v>46198.55105587963</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.62818306713</v>
+        <v>46073.79484973379</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.63182189815</v>
+        <v>46114.79848856482</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.54021584491</v>
+        <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.62817972222</v>
+        <v>46073.79484638889</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.63205997685</v>
+        <v>46114.79872664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.5402490625</v>
+        <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.6432952662</v>
+        <v>46087.80996193287</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.63212616898</v>
+        <v>46114.798792835645</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.63214876158</v>
+        <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4425,13 +4425,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.64335503472</v>
+        <v>46087.810021701385</v>
       </c>
       <c r="C49" s="8">
-        <v>46198.38435740741</v>
+        <v>46198.55102407407</v>
       </c>
       <c r="D49" s="8">
-        <v>46198.38437626157</v>
+        <v>46198.551042928244</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4488,13 +4488,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.6281800463</v>
+        <v>46073.79484671296</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.50667412037</v>
+        <v>46121.673340787034</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.50668688657</v>
+        <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4541,13 +4541,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.628180300926</v>
+        <v>46073.79484696759</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.63278359953</v>
+        <v>46120.799450266204</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.63280086806</v>
+        <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4606,13 +4606,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.62818056713</v>
+        <v>46073.794847233796</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.50665810185</v>
+        <v>46121.67332476852</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.50689269676</v>
+        <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4671,13 +4671,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.62818082176</v>
+        <v>46073.794847488425</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.60070484954</v>
+        <v>46132.76737151621</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.60071787037</v>
+        <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4724,13 +4724,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.62818108796</v>
+        <v>46073.79484775463</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.632385439814</v>
+        <v>46120.79905210648</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.757545243054</v>
+        <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4789,13 +4789,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.62818134259</v>
+        <v>46073.79484800926</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.394725266204</v>
+        <v>46132.561391932875</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.39474199074</v>
+        <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4854,13 +4854,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.60068640046</v>
+        <v>46132.76735306713</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.60070510417</v>
+        <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4919,13 +4919,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.54959740741</v>
+        <v>46129.71626407407</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.54968293982</v>
+        <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4968,13 +4968,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.450968784724</v>
+        <v>46122.61763545139</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.450987118056</v>
+        <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5033,13 +5033,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.62817998843</v>
+        <v>46073.79484665509</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.49241293981</v>
+        <v>46122.659079606485</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.00931273148</v>
+        <v>46147.17597939815</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5098,13 +5098,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.62818046296</v>
+        <v>46073.794847129626</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.50250782407</v>
+        <v>46127.669174490744</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.00931284722</v>
+        <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5163,13 +5163,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.62818075232</v>
+        <v>46073.794847418976</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.50256168982</v>
+        <v>46127.66922835648</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.00809422454</v>
+        <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5228,13 +5228,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.41694188658</v>
+        <v>46076.583608553236</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.549582754626</v>
+        <v>46129.7162494213</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.0342689699</v>
+        <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5293,13 +5293,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.62818101852</v>
+        <v>46073.79484768519</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.342654409724</v>
+        <v>46197.50932107639</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.34266809028</v>
+        <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5346,13 +5346,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.521572199075</v>
+        <v>46195.68823886574</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.52158965278</v>
+        <v>46195.688256319445</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5411,13 +5411,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.34250943287</v>
+        <v>46197.50917609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.34252800926</v>
+        <v>46197.50919467593</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5476,13 +5476,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.34251795139</v>
+        <v>46197.50918461806</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.34253938658</v>
+        <v>46197.50920605324</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5541,13 +5541,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.628182175926</v>
+        <v>46073.79484884259</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.3425265625</v>
+        <v>46197.50919322917</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.342540694444</v>
+        <v>46197.509207361116</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5606,13 +5606,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.45626391204</v>
+        <v>46076.6229305787</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.342535393516</v>
+        <v>46197.50920206019</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.34255072917</v>
+        <v>46197.50921739583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5671,13 +5671,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.6281824537</v>
+        <v>46073.79484912037</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.34258650463</v>
+        <v>46197.5092531713</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.34260322917</v>
+        <v>46197.50926989583</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5734,13 +5734,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.6281827662</v>
+        <v>46073.794849432874</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.34263151621</v>
+        <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46198.384375023146</v>
+        <v>46198.55104168982</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5797,11 +5797,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.6281803125</v>
+        <v>46073.794846979166</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.73346216435</v>
+        <v>46197.90012883102</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5844,11 +5844,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.62818071759</v>
+        <v>46073.794847384255</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.342650624996</v>
+        <v>46197.50931729167</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5905,11 +5905,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.62818100695</v>
+        <v>46073.79484767361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.00153725695</v>
+        <v>46179.16820392361</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5968,13 +5968,13 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C74" s="5">
-        <v>46197.73345193287</v>
+        <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46197.733470231484</v>
+        <v>46197.90013689815</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6031,11 +6031,11 @@
         <v>281</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.62818158565</v>
+        <v>46073.79484825231</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46197.733469652776</v>
+        <v>46197.90013631944</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>282</v>
@@ -6092,11 +6092,11 @@
         <v>284</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.50286570602</v>
+        <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>285</v>
@@ -6139,11 +6139,11 @@
         <v>287</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.62818219907</v>
+        <v>46073.79484886574</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>288</v>
@@ -6202,11 +6202,11 @@
         <v>292</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.62818248842</v>
+        <v>46073.79484915509</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>293</v>
@@ -6265,11 +6265,11 @@
         <v>294</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.47971854167</v>
+        <v>46090.64638520833</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.50289863426</v>
+        <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>295</v>
@@ -6312,11 +6312,11 @@
         <v>297</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.47982414352</v>
+        <v>46090.646490810184</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.020989675926</v>
+        <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>298</v>
@@ -6375,11 +6375,11 @@
         <v>300</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.48022813657</v>
+        <v>46090.64689480324</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46192.00939141204</v>
+        <v>46192.17605807871</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5974,7 +5974,7 @@
         <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46197.90013689815</v>
+        <v>46198.89910809028</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46192.17605807871</v>
+        <v>46199.25036193287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46199.25036193287</v>
+        <v>46200.17552224537</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>
@@ -6429,8 +6429,8 @@
       <c r="T81" s="9">
         <v>0</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>81</v>
+      <c r="U81" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -909,10 +909,10 @@
     <t>Coordinacion Entrega con Cliente</t>
   </si>
   <si>
-    <t>Francisca Alejandra Ramos Aravales</t>
-  </si>
-  <si>
-    <t>francisca@zitron.com</t>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.50931729167</v>
+        <v>46204.69436715278</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1630,13 +1630,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.79484634259</v>
+        <v>46073.62817967593</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.716893206016</v>
+        <v>46092.55022653935</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.71434277778</v>
+        <v>46129.547676111106</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1679,13 +1679,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.794846689816</v>
+        <v>46073.62818002315</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71686800926</v>
+        <v>46092.550201342594</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877754201385</v>
+        <v>46133.71108753472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1744,13 +1744,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.794847060184</v>
+        <v>46073.62818039352</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.716868564814</v>
+        <v>46092.55020189815</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.64561201389</v>
+        <v>46134.47894534722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1809,13 +1809,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.79484736111</v>
+        <v>46073.628180694446</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71686905093</v>
+        <v>46092.55020238426</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.64560787037</v>
+        <v>46134.478941203706</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1874,13 +1874,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.794847627316</v>
+        <v>46073.628180960644</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71686943287</v>
+        <v>46092.5502027662</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.64560351852</v>
+        <v>46134.478936851854</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1939,13 +1939,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.7948479051</v>
+        <v>46073.628181238426</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71687001157</v>
+        <v>46092.55020334491</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.64559775463</v>
+        <v>46134.478931087964</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2004,13 +2004,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.794848668986</v>
+        <v>46073.628182002314</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.60128928241</v>
+        <v>46129.434622615736</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.71438604167</v>
+        <v>46129.547719375</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2053,13 +2053,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.794848958336</v>
+        <v>46073.628182291664</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54943753472</v>
+        <v>46097.382770868055</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.549452499996</v>
+        <v>46097.38278583333</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2118,13 +2118,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.79484923611</v>
+        <v>46073.628182569446</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.60127643518</v>
+        <v>46129.43460976852</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.171658692125</v>
+        <v>46154.00499202547</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2183,13 +2183,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.794849513884</v>
+        <v>46073.62818284723</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.54717446759</v>
+        <v>46097.380507800925</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.71444074074</v>
+        <v>46129.547774074075</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2232,13 +2232,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.79484703703</v>
+        <v>46073.628180370375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54673729167</v>
+        <v>46097.380070625004</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.554936064815</v>
+        <v>46104.38826939814</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2297,13 +2297,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.794847592595</v>
+        <v>46073.62818092592</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54711586806</v>
+        <v>46097.38044920139</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.55553096065</v>
+        <v>46104.388864293986</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2362,13 +2362,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.79484783565</v>
+        <v>46073.628181168984</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.54692731482</v>
+        <v>46097.38026064815</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.56897644676</v>
+        <v>46104.4023097801</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2427,13 +2427,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.79484809028</v>
+        <v>46073.62818142361</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.5471527662</v>
+        <v>46097.38048609954</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.77890356482</v>
+        <v>46100.612236898145</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2492,13 +2492,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.79484833333</v>
+        <v>46073.62818166667</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.50368701389</v>
+        <v>46114.33702034722</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.50370078704</v>
+        <v>46114.33703412037</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2545,13 +2545,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.81311775463</v>
+        <v>46101.64645108796</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.56950603009</v>
+        <v>46104.40283936342</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2610,13 +2610,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.547598136574</v>
+        <v>46097.3809314699</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.56972186343</v>
+        <v>46104.40305519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2675,13 +2675,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.79484905093</v>
+        <v>46073.62818238426</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54952784722</v>
+        <v>46097.38286118055</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.570394375</v>
+        <v>46104.40372770833</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2740,13 +2740,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.79484929398</v>
+        <v>46073.62818262732</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.81417637732</v>
+        <v>46101.647509710645</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.814193136575</v>
+        <v>46101.64752646991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2805,13 +2805,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.58214225694</v>
+        <v>46076.41547559028</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.50366746528</v>
+        <v>46114.33700079861</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.503793055555</v>
+        <v>46114.337126388884</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2870,13 +2870,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.79484642361</v>
+        <v>46073.62817975694</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.54785292824</v>
+        <v>46097.38118626157</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.778066307874</v>
+        <v>46100.6113996412</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2935,13 +2935,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.79484674768</v>
+        <v>46073.62818008102</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.71470650463</v>
+        <v>46129.54803983796</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.71472099537</v>
+        <v>46129.548054328705</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2988,13 +2988,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.54735603009</v>
+        <v>46097.380689363425</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.20558688657</v>
+        <v>46134.03892021991</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3053,13 +3053,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.794847268524</v>
+        <v>46073.62818060185</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.54729899306</v>
+        <v>46097.380632326385</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.813124513894</v>
+        <v>46101.64645784722</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3118,13 +3118,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.79484752315</v>
+        <v>46073.62818085648</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54733972222</v>
+        <v>46097.38067305555</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.54734099537</v>
+        <v>46097.3806743287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3183,13 +3183,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.7948477662</v>
+        <v>46073.62818109954</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.58757038195</v>
+        <v>46104.420903715276</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.20558681713</v>
+        <v>46134.03892015046</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3248,13 +3248,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.79484803241</v>
+        <v>46073.62818136574</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.58750148148</v>
+        <v>46104.42083481481</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.58750311343</v>
+        <v>46104.42083644676</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3309,13 +3309,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.79484828704</v>
+        <v>46073.62818162037</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.58755459491</v>
+        <v>46104.42088792824</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.58755618056</v>
+        <v>46104.42088951389</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3370,13 +3370,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.79484853009</v>
+        <v>46073.62818186343</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.583659386575</v>
+        <v>46104.41699271991</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.58367331019</v>
+        <v>46104.41700664352</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3435,13 +3435,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.79484878472</v>
+        <v>46073.62818211806</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.58357604167</v>
+        <v>46104.416909374995</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.583577881946</v>
+        <v>46104.416911215274</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3496,13 +3496,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.58364541667</v>
+        <v>46104.41697875</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.58364686342</v>
+        <v>46104.41698019676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3557,13 +3557,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.79484739584</v>
+        <v>46073.62818072917</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.584286990736</v>
+        <v>46104.41762032408</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.2060525</v>
+        <v>46165.039385833334</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3622,13 +3622,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.79484769676</v>
+        <v>46073.62818103009</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.58417509259</v>
+        <v>46104.417508425926</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.58417674768</v>
+        <v>46104.41751008102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3683,13 +3683,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.79484798611</v>
+        <v>46073.628181319444</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.58422200232</v>
+        <v>46104.41755533565</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.58422371528</v>
+        <v>46104.41755704861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3744,13 +3744,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.79484826389</v>
+        <v>46073.62818159722</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.58427152778</v>
+        <v>46104.41760486111</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.58427320602</v>
+        <v>46104.417606539355</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3805,13 +3805,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.794848564816</v>
+        <v>46073.62818189815</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.801113587964</v>
+        <v>46114.63444692129</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.801124247686</v>
+        <v>46114.63445758102</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3870,13 +3870,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.79484883102</v>
+        <v>46073.62818216435</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.591430416665</v>
+        <v>46112.42476375</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.59143256945</v>
+        <v>46112.424765902775</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3931,13 +3931,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.79484913194</v>
+        <v>46073.628182465276</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.80109980324</v>
+        <v>46114.63443313657</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.80110109954</v>
+        <v>46114.63443443287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3992,13 +3992,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.58266418982</v>
+        <v>46076.415997523145</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.49794984954</v>
+        <v>46112.331283182866</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.19208922454</v>
+        <v>46134.02542255787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4057,13 +4057,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.58280495371</v>
+        <v>46076.41613828704</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.7145863426</v>
+        <v>46129.547919675926</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.714587407405</v>
+        <v>46129.54792074074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4118,13 +4118,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.58302251158</v>
+        <v>46076.41635584491</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.7146324537</v>
+        <v>46129.54796578704</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.714633553245</v>
+        <v>46129.547966886574</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4179,13 +4179,13 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.794849467595</v>
+        <v>46073.62818280092</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.551042673615</v>
+        <v>46198.38437600694</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.55105587963</v>
+        <v>46198.384389212966</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.79484973379</v>
+        <v>46073.62818306713</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.79848856482</v>
+        <v>46114.63182189815</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.70688251157</v>
+        <v>46197.54021584491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.79484638889</v>
+        <v>46073.62817972222</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.79872664352</v>
+        <v>46114.63205997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.70691572917</v>
+        <v>46197.5402490625</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.80996193287</v>
+        <v>46087.6432952662</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.798792835645</v>
+        <v>46114.63212616898</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.798815428236</v>
+        <v>46114.63214876158</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4425,13 +4425,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.810021701385</v>
+        <v>46087.64335503472</v>
       </c>
       <c r="C49" s="8">
-        <v>46198.55102407407</v>
+        <v>46198.38435740741</v>
       </c>
       <c r="D49" s="8">
-        <v>46198.551042928244</v>
+        <v>46198.38437626157</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4488,13 +4488,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.79484671296</v>
+        <v>46073.6281800463</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.673340787034</v>
+        <v>46121.50667412037</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.67335355324</v>
+        <v>46121.50668688657</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4541,13 +4541,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.79484696759</v>
+        <v>46073.628180300926</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.799450266204</v>
+        <v>46120.63278359953</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.79946753472</v>
+        <v>46120.63280086806</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4606,13 +4606,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.794847233796</v>
+        <v>46073.62818056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.67332476852</v>
+        <v>46121.50665810185</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.67355936342</v>
+        <v>46121.50689269676</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4671,13 +4671,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.794847488425</v>
+        <v>46073.62818082176</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76737151621</v>
+        <v>46132.60070484954</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.76738453704</v>
+        <v>46132.60071787037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4724,13 +4724,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.79484775463</v>
+        <v>46073.62818108796</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.79905210648</v>
+        <v>46120.632385439814</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.92421190972</v>
+        <v>46132.757545243054</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4789,13 +4789,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.79484800926</v>
+        <v>46073.62818134259</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.561391932875</v>
+        <v>46132.394725266204</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.561408657406</v>
+        <v>46132.39474199074</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4854,13 +4854,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76735306713</v>
+        <v>46132.60068640046</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.76737177084</v>
+        <v>46132.60070510417</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4919,13 +4919,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.71626407407</v>
+        <v>46129.54959740741</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.71634960648</v>
+        <v>46129.54968293982</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4968,13 +4968,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.61763545139</v>
+        <v>46122.450968784724</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.61765378472</v>
+        <v>46122.450987118056</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5033,13 +5033,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.79484665509</v>
+        <v>46073.62817998843</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.659079606485</v>
+        <v>46122.49241293981</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.17597939815</v>
+        <v>46147.00931273148</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5098,13 +5098,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.794847129626</v>
+        <v>46073.62818046296</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.669174490744</v>
+        <v>46127.50250782407</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.17597951389</v>
+        <v>46147.00931284722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5163,13 +5163,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.794847418976</v>
+        <v>46073.62818075232</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.66922835648</v>
+        <v>46127.50256168982</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.174760891205</v>
+        <v>46169.00809422454</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5228,13 +5228,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.583608553236</v>
+        <v>46076.41694188658</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.7162494213</v>
+        <v>46129.549582754626</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.200935636574</v>
+        <v>46136.0342689699</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5293,13 +5293,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.79484768519</v>
+        <v>46073.62818101852</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.50932107639</v>
+        <v>46197.342654409724</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.50933475695</v>
+        <v>46197.34266809028</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5346,13 +5346,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.68823886574</v>
+        <v>46195.521572199075</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.688256319445</v>
+        <v>46195.52158965278</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5411,13 +5411,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50917609954</v>
+        <v>46197.34250943287</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50919467593</v>
+        <v>46197.34252800926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5476,13 +5476,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50918461806</v>
+        <v>46197.34251795139</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50920605324</v>
+        <v>46197.34253938658</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5541,13 +5541,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.79484884259</v>
+        <v>46073.628182175926</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.50919322917</v>
+        <v>46197.3425265625</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.509207361116</v>
+        <v>46197.342540694444</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5606,13 +5606,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.6229305787</v>
+        <v>46076.45626391204</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.50920206019</v>
+        <v>46197.342535393516</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.50921739583</v>
+        <v>46197.34255072917</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5671,13 +5671,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.79484912037</v>
+        <v>46073.6281824537</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.5092531713</v>
+        <v>46197.34258650463</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.50926989583</v>
+        <v>46197.34260322917</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5734,13 +5734,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.794849432874</v>
+        <v>46073.6281827662</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.50929818287</v>
+        <v>46197.34263151621</v>
       </c>
       <c r="D70" s="5">
-        <v>46198.55104168982</v>
+        <v>46198.384375023146</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5797,11 +5797,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.794846979166</v>
+        <v>46073.6281803125</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.90012883102</v>
+        <v>46197.73346216435</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5844,11 +5844,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.794847384255</v>
+        <v>46073.62818071759</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.69436715278</v>
+        <v>46204.52770048611</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5905,11 +5905,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.79484767361</v>
+        <v>46073.62818100695</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.16820392361</v>
+        <v>46179.00153725695</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5968,13 +5968,13 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C74" s="5">
-        <v>46197.90011859954</v>
+        <v>46197.73345193287</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.89910809028</v>
+        <v>46198.732441423606</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6031,11 +6031,11 @@
         <v>281</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.79484825231</v>
+        <v>46073.62818158565</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46197.90013631944</v>
+        <v>46197.733469652776</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>282</v>
@@ -6092,11 +6092,11 @@
         <v>284</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.66953237269</v>
+        <v>46090.50286570602</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>285</v>
@@ -6139,11 +6139,11 @@
         <v>287</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.79484886574</v>
+        <v>46073.62818219907</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>288</v>
@@ -6202,11 +6202,11 @@
         <v>292</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.79484915509</v>
+        <v>46073.62818248842</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>293</v>
@@ -6265,11 +6265,11 @@
         <v>294</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.64638520833</v>
+        <v>46090.47971854167</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.66956530092</v>
+        <v>46090.50289863426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>295</v>
@@ -6312,11 +6312,11 @@
         <v>297</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.646490810184</v>
+        <v>46090.47982414352</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.18765634259</v>
+        <v>46191.020989675926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>298</v>
@@ -6375,11 +6375,11 @@
         <v>300</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.64689480324</v>
+        <v>46090.48022813657</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46200.17552224537</v>
+        <v>46200.00885557871</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1630,13 +1630,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.62817967593</v>
+        <v>46073.79484634259</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55022653935</v>
+        <v>46092.716893206016</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.547676111106</v>
+        <v>46129.71434277778</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1679,13 +1679,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.62818002315</v>
+        <v>46073.794846689816</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.550201342594</v>
+        <v>46092.71686800926</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71108753472</v>
+        <v>46133.877754201385</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1744,13 +1744,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.62818039352</v>
+        <v>46073.794847060184</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55020189815</v>
+        <v>46092.716868564814</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.47894534722</v>
+        <v>46134.64561201389</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1809,13 +1809,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.628180694446</v>
+        <v>46073.79484736111</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55020238426</v>
+        <v>46092.71686905093</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.478941203706</v>
+        <v>46134.64560787037</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1874,13 +1874,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.628180960644</v>
+        <v>46073.794847627316</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.5502027662</v>
+        <v>46092.71686943287</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.478936851854</v>
+        <v>46134.64560351852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1939,13 +1939,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.628181238426</v>
+        <v>46073.7948479051</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55020334491</v>
+        <v>46092.71687001157</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.478931087964</v>
+        <v>46134.64559775463</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2004,13 +2004,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.628182002314</v>
+        <v>46073.794848668986</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.434622615736</v>
+        <v>46129.60128928241</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.547719375</v>
+        <v>46129.71438604167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2053,13 +2053,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.628182291664</v>
+        <v>46073.794848958336</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.382770868055</v>
+        <v>46097.54943753472</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38278583333</v>
+        <v>46097.549452499996</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2118,13 +2118,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.628182569446</v>
+        <v>46073.79484923611</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.43460976852</v>
+        <v>46129.60127643518</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.00499202547</v>
+        <v>46154.171658692125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2183,13 +2183,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.62818284723</v>
+        <v>46073.794849513884</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.380507800925</v>
+        <v>46097.54717446759</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.547774074075</v>
+        <v>46129.71444074074</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2232,13 +2232,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.628180370375</v>
+        <v>46073.79484703703</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.380070625004</v>
+        <v>46097.54673729167</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.38826939814</v>
+        <v>46104.554936064815</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2297,13 +2297,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.62818092592</v>
+        <v>46073.794847592595</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.38044920139</v>
+        <v>46097.54711586806</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.388864293986</v>
+        <v>46104.55553096065</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2362,13 +2362,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.628181168984</v>
+        <v>46073.79484783565</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38026064815</v>
+        <v>46097.54692731482</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.4023097801</v>
+        <v>46104.56897644676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2427,13 +2427,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.62818142361</v>
+        <v>46073.79484809028</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.38048609954</v>
+        <v>46097.5471527662</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.612236898145</v>
+        <v>46100.77890356482</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2492,13 +2492,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.62818166667</v>
+        <v>46073.79484833333</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.33702034722</v>
+        <v>46114.50368701389</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.33703412037</v>
+        <v>46114.50370078704</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2545,13 +2545,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.64645108796</v>
+        <v>46101.81311775463</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.40283936342</v>
+        <v>46104.56950603009</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2610,13 +2610,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3809314699</v>
+        <v>46097.547598136574</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.40305519676</v>
+        <v>46104.56972186343</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2675,13 +2675,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.62818238426</v>
+        <v>46073.79484905093</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38286118055</v>
+        <v>46097.54952784722</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.40372770833</v>
+        <v>46104.570394375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2740,13 +2740,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.62818262732</v>
+        <v>46073.79484929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.647509710645</v>
+        <v>46101.81417637732</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.64752646991</v>
+        <v>46101.814193136575</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2805,13 +2805,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.41547559028</v>
+        <v>46076.58214225694</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.33700079861</v>
+        <v>46114.50366746528</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.337126388884</v>
+        <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2870,13 +2870,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.62817975694</v>
+        <v>46073.79484642361</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38118626157</v>
+        <v>46097.54785292824</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.6113996412</v>
+        <v>46100.778066307874</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2935,13 +2935,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.62818008102</v>
+        <v>46073.79484674768</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.54803983796</v>
+        <v>46129.71470650463</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.548054328705</v>
+        <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2988,13 +2988,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.380689363425</v>
+        <v>46097.54735603009</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.03892021991</v>
+        <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3053,13 +3053,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.62818060185</v>
+        <v>46073.794847268524</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.380632326385</v>
+        <v>46097.54729899306</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.64645784722</v>
+        <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3118,13 +3118,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.62818085648</v>
+        <v>46073.79484752315</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38067305555</v>
+        <v>46097.54733972222</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.3806743287</v>
+        <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3183,13 +3183,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.62818109954</v>
+        <v>46073.7948477662</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.420903715276</v>
+        <v>46104.58757038195</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.03892015046</v>
+        <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3248,13 +3248,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.62818136574</v>
+        <v>46073.79484803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.42083481481</v>
+        <v>46104.58750148148</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.42083644676</v>
+        <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3309,13 +3309,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.62818162037</v>
+        <v>46073.79484828704</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.42088792824</v>
+        <v>46104.58755459491</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42088951389</v>
+        <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3370,13 +3370,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.62818186343</v>
+        <v>46073.79484853009</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.41699271991</v>
+        <v>46104.583659386575</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.41700664352</v>
+        <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3435,13 +3435,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.62818211806</v>
+        <v>46073.79484878472</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.416909374995</v>
+        <v>46104.58357604167</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.416911215274</v>
+        <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3496,13 +3496,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.41697875</v>
+        <v>46104.58364541667</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.41698019676</v>
+        <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3557,13 +3557,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.62818072917</v>
+        <v>46073.79484739584</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.41762032408</v>
+        <v>46104.584286990736</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.039385833334</v>
+        <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3622,13 +3622,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.62818103009</v>
+        <v>46073.79484769676</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.417508425926</v>
+        <v>46104.58417509259</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.41751008102</v>
+        <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3683,13 +3683,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.628181319444</v>
+        <v>46073.79484798611</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.41755533565</v>
+        <v>46104.58422200232</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.41755704861</v>
+        <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3744,13 +3744,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.62818159722</v>
+        <v>46073.79484826389</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.41760486111</v>
+        <v>46104.58427152778</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.417606539355</v>
+        <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3805,13 +3805,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.62818189815</v>
+        <v>46073.794848564816</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.63444692129</v>
+        <v>46114.801113587964</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.63445758102</v>
+        <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3870,13 +3870,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.62818216435</v>
+        <v>46073.79484883102</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.42476375</v>
+        <v>46112.591430416665</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.424765902775</v>
+        <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3931,13 +3931,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.628182465276</v>
+        <v>46073.79484913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.63443313657</v>
+        <v>46114.80109980324</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.63443443287</v>
+        <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3992,13 +3992,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.415997523145</v>
+        <v>46076.58266418982</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.331283182866</v>
+        <v>46112.49794984954</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.02542255787</v>
+        <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4057,13 +4057,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.41613828704</v>
+        <v>46076.58280495371</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.547919675926</v>
+        <v>46129.7145863426</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.54792074074</v>
+        <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4118,13 +4118,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.41635584491</v>
+        <v>46076.58302251158</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.54796578704</v>
+        <v>46129.7146324537</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.547966886574</v>
+        <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4179,13 +4179,13 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.62818280092</v>
+        <v>46073.794849467595</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.38437600694</v>
+        <v>46198.551042673615</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.384389212966</v>
+        <v>46198.55105587963</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.62818306713</v>
+        <v>46073.79484973379</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.63182189815</v>
+        <v>46114.79848856482</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.54021584491</v>
+        <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.62817972222</v>
+        <v>46073.79484638889</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.63205997685</v>
+        <v>46114.79872664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.5402490625</v>
+        <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.6432952662</v>
+        <v>46087.80996193287</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.63212616898</v>
+        <v>46114.798792835645</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.63214876158</v>
+        <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4425,13 +4425,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.64335503472</v>
+        <v>46087.810021701385</v>
       </c>
       <c r="C49" s="8">
-        <v>46198.38435740741</v>
+        <v>46198.55102407407</v>
       </c>
       <c r="D49" s="8">
-        <v>46198.38437626157</v>
+        <v>46198.551042928244</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4488,13 +4488,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.6281800463</v>
+        <v>46073.79484671296</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.50667412037</v>
+        <v>46121.673340787034</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.50668688657</v>
+        <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4541,13 +4541,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.628180300926</v>
+        <v>46073.79484696759</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.63278359953</v>
+        <v>46120.799450266204</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.63280086806</v>
+        <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4606,13 +4606,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.62818056713</v>
+        <v>46073.794847233796</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.50665810185</v>
+        <v>46121.67332476852</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.50689269676</v>
+        <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4671,13 +4671,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.62818082176</v>
+        <v>46073.794847488425</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.60070484954</v>
+        <v>46132.76737151621</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.60071787037</v>
+        <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4724,13 +4724,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.62818108796</v>
+        <v>46073.79484775463</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.632385439814</v>
+        <v>46120.79905210648</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.757545243054</v>
+        <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4789,13 +4789,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.62818134259</v>
+        <v>46073.79484800926</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.394725266204</v>
+        <v>46132.561391932875</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.39474199074</v>
+        <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4854,13 +4854,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.60068640046</v>
+        <v>46132.76735306713</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.60070510417</v>
+        <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4919,13 +4919,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.54959740741</v>
+        <v>46129.71626407407</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.54968293982</v>
+        <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4968,13 +4968,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.450968784724</v>
+        <v>46122.61763545139</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.450987118056</v>
+        <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5033,13 +5033,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.62817998843</v>
+        <v>46073.79484665509</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.49241293981</v>
+        <v>46122.659079606485</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.00931273148</v>
+        <v>46147.17597939815</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5098,13 +5098,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.62818046296</v>
+        <v>46073.794847129626</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.50250782407</v>
+        <v>46127.669174490744</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.00931284722</v>
+        <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5163,13 +5163,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.62818075232</v>
+        <v>46073.794847418976</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.50256168982</v>
+        <v>46127.66922835648</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.00809422454</v>
+        <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5228,13 +5228,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.41694188658</v>
+        <v>46076.583608553236</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.549582754626</v>
+        <v>46129.7162494213</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.0342689699</v>
+        <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5293,13 +5293,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.62818101852</v>
+        <v>46073.79484768519</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.342654409724</v>
+        <v>46197.50932107639</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.34266809028</v>
+        <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5346,13 +5346,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.521572199075</v>
+        <v>46195.68823886574</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.52158965278</v>
+        <v>46195.688256319445</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5411,13 +5411,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.34250943287</v>
+        <v>46197.50917609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.34252800926</v>
+        <v>46197.50919467593</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5476,13 +5476,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.34251795139</v>
+        <v>46197.50918461806</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.34253938658</v>
+        <v>46197.50920605324</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5541,13 +5541,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.628182175926</v>
+        <v>46073.79484884259</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.3425265625</v>
+        <v>46197.50919322917</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.342540694444</v>
+        <v>46197.509207361116</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5606,13 +5606,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.45626391204</v>
+        <v>46076.6229305787</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.342535393516</v>
+        <v>46197.50920206019</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.34255072917</v>
+        <v>46197.50921739583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5671,13 +5671,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.6281824537</v>
+        <v>46073.79484912037</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.34258650463</v>
+        <v>46197.5092531713</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.34260322917</v>
+        <v>46197.50926989583</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5734,13 +5734,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.6281827662</v>
+        <v>46073.794849432874</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.34263151621</v>
+        <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46198.384375023146</v>
+        <v>46198.55104168982</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5797,11 +5797,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.6281803125</v>
+        <v>46073.794846979166</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.73346216435</v>
+        <v>46197.90012883102</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5844,11 +5844,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.62818071759</v>
+        <v>46073.794847384255</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.52770048611</v>
+        <v>46204.69436715278</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5905,11 +5905,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.62818100695</v>
+        <v>46073.79484767361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.00153725695</v>
+        <v>46179.16820392361</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5968,13 +5968,13 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C74" s="5">
-        <v>46197.73345193287</v>
+        <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.732441423606</v>
+        <v>46205.63226972222</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6031,11 +6031,11 @@
         <v>281</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.62818158565</v>
+        <v>46073.79484825231</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46197.733469652776</v>
+        <v>46197.90013631944</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>282</v>
@@ -6092,11 +6092,11 @@
         <v>284</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.50286570602</v>
+        <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>285</v>
@@ -6139,11 +6139,11 @@
         <v>287</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.62818219907</v>
+        <v>46073.79484886574</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>288</v>
@@ -6202,11 +6202,11 @@
         <v>292</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.62818248842</v>
+        <v>46073.79484915509</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>293</v>
@@ -6265,11 +6265,11 @@
         <v>294</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.47971854167</v>
+        <v>46090.64638520833</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.50289863426</v>
+        <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>295</v>
@@ -6312,11 +6312,11 @@
         <v>297</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.47982414352</v>
+        <v>46090.646490810184</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.020989675926</v>
+        <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>298</v>
@@ -6375,11 +6375,11 @@
         <v>300</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.48022813657</v>
+        <v>46090.64689480324</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46200.00885557871</v>
+        <v>46200.17552224537</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46179.16820392361</v>
+        <v>46209.925254525464</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5957,10 +5957,10 @@
         <v>60</v>
       </c>
       <c r="T73" s="9">
-        <v>0</v>
-      </c>
-      <c r="U73" s="10" t="s">
-        <v>61</v>
+        <v>0.7</v>
+      </c>
+      <c r="U73" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1630,13 +1630,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.79484634259</v>
+        <v>46073.62817967593</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.716893206016</v>
+        <v>46092.55022653935</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.71434277778</v>
+        <v>46129.547676111106</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1679,13 +1679,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.794846689816</v>
+        <v>46073.62818002315</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71686800926</v>
+        <v>46092.550201342594</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877754201385</v>
+        <v>46133.71108753472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1744,13 +1744,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.794847060184</v>
+        <v>46073.62818039352</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.716868564814</v>
+        <v>46092.55020189815</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.64561201389</v>
+        <v>46134.47894534722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1809,13 +1809,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.79484736111</v>
+        <v>46073.628180694446</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71686905093</v>
+        <v>46092.55020238426</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.64560787037</v>
+        <v>46134.478941203706</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1874,13 +1874,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.794847627316</v>
+        <v>46073.628180960644</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71686943287</v>
+        <v>46092.5502027662</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.64560351852</v>
+        <v>46134.478936851854</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1939,13 +1939,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.7948479051</v>
+        <v>46073.628181238426</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71687001157</v>
+        <v>46092.55020334491</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.64559775463</v>
+        <v>46134.478931087964</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2004,13 +2004,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.794848668986</v>
+        <v>46073.628182002314</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.60128928241</v>
+        <v>46129.434622615736</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.71438604167</v>
+        <v>46129.547719375</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2053,13 +2053,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.794848958336</v>
+        <v>46073.628182291664</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54943753472</v>
+        <v>46097.382770868055</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.549452499996</v>
+        <v>46097.38278583333</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2118,13 +2118,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.79484923611</v>
+        <v>46073.628182569446</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.60127643518</v>
+        <v>46129.43460976852</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.171658692125</v>
+        <v>46154.00499202547</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2183,13 +2183,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.794849513884</v>
+        <v>46073.62818284723</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.54717446759</v>
+        <v>46097.380507800925</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.71444074074</v>
+        <v>46129.547774074075</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2232,13 +2232,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.79484703703</v>
+        <v>46073.628180370375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54673729167</v>
+        <v>46097.380070625004</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.554936064815</v>
+        <v>46104.38826939814</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2297,13 +2297,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.794847592595</v>
+        <v>46073.62818092592</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.54711586806</v>
+        <v>46097.38044920139</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.55553096065</v>
+        <v>46104.388864293986</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2362,13 +2362,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.79484783565</v>
+        <v>46073.628181168984</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.54692731482</v>
+        <v>46097.38026064815</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.56897644676</v>
+        <v>46104.4023097801</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2427,13 +2427,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.79484809028</v>
+        <v>46073.62818142361</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.5471527662</v>
+        <v>46097.38048609954</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.77890356482</v>
+        <v>46100.612236898145</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2492,13 +2492,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.79484833333</v>
+        <v>46073.62818166667</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.50368701389</v>
+        <v>46114.33702034722</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.50370078704</v>
+        <v>46114.33703412037</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2545,13 +2545,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.81311775463</v>
+        <v>46101.64645108796</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.56950603009</v>
+        <v>46104.40283936342</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2610,13 +2610,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.547598136574</v>
+        <v>46097.3809314699</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.56972186343</v>
+        <v>46104.40305519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2675,13 +2675,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.79484905093</v>
+        <v>46073.62818238426</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54952784722</v>
+        <v>46097.38286118055</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.570394375</v>
+        <v>46104.40372770833</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2740,13 +2740,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.79484929398</v>
+        <v>46073.62818262732</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.81417637732</v>
+        <v>46101.647509710645</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.814193136575</v>
+        <v>46101.64752646991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2805,13 +2805,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.58214225694</v>
+        <v>46076.41547559028</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.50366746528</v>
+        <v>46114.33700079861</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.503793055555</v>
+        <v>46114.337126388884</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2870,13 +2870,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.79484642361</v>
+        <v>46073.62817975694</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.54785292824</v>
+        <v>46097.38118626157</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.778066307874</v>
+        <v>46100.6113996412</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2935,13 +2935,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.79484674768</v>
+        <v>46073.62818008102</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.71470650463</v>
+        <v>46129.54803983796</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.71472099537</v>
+        <v>46129.548054328705</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2988,13 +2988,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.54735603009</v>
+        <v>46097.380689363425</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.20558688657</v>
+        <v>46134.03892021991</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3053,13 +3053,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.794847268524</v>
+        <v>46073.62818060185</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.54729899306</v>
+        <v>46097.380632326385</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.813124513894</v>
+        <v>46101.64645784722</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3118,13 +3118,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.79484752315</v>
+        <v>46073.62818085648</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.54733972222</v>
+        <v>46097.38067305555</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.54734099537</v>
+        <v>46097.3806743287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3183,13 +3183,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.7948477662</v>
+        <v>46073.62818109954</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.58757038195</v>
+        <v>46104.420903715276</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.20558681713</v>
+        <v>46134.03892015046</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3248,13 +3248,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.79484803241</v>
+        <v>46073.62818136574</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.58750148148</v>
+        <v>46104.42083481481</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.58750311343</v>
+        <v>46104.42083644676</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3309,13 +3309,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.79484828704</v>
+        <v>46073.62818162037</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.58755459491</v>
+        <v>46104.42088792824</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.58755618056</v>
+        <v>46104.42088951389</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3370,13 +3370,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.79484853009</v>
+        <v>46073.62818186343</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.583659386575</v>
+        <v>46104.41699271991</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.58367331019</v>
+        <v>46104.41700664352</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3435,13 +3435,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.79484878472</v>
+        <v>46073.62818211806</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.58357604167</v>
+        <v>46104.416909374995</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.583577881946</v>
+        <v>46104.416911215274</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3496,13 +3496,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.79484700231</v>
+        <v>46073.62818033565</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.58364541667</v>
+        <v>46104.41697875</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.58364686342</v>
+        <v>46104.41698019676</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3557,13 +3557,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.79484739584</v>
+        <v>46073.62818072917</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.584286990736</v>
+        <v>46104.41762032408</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.2060525</v>
+        <v>46165.039385833334</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3622,13 +3622,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.79484769676</v>
+        <v>46073.62818103009</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.58417509259</v>
+        <v>46104.417508425926</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.58417674768</v>
+        <v>46104.41751008102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3683,13 +3683,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.79484798611</v>
+        <v>46073.628181319444</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.58422200232</v>
+        <v>46104.41755533565</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.58422371528</v>
+        <v>46104.41755704861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3744,13 +3744,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.79484826389</v>
+        <v>46073.62818159722</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.58427152778</v>
+        <v>46104.41760486111</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.58427320602</v>
+        <v>46104.417606539355</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3805,13 +3805,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.794848564816</v>
+        <v>46073.62818189815</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.801113587964</v>
+        <v>46114.63444692129</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.801124247686</v>
+        <v>46114.63445758102</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3870,13 +3870,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.79484883102</v>
+        <v>46073.62818216435</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.591430416665</v>
+        <v>46112.42476375</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.59143256945</v>
+        <v>46112.424765902775</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3931,13 +3931,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.79484913194</v>
+        <v>46073.628182465276</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.80109980324</v>
+        <v>46114.63443313657</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.80110109954</v>
+        <v>46114.63443443287</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3992,13 +3992,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.58266418982</v>
+        <v>46076.415997523145</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.49794984954</v>
+        <v>46112.331283182866</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.19208922454</v>
+        <v>46134.02542255787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4057,13 +4057,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.58280495371</v>
+        <v>46076.41613828704</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.7145863426</v>
+        <v>46129.547919675926</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.714587407405</v>
+        <v>46129.54792074074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4118,13 +4118,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.58302251158</v>
+        <v>46076.41635584491</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.7146324537</v>
+        <v>46129.54796578704</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.714633553245</v>
+        <v>46129.547966886574</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4179,13 +4179,13 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.794849467595</v>
+        <v>46073.62818280092</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.551042673615</v>
+        <v>46198.38437600694</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.55105587963</v>
+        <v>46198.384389212966</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.79484973379</v>
+        <v>46073.62818306713</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.79848856482</v>
+        <v>46114.63182189815</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.70688251157</v>
+        <v>46197.54021584491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.79484638889</v>
+        <v>46073.62817972222</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.79872664352</v>
+        <v>46114.63205997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.70691572917</v>
+        <v>46197.5402490625</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.80996193287</v>
+        <v>46087.6432952662</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.798792835645</v>
+        <v>46114.63212616898</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.798815428236</v>
+        <v>46114.63214876158</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4425,13 +4425,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.810021701385</v>
+        <v>46087.64335503472</v>
       </c>
       <c r="C49" s="8">
-        <v>46198.55102407407</v>
+        <v>46198.38435740741</v>
       </c>
       <c r="D49" s="8">
-        <v>46198.551042928244</v>
+        <v>46198.38437626157</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4488,13 +4488,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.79484671296</v>
+        <v>46073.6281800463</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.673340787034</v>
+        <v>46121.50667412037</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.67335355324</v>
+        <v>46121.50668688657</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4541,13 +4541,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.79484696759</v>
+        <v>46073.628180300926</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.799450266204</v>
+        <v>46120.63278359953</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.79946753472</v>
+        <v>46120.63280086806</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4606,13 +4606,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.794847233796</v>
+        <v>46073.62818056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.67332476852</v>
+        <v>46121.50665810185</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.67355936342</v>
+        <v>46121.50689269676</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4671,13 +4671,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.794847488425</v>
+        <v>46073.62818082176</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.76737151621</v>
+        <v>46132.60070484954</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.76738453704</v>
+        <v>46132.60071787037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4724,13 +4724,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.79484775463</v>
+        <v>46073.62818108796</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.79905210648</v>
+        <v>46120.632385439814</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.92421190972</v>
+        <v>46132.757545243054</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4789,13 +4789,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.79484800926</v>
+        <v>46073.62818134259</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.561391932875</v>
+        <v>46132.394725266204</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.561408657406</v>
+        <v>46132.39474199074</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4854,13 +4854,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.76735306713</v>
+        <v>46132.60068640046</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.76737177084</v>
+        <v>46132.60070510417</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4919,13 +4919,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.71626407407</v>
+        <v>46129.54959740741</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.71634960648</v>
+        <v>46129.54968293982</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4968,13 +4968,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.79484880787</v>
+        <v>46073.628182141205</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.61763545139</v>
+        <v>46122.450968784724</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.61765378472</v>
+        <v>46122.450987118056</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5033,13 +5033,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.79484665509</v>
+        <v>46073.62817998843</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.659079606485</v>
+        <v>46122.49241293981</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.17597939815</v>
+        <v>46147.00931273148</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5098,13 +5098,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.794847129626</v>
+        <v>46073.62818046296</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.669174490744</v>
+        <v>46127.50250782407</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.17597951389</v>
+        <v>46147.00931284722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5163,13 +5163,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.794847418976</v>
+        <v>46073.62818075232</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.66922835648</v>
+        <v>46127.50256168982</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.174760891205</v>
+        <v>46169.00809422454</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5228,13 +5228,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.583608553236</v>
+        <v>46076.41694188658</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.7162494213</v>
+        <v>46129.549582754626</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.200935636574</v>
+        <v>46136.0342689699</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5293,13 +5293,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.79484768519</v>
+        <v>46073.62818101852</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.50932107639</v>
+        <v>46197.342654409724</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.50933475695</v>
+        <v>46197.34266809028</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5346,13 +5346,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.68823886574</v>
+        <v>46195.521572199075</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.688256319445</v>
+        <v>46195.52158965278</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5411,13 +5411,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.79484829861</v>
+        <v>46073.628181631946</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50917609954</v>
+        <v>46197.34250943287</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50919467593</v>
+        <v>46197.34252800926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5476,13 +5476,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.79484857639</v>
+        <v>46073.62818190972</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50918461806</v>
+        <v>46197.34251795139</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50920605324</v>
+        <v>46197.34253938658</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5541,13 +5541,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.79484884259</v>
+        <v>46073.628182175926</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.50919322917</v>
+        <v>46197.3425265625</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.509207361116</v>
+        <v>46197.342540694444</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5606,13 +5606,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.6229305787</v>
+        <v>46076.45626391204</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.50920206019</v>
+        <v>46197.342535393516</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.50921739583</v>
+        <v>46197.34255072917</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5671,13 +5671,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.79484912037</v>
+        <v>46073.6281824537</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.5092531713</v>
+        <v>46197.34258650463</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.50926989583</v>
+        <v>46197.34260322917</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5734,13 +5734,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.794849432874</v>
+        <v>46073.6281827662</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.50929818287</v>
+        <v>46197.34263151621</v>
       </c>
       <c r="D70" s="5">
-        <v>46198.55104168982</v>
+        <v>46198.384375023146</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5797,11 +5797,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.794846979166</v>
+        <v>46073.6281803125</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.90012883102</v>
+        <v>46197.73346216435</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5844,11 +5844,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.794847384255</v>
+        <v>46073.62818071759</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.69436715278</v>
+        <v>46204.52770048611</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5905,11 +5905,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.79484767361</v>
+        <v>46073.62818100695</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46209.925254525464</v>
+        <v>46209.7585878588</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5968,13 +5968,13 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.79484796296</v>
+        <v>46073.6281812963</v>
       </c>
       <c r="C74" s="5">
-        <v>46197.90011859954</v>
+        <v>46197.73345193287</v>
       </c>
       <c r="D74" s="5">
-        <v>46205.63226972222</v>
+        <v>46205.465603055556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6031,11 +6031,11 @@
         <v>281</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.79484825231</v>
+        <v>46073.62818158565</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46197.90013631944</v>
+        <v>46197.733469652776</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>282</v>
@@ -6092,11 +6092,11 @@
         <v>284</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.79484855324</v>
+        <v>46073.628181886575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.66953237269</v>
+        <v>46090.50286570602</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>285</v>
@@ -6139,11 +6139,11 @@
         <v>287</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.79484886574</v>
+        <v>46073.62818219907</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>288</v>
@@ -6202,11 +6202,11 @@
         <v>292</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.79484915509</v>
+        <v>46073.62818248842</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.175525451385</v>
+        <v>46192.00885878473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>293</v>
@@ -6265,11 +6265,11 @@
         <v>294</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.64638520833</v>
+        <v>46090.47971854167</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.66956530092</v>
+        <v>46090.50289863426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>295</v>
@@ -6312,11 +6312,11 @@
         <v>297</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.646490810184</v>
+        <v>46090.47982414352</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.18765634259</v>
+        <v>46191.020989675926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>298</v>
@@ -6375,11 +6375,11 @@
         <v>300</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.64689480324</v>
+        <v>46090.48022813657</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46200.17552224537</v>
+        <v>46200.00885557871</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -1630,13 +1630,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.62817967593</v>
+        <v>46073.79484634259</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55022653935</v>
+        <v>46092.716893206016</v>
       </c>
       <c r="D4" s="5">
-        <v>46129.547676111106</v>
+        <v>46129.71434277778</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1679,13 +1679,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.62818002315</v>
+        <v>46073.794846689816</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.550201342594</v>
+        <v>46092.71686800926</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71108753472</v>
+        <v>46133.877754201385</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1744,13 +1744,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.62818039352</v>
+        <v>46073.794847060184</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55020189815</v>
+        <v>46092.716868564814</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.47894534722</v>
+        <v>46134.64561201389</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1809,13 +1809,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.628180694446</v>
+        <v>46073.79484736111</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55020238426</v>
+        <v>46092.71686905093</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.478941203706</v>
+        <v>46134.64560787037</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1874,13 +1874,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.628180960644</v>
+        <v>46073.794847627316</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.5502027662</v>
+        <v>46092.71686943287</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.478936851854</v>
+        <v>46134.64560351852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -1939,13 +1939,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.628181238426</v>
+        <v>46073.7948479051</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55020334491</v>
+        <v>46092.71687001157</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.478931087964</v>
+        <v>46134.64559775463</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2004,13 +2004,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.628182002314</v>
+        <v>46073.794848668986</v>
       </c>
       <c r="C10" s="5">
-        <v>46129.434622615736</v>
+        <v>46129.60128928241</v>
       </c>
       <c r="D10" s="5">
-        <v>46129.547719375</v>
+        <v>46129.71438604167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2053,13 +2053,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.628182291664</v>
+        <v>46073.794848958336</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.382770868055</v>
+        <v>46097.54943753472</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38278583333</v>
+        <v>46097.549452499996</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2118,13 +2118,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.628182569446</v>
+        <v>46073.79484923611</v>
       </c>
       <c r="C12" s="5">
-        <v>46129.43460976852</v>
+        <v>46129.60127643518</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.00499202547</v>
+        <v>46154.171658692125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2183,13 +2183,13 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.62818284723</v>
+        <v>46073.794849513884</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.380507800925</v>
+        <v>46097.54717446759</v>
       </c>
       <c r="D13" s="8">
-        <v>46129.547774074075</v>
+        <v>46129.71444074074</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2232,13 +2232,13 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.628180370375</v>
+        <v>46073.79484703703</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.380070625004</v>
+        <v>46097.54673729167</v>
       </c>
       <c r="D14" s="5">
-        <v>46104.38826939814</v>
+        <v>46104.554936064815</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2297,13 +2297,13 @@
         <v>69</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.62818092592</v>
+        <v>46073.794847592595</v>
       </c>
       <c r="C15" s="8">
-        <v>46097.38044920139</v>
+        <v>46097.54711586806</v>
       </c>
       <c r="D15" s="8">
-        <v>46104.388864293986</v>
+        <v>46104.55553096065</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>70</v>
@@ -2362,13 +2362,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.628181168984</v>
+        <v>46073.79484783565</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38026064815</v>
+        <v>46097.54692731482</v>
       </c>
       <c r="D16" s="5">
-        <v>46104.4023097801</v>
+        <v>46104.56897644676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>74</v>
@@ -2427,13 +2427,13 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.62818142361</v>
+        <v>46073.79484809028</v>
       </c>
       <c r="C17" s="8">
-        <v>46097.38048609954</v>
+        <v>46097.5471527662</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.612236898145</v>
+        <v>46100.77890356482</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2492,13 +2492,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.62818166667</v>
+        <v>46073.79484833333</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.33702034722</v>
+        <v>46114.50368701389</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.33703412037</v>
+        <v>46114.50370078704</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2545,13 +2545,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C19" s="8">
-        <v>46101.64645108796</v>
+        <v>46101.81311775463</v>
       </c>
       <c r="D19" s="8">
-        <v>46104.40283936342</v>
+        <v>46104.56950603009</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2610,13 +2610,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3809314699</v>
+        <v>46097.547598136574</v>
       </c>
       <c r="D20" s="5">
-        <v>46104.40305519676</v>
+        <v>46104.56972186343</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2675,13 +2675,13 @@
         <v>93</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.62818238426</v>
+        <v>46073.79484905093</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38286118055</v>
+        <v>46097.54952784722</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.40372770833</v>
+        <v>46104.570394375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>94</v>
@@ -2740,13 +2740,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.62818262732</v>
+        <v>46073.79484929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46101.647509710645</v>
+        <v>46101.81417637732</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.64752646991</v>
+        <v>46101.814193136575</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2805,13 +2805,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.41547559028</v>
+        <v>46076.58214225694</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.33700079861</v>
+        <v>46114.50366746528</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.337126388884</v>
+        <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -2870,13 +2870,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.62817975694</v>
+        <v>46073.79484642361</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38118626157</v>
+        <v>46097.54785292824</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.6113996412</v>
+        <v>46100.778066307874</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -2935,13 +2935,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.62818008102</v>
+        <v>46073.79484674768</v>
       </c>
       <c r="C25" s="8">
-        <v>46129.54803983796</v>
+        <v>46129.71470650463</v>
       </c>
       <c r="D25" s="8">
-        <v>46129.548054328705</v>
+        <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2988,13 +2988,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.380689363425</v>
+        <v>46097.54735603009</v>
       </c>
       <c r="D26" s="5">
-        <v>46134.03892021991</v>
+        <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3053,13 +3053,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.62818060185</v>
+        <v>46073.794847268524</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.380632326385</v>
+        <v>46097.54729899306</v>
       </c>
       <c r="D27" s="8">
-        <v>46101.64645784722</v>
+        <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>118</v>
@@ -3118,13 +3118,13 @@
         <v>120</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.62818085648</v>
+        <v>46073.79484752315</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.38067305555</v>
+        <v>46097.54733972222</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.3806743287</v>
+        <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>121</v>
@@ -3183,13 +3183,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.62818109954</v>
+        <v>46073.7948477662</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.420903715276</v>
+        <v>46104.58757038195</v>
       </c>
       <c r="D29" s="8">
-        <v>46134.03892015046</v>
+        <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3248,13 +3248,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.62818136574</v>
+        <v>46073.79484803241</v>
       </c>
       <c r="C30" s="5">
-        <v>46104.42083481481</v>
+        <v>46104.58750148148</v>
       </c>
       <c r="D30" s="5">
-        <v>46104.42083644676</v>
+        <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3309,13 +3309,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.62818162037</v>
+        <v>46073.79484828704</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.42088792824</v>
+        <v>46104.58755459491</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42088951389</v>
+        <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3370,13 +3370,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.62818186343</v>
+        <v>46073.79484853009</v>
       </c>
       <c r="C32" s="5">
-        <v>46104.41699271991</v>
+        <v>46104.583659386575</v>
       </c>
       <c r="D32" s="5">
-        <v>46104.41700664352</v>
+        <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3435,13 +3435,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.62818211806</v>
+        <v>46073.79484878472</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.416909374995</v>
+        <v>46104.58357604167</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.416911215274</v>
+        <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3496,13 +3496,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.62818033565</v>
+        <v>46073.79484700231</v>
       </c>
       <c r="C34" s="5">
-        <v>46104.41697875</v>
+        <v>46104.58364541667</v>
       </c>
       <c r="D34" s="5">
-        <v>46104.41698019676</v>
+        <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3557,13 +3557,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.62818072917</v>
+        <v>46073.79484739584</v>
       </c>
       <c r="C35" s="8">
-        <v>46104.41762032408</v>
+        <v>46104.584286990736</v>
       </c>
       <c r="D35" s="8">
-        <v>46165.039385833334</v>
+        <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3622,13 +3622,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.62818103009</v>
+        <v>46073.79484769676</v>
       </c>
       <c r="C36" s="5">
-        <v>46104.417508425926</v>
+        <v>46104.58417509259</v>
       </c>
       <c r="D36" s="5">
-        <v>46104.41751008102</v>
+        <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3683,13 +3683,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.628181319444</v>
+        <v>46073.79484798611</v>
       </c>
       <c r="C37" s="8">
-        <v>46104.41755533565</v>
+        <v>46104.58422200232</v>
       </c>
       <c r="D37" s="8">
-        <v>46104.41755704861</v>
+        <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3744,13 +3744,13 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.62818159722</v>
+        <v>46073.79484826389</v>
       </c>
       <c r="C38" s="5">
-        <v>46104.41760486111</v>
+        <v>46104.58427152778</v>
       </c>
       <c r="D38" s="5">
-        <v>46104.417606539355</v>
+        <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3805,13 +3805,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.62818189815</v>
+        <v>46073.794848564816</v>
       </c>
       <c r="C39" s="8">
-        <v>46114.63444692129</v>
+        <v>46114.801113587964</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.63445758102</v>
+        <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>154</v>
@@ -3870,13 +3870,13 @@
         <v>158</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.62818216435</v>
+        <v>46073.79484883102</v>
       </c>
       <c r="C40" s="5">
-        <v>46112.42476375</v>
+        <v>46112.591430416665</v>
       </c>
       <c r="D40" s="5">
-        <v>46112.424765902775</v>
+        <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>159</v>
@@ -3931,13 +3931,13 @@
         <v>161</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.628182465276</v>
+        <v>46073.79484913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.63443313657</v>
+        <v>46114.80109980324</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.63443443287</v>
+        <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>162</v>
@@ -3992,13 +3992,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="5">
-        <v>46076.415997523145</v>
+        <v>46076.58266418982</v>
       </c>
       <c r="C42" s="5">
-        <v>46112.331283182866</v>
+        <v>46112.49794984954</v>
       </c>
       <c r="D42" s="5">
-        <v>46134.02542255787</v>
+        <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>165</v>
@@ -4057,13 +4057,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="8">
-        <v>46076.41613828704</v>
+        <v>46076.58280495371</v>
       </c>
       <c r="C43" s="8">
-        <v>46129.547919675926</v>
+        <v>46129.7145863426</v>
       </c>
       <c r="D43" s="8">
-        <v>46129.54792074074</v>
+        <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
@@ -4118,13 +4118,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="5">
-        <v>46076.41635584491</v>
+        <v>46076.58302251158</v>
       </c>
       <c r="C44" s="5">
-        <v>46129.54796578704</v>
+        <v>46129.7146324537</v>
       </c>
       <c r="D44" s="5">
-        <v>46129.547966886574</v>
+        <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>171</v>
@@ -4179,13 +4179,13 @@
         <v>173</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.62818280092</v>
+        <v>46073.794849467595</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.38437600694</v>
+        <v>46198.551042673615</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.384389212966</v>
+        <v>46198.55105587963</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>174</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.62818306713</v>
+        <v>46073.79484973379</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.63182189815</v>
+        <v>46114.79848856482</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.54021584491</v>
+        <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>181</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.62817972222</v>
+        <v>46073.79484638889</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.63205997685</v>
+        <v>46114.79872664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.5402490625</v>
+        <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>182</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B48" s="5">
-        <v>46087.6432952662</v>
+        <v>46087.80996193287</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.63212616898</v>
+        <v>46114.798792835645</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.63214876158</v>
+        <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>186</v>
@@ -4425,13 +4425,13 @@
         <v>190</v>
       </c>
       <c r="B49" s="8">
-        <v>46087.64335503472</v>
+        <v>46087.810021701385</v>
       </c>
       <c r="C49" s="8">
-        <v>46198.38435740741</v>
+        <v>46198.55102407407</v>
       </c>
       <c r="D49" s="8">
-        <v>46198.38437626157</v>
+        <v>46198.551042928244</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>191</v>
@@ -4488,13 +4488,13 @@
         <v>196</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.6281800463</v>
+        <v>46073.79484671296</v>
       </c>
       <c r="C50" s="5">
-        <v>46121.50667412037</v>
+        <v>46121.673340787034</v>
       </c>
       <c r="D50" s="5">
-        <v>46121.50668688657</v>
+        <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>197</v>
@@ -4541,13 +4541,13 @@
         <v>199</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.628180300926</v>
+        <v>46073.79484696759</v>
       </c>
       <c r="C51" s="8">
-        <v>46120.63278359953</v>
+        <v>46120.799450266204</v>
       </c>
       <c r="D51" s="8">
-        <v>46120.63280086806</v>
+        <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>200</v>
@@ -4606,13 +4606,13 @@
         <v>204</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.62818056713</v>
+        <v>46073.794847233796</v>
       </c>
       <c r="C52" s="5">
-        <v>46121.50665810185</v>
+        <v>46121.67332476852</v>
       </c>
       <c r="D52" s="5">
-        <v>46121.50689269676</v>
+        <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>205</v>
@@ -4671,13 +4671,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.62818082176</v>
+        <v>46073.794847488425</v>
       </c>
       <c r="C53" s="8">
-        <v>46132.60070484954</v>
+        <v>46132.76737151621</v>
       </c>
       <c r="D53" s="8">
-        <v>46132.60071787037</v>
+        <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4724,13 +4724,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.62818108796</v>
+        <v>46073.79484775463</v>
       </c>
       <c r="C54" s="5">
-        <v>46120.632385439814</v>
+        <v>46120.79905210648</v>
       </c>
       <c r="D54" s="5">
-        <v>46132.757545243054</v>
+        <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4789,13 +4789,13 @@
         <v>217</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.62818134259</v>
+        <v>46073.79484800926</v>
       </c>
       <c r="C55" s="8">
-        <v>46132.394725266204</v>
+        <v>46132.561391932875</v>
       </c>
       <c r="D55" s="8">
-        <v>46132.39474199074</v>
+        <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>218</v>
@@ -4854,13 +4854,13 @@
         <v>221</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C56" s="5">
-        <v>46132.60068640046</v>
+        <v>46132.76735306713</v>
       </c>
       <c r="D56" s="5">
-        <v>46132.60070510417</v>
+        <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>222</v>
@@ -4919,13 +4919,13 @@
         <v>225</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C57" s="8">
-        <v>46129.54959740741</v>
+        <v>46129.71626407407</v>
       </c>
       <c r="D57" s="8">
-        <v>46129.54968293982</v>
+        <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>197</v>
@@ -4968,13 +4968,13 @@
         <v>227</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.628182141205</v>
+        <v>46073.79484880787</v>
       </c>
       <c r="C58" s="5">
-        <v>46122.450968784724</v>
+        <v>46122.61763545139</v>
       </c>
       <c r="D58" s="5">
-        <v>46122.450987118056</v>
+        <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>228</v>
@@ -5033,13 +5033,13 @@
         <v>230</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.62817998843</v>
+        <v>46073.79484665509</v>
       </c>
       <c r="C59" s="8">
-        <v>46122.49241293981</v>
+        <v>46122.659079606485</v>
       </c>
       <c r="D59" s="8">
-        <v>46147.00931273148</v>
+        <v>46147.17597939815</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>58</v>
@@ -5098,13 +5098,13 @@
         <v>232</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.62818046296</v>
+        <v>46073.794847129626</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.50250782407</v>
+        <v>46127.669174490744</v>
       </c>
       <c r="D60" s="5">
-        <v>46147.00931284722</v>
+        <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>233</v>
@@ -5163,13 +5163,13 @@
         <v>235</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.62818075232</v>
+        <v>46073.794847418976</v>
       </c>
       <c r="C61" s="8">
-        <v>46127.50256168982</v>
+        <v>46127.66922835648</v>
       </c>
       <c r="D61" s="8">
-        <v>46169.00809422454</v>
+        <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>236</v>
@@ -5228,13 +5228,13 @@
         <v>238</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.41694188658</v>
+        <v>46076.583608553236</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.549582754626</v>
+        <v>46129.7162494213</v>
       </c>
       <c r="D62" s="5">
-        <v>46136.0342689699</v>
+        <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>239</v>
@@ -5293,13 +5293,13 @@
         <v>241</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.62818101852</v>
+        <v>46073.79484768519</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.342654409724</v>
+        <v>46197.50932107639</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.34266809028</v>
+        <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>242</v>
@@ -5346,13 +5346,13 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.521572199075</v>
+        <v>46195.68823886574</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.52158965278</v>
+        <v>46195.688256319445</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>
@@ -5411,13 +5411,13 @@
         <v>247</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.628181631946</v>
+        <v>46073.79484829861</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.34250943287</v>
+        <v>46197.50917609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.34252800926</v>
+        <v>46197.50919467593</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>248</v>
@@ -5476,13 +5476,13 @@
         <v>251</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.62818190972</v>
+        <v>46073.79484857639</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.34251795139</v>
+        <v>46197.50918461806</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.34253938658</v>
+        <v>46197.50920605324</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>252</v>
@@ -5541,13 +5541,13 @@
         <v>254</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.628182175926</v>
+        <v>46073.79484884259</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.3425265625</v>
+        <v>46197.50919322917</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.342540694444</v>
+        <v>46197.509207361116</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>255</v>
@@ -5606,13 +5606,13 @@
         <v>257</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.45626391204</v>
+        <v>46076.6229305787</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.342535393516</v>
+        <v>46197.50920206019</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.34255072917</v>
+        <v>46197.50921739583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>258</v>
@@ -5671,13 +5671,13 @@
         <v>260</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.6281824537</v>
+        <v>46073.79484912037</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.34258650463</v>
+        <v>46197.5092531713</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.34260322917</v>
+        <v>46197.50926989583</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>194</v>
@@ -5734,13 +5734,13 @@
         <v>263</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.6281827662</v>
+        <v>46073.794849432874</v>
       </c>
       <c r="C70" s="5">
-        <v>46197.34263151621</v>
+        <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46198.384375023146</v>
+        <v>46198.55104168982</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5797,11 +5797,11 @@
         <v>265</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.6281803125</v>
+        <v>46073.794846979166</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.73346216435</v>
+        <v>46197.90012883102</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>266</v>
@@ -5844,11 +5844,11 @@
         <v>268</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.62818071759</v>
+        <v>46073.794847384255</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.52770048611</v>
+        <v>46211.69907109954</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>269</v>
@@ -5905,11 +5905,11 @@
         <v>273</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.62818100695</v>
+        <v>46073.79484767361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46209.7585878588</v>
+        <v>46209.925254525464</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>
@@ -5968,13 +5968,13 @@
         <v>277</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.6281812963</v>
+        <v>46073.79484796296</v>
       </c>
       <c r="C74" s="5">
-        <v>46197.73345193287</v>
+        <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46205.465603055556</v>
+        <v>46205.63226972222</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>278</v>
@@ -6031,11 +6031,11 @@
         <v>281</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.62818158565</v>
+        <v>46073.79484825231</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46197.733469652776</v>
+        <v>46197.90013631944</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>282</v>
@@ -6092,11 +6092,11 @@
         <v>284</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.628181886575</v>
+        <v>46073.79484855324</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.50286570602</v>
+        <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>285</v>
@@ -6139,11 +6139,11 @@
         <v>287</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.62818219907</v>
+        <v>46073.79484886574</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>288</v>
@@ -6202,11 +6202,11 @@
         <v>292</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.62818248842</v>
+        <v>46073.79484915509</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46192.00885878473</v>
+        <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>293</v>
@@ -6265,11 +6265,11 @@
         <v>294</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.47971854167</v>
+        <v>46090.64638520833</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.50289863426</v>
+        <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>295</v>
@@ -6312,11 +6312,11 @@
         <v>297</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.47982414352</v>
+        <v>46090.646490810184</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.020989675926</v>
+        <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>298</v>
@@ -6375,11 +6375,11 @@
         <v>300</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.48022813657</v>
+        <v>46090.64689480324</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46200.00885557871</v>
+        <v>46200.17552224537</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>301</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46209.925254525464</v>
+        <v>46217.59359769676</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46217.59359769676</v>
+        <v>46218.60318394676</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>274</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="299">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -396,9 +396,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete,Propuesta compras:</t>
   </si>
   <si>
@@ -415,12 +412,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Generación OC materiales,Propuesta compras:</t>
@@ -2755,11 +2746,9 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46023</v>
       </c>
@@ -2782,7 +2771,7 @@
         <v>70</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q22" s="5">
         <v>46023</v>
@@ -2802,7 +2791,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8">
         <v>46076.58214225694</v>
@@ -2814,7 +2803,7 @@
         <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2847,7 +2836,7 @@
         <v>74</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q23" s="8">
         <v>46023</v>
@@ -2867,7 +2856,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>46073.79484642361</v>
@@ -2879,17 +2868,15 @@
         <v>46100.778066307874</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>107</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46023</v>
       </c>
@@ -2912,7 +2899,7 @@
         <v>74</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q24" s="5">
         <v>46023</v>
@@ -2932,7 +2919,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B25" s="8">
         <v>46073.79484674768</v>
@@ -2944,7 +2931,7 @@
         <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2968,7 +2955,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2985,7 +2972,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46073.79484700231</v>
@@ -2997,16 +2984,16 @@
         <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I26" s="5">
         <v>46027</v>
@@ -3024,13 +3011,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q26" s="5">
         <v>46027</v>
@@ -3050,7 +3037,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="8">
         <v>46073.794847268524</v>
@@ -3062,16 +3049,16 @@
         <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I27" s="8">
         <v>46027</v>
@@ -3089,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q27" s="8">
         <v>46027</v>
@@ -3115,7 +3102,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5">
         <v>46073.79484752315</v>
@@ -3127,16 +3114,16 @@
         <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I28" s="5">
         <v>46029</v>
@@ -3154,13 +3141,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q28" s="5">
         <v>46029</v>
@@ -3180,7 +3167,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B29" s="8">
         <v>46073.7948477662</v>
@@ -3192,16 +3179,16 @@
         <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3219,13 +3206,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="8">
         <v>46027</v>
@@ -3245,7 +3232,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46073.79484803241</v>
@@ -3257,16 +3244,16 @@
         <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I30" s="5">
         <v>46027</v>
@@ -3284,13 +3271,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3306,7 +3293,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B31" s="8">
         <v>46073.79484828704</v>
@@ -3318,16 +3305,16 @@
         <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I31" s="8">
         <v>46036</v>
@@ -3345,13 +3332,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>127</v>
-      </c>
       <c r="P31" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3367,7 +3354,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
         <v>46073.79484853009</v>
@@ -3379,16 +3366,16 @@
         <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I32" s="5">
         <v>46027</v>
@@ -3406,13 +3393,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q32" s="5">
         <v>46027</v>
@@ -3432,7 +3419,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B33" s="8">
         <v>46073.79484878472</v>
@@ -3444,16 +3431,16 @@
         <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I33" s="8">
         <v>46027</v>
@@ -3471,13 +3458,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3493,7 +3480,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46073.79484700231</v>
@@ -3505,16 +3492,16 @@
         <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I34" s="5">
         <v>46029</v>
@@ -3532,13 +3519,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="P34" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3554,7 +3541,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B35" s="8">
         <v>46073.79484739584</v>
@@ -3566,16 +3553,16 @@
         <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I35" s="8">
         <v>46020</v>
@@ -3593,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q35" s="8">
         <v>46020</v>
@@ -3619,7 +3606,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46073.79484769676</v>
@@ -3631,16 +3618,16 @@
         <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I36" s="5">
         <v>46020</v>
@@ -3658,13 +3645,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3680,7 +3667,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B37" s="8">
         <v>46073.79484798611</v>
@@ -3692,16 +3679,16 @@
         <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I37" s="8">
         <v>46038</v>
@@ -3719,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3741,7 +3728,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46073.79484826389</v>
@@ -3753,16 +3740,16 @@
         <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I38" s="5">
         <v>46038</v>
@@ -3780,13 +3767,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="P38" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3802,7 +3789,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B39" s="8">
         <v>46073.794848564816</v>
@@ -3814,16 +3801,16 @@
         <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I39" s="8">
         <v>46024</v>
@@ -3841,13 +3828,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q39" s="8">
         <v>46024</v>
@@ -3867,7 +3854,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B40" s="5">
         <v>46073.79484883102</v>
@@ -3879,16 +3866,16 @@
         <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I40" s="5">
         <v>46024</v>
@@ -3906,13 +3893,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3928,7 +3915,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B41" s="8">
         <v>46073.79484913194</v>
@@ -3940,16 +3927,16 @@
         <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I41" s="8">
         <v>46044</v>
@@ -3967,13 +3954,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3989,7 +3976,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46076.58266418982</v>
@@ -4001,16 +3988,16 @@
         <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46027</v>
@@ -4028,13 +4015,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q42" s="5">
         <v>46027</v>
@@ -4054,7 +4041,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B43" s="8">
         <v>46076.58280495371</v>
@@ -4066,16 +4053,16 @@
         <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I43" s="8">
         <v>46027</v>
@@ -4093,13 +4080,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4115,7 +4102,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46076.58302251158</v>
@@ -4127,16 +4114,16 @@
         <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I44" s="5">
         <v>46056</v>
@@ -4154,13 +4141,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="O44" s="6" t="s">
-        <v>168</v>
-      </c>
       <c r="P44" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4176,7 +4163,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B45" s="8">
         <v>46073.794849467595</v>
@@ -4188,7 +4175,7 @@
         <v>46198.55105587963</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4212,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4229,7 +4216,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46073.79484973379</v>
@@ -4241,16 +4228,16 @@
         <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I46" s="5">
         <v>46023</v>
@@ -4268,13 +4255,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q46" s="5">
         <v>46023</v>
@@ -4294,7 +4281,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B47" s="8">
         <v>46073.79484638889</v>
@@ -4306,16 +4293,16 @@
         <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I47" s="8">
         <v>46078</v>
@@ -4333,13 +4320,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q47" s="8">
         <v>46078</v>
@@ -4359,7 +4346,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B48" s="5">
         <v>46087.80996193287</v>
@@ -4371,16 +4358,16 @@
         <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4396,13 +4383,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q48" s="5">
         <v>46085</v>
@@ -4422,7 +4409,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B49" s="8">
         <v>46087.810021701385</v>
@@ -4434,16 +4421,16 @@
         <v>46198.551042928244</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4459,13 +4446,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q49" s="8">
         <v>46171</v>
@@ -4485,7 +4472,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B50" s="5">
         <v>46073.79484671296</v>
@@ -4497,7 +4484,7 @@
         <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4521,7 +4508,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4538,7 +4525,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B51" s="8">
         <v>46073.79484696759</v>
@@ -4550,16 +4537,16 @@
         <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I51" s="8">
         <v>46073</v>
@@ -4577,13 +4564,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q51" s="8">
         <v>46073</v>
@@ -4603,7 +4590,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B52" s="5">
         <v>46073.794847233796</v>
@@ -4615,16 +4602,16 @@
         <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I52" s="5">
         <v>46077</v>
@@ -4642,13 +4629,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O52" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="O52" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="P52" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q52" s="5">
         <v>46077</v>
@@ -4668,7 +4655,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B53" s="8">
         <v>46073.794847488425</v>
@@ -4680,7 +4667,7 @@
         <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4704,7 +4691,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4721,7 +4708,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B54" s="5">
         <v>46073.79484775463</v>
@@ -4733,16 +4720,16 @@
         <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I54" s="5">
         <v>46079</v>
@@ -4760,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q54" s="5">
         <v>46079</v>
@@ -4786,7 +4773,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B55" s="8">
         <v>46073.79484800926</v>
@@ -4798,16 +4785,16 @@
         <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I55" s="8">
         <v>46090</v>
@@ -4825,13 +4812,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q55" s="8">
         <v>46090</v>
@@ -4851,7 +4838,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B56" s="5">
         <v>46073.79484829861</v>
@@ -4863,16 +4850,16 @@
         <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I56" s="5">
         <v>46119</v>
@@ -4890,13 +4877,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q56" s="5">
         <v>46119</v>
@@ -4916,7 +4903,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B57" s="8">
         <v>46073.79484855324</v>
@@ -4928,7 +4915,7 @@
         <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4952,7 +4939,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4965,7 +4952,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B58" s="5">
         <v>46073.79484880787</v>
@@ -4977,16 +4964,16 @@
         <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46078</v>
@@ -5004,13 +4991,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q58" s="5">
         <v>46078</v>
@@ -5030,7 +5017,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B59" s="8">
         <v>46073.79484665509</v>
@@ -5048,10 +5035,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I59" s="8">
         <v>46142</v>
@@ -5069,13 +5056,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q59" s="8">
         <v>46142</v>
@@ -5095,7 +5082,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B60" s="5">
         <v>46073.794847129626</v>
@@ -5107,16 +5094,16 @@
         <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I60" s="5">
         <v>46142</v>
@@ -5134,13 +5121,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q60" s="5">
         <v>46142</v>
@@ -5160,7 +5147,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B61" s="8">
         <v>46073.794847418976</v>
@@ -5172,16 +5159,16 @@
         <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I61" s="8">
         <v>46164</v>
@@ -5199,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q61" s="8">
         <v>46167</v>
@@ -5225,7 +5212,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B62" s="5">
         <v>46076.583608553236</v>
@@ -5237,16 +5224,16 @@
         <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I62" s="5">
         <v>46134</v>
@@ -5264,13 +5251,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q62" s="5">
         <v>46134</v>
@@ -5290,7 +5277,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B63" s="8">
         <v>46073.79484768519</v>
@@ -5302,7 +5289,7 @@
         <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5326,7 +5313,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5343,7 +5330,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B64" s="5">
         <v>46073.79484796296</v>
@@ -5355,17 +5342,15 @@
         <v>46195.688256319445</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="5">
         <v>46121</v>
       </c>
@@ -5382,13 +5367,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q64" s="5">
         <v>46121</v>
@@ -5408,7 +5393,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B65" s="8">
         <v>46073.79484829861</v>
@@ -5420,17 +5405,15 @@
         <v>46197.50919467593</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8">
         <v>46168</v>
       </c>
@@ -5447,13 +5430,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q65" s="8">
         <v>46169</v>
@@ -5473,7 +5456,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B66" s="5">
         <v>46073.79484857639</v>
@@ -5485,17 +5468,15 @@
         <v>46197.50920605324</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>46147</v>
       </c>
@@ -5512,13 +5493,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q66" s="5">
         <v>46147</v>
@@ -5538,7 +5519,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B67" s="8">
         <v>46073.79484884259</v>
@@ -5550,17 +5531,15 @@
         <v>46197.509207361116</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8">
         <v>46149</v>
       </c>
@@ -5577,13 +5556,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q67" s="8">
         <v>46149</v>
@@ -5603,7 +5582,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B68" s="5">
         <v>46076.6229305787</v>
@@ -5615,17 +5594,15 @@
         <v>46197.50921739583</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>46136</v>
       </c>
@@ -5642,13 +5619,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q68" s="5">
         <v>46136</v>
@@ -5668,7 +5645,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B69" s="8">
         <v>46073.79484912037</v>
@@ -5680,17 +5657,15 @@
         <v>46197.50926989583</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
         <v>46170</v>
@@ -5705,13 +5680,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q69" s="8">
         <v>46170</v>
@@ -5731,7 +5706,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B70" s="5">
         <v>46073.794849432874</v>
@@ -5743,17 +5718,15 @@
         <v>46198.55104168982</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46172</v>
@@ -5768,13 +5741,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q70" s="5">
         <v>46172</v>
@@ -5794,7 +5767,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B71" s="8">
         <v>46073.794846979166</v>
@@ -5804,7 +5777,7 @@
         <v>46197.90012883102</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5828,7 +5801,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5841,7 +5814,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B72" s="5">
         <v>46073.794847384255</v>
@@ -5851,16 +5824,16 @@
         <v>46211.69907109954</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5876,13 +5849,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q72" s="5">
         <v>46175</v>
@@ -5902,7 +5875,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B73" s="8">
         <v>46073.79484767361</v>
@@ -5912,17 +5885,15 @@
         <v>46218.60318394676</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8">
         <v>46175</v>
       </c>
@@ -5939,13 +5910,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q73" s="8">
         <v>46176</v>
@@ -5965,7 +5936,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B74" s="5">
         <v>46073.79484796296</v>
@@ -5977,16 +5948,16 @@
         <v>46205.63226972222</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5996,19 +5967,19 @@
         <v>26</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Q74" s="5">
         <v>46181</v>
@@ -6028,7 +5999,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B75" s="8">
         <v>46073.79484825231</v>
@@ -6038,16 +6009,16 @@
         <v>46197.90013631944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -6063,13 +6034,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q75" s="8">
         <v>46182</v>
@@ -6089,7 +6060,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B76" s="5">
         <v>46073.79484855324</v>
@@ -6099,7 +6070,7 @@
         <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6123,7 +6094,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6136,7 +6107,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B77" s="8">
         <v>46073.79484886574</v>
@@ -6146,16 +6117,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I77" s="8">
         <v>46182</v>
@@ -6173,13 +6144,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q77" s="8">
         <v>46183</v>
@@ -6199,7 +6170,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B78" s="5">
         <v>46073.79484915509</v>
@@ -6209,16 +6180,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I78" s="5">
         <v>46182</v>
@@ -6236,13 +6207,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="Q78" s="5">
         <v>46183</v>
@@ -6262,7 +6233,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B79" s="8">
         <v>46090.64638520833</v>
@@ -6272,7 +6243,7 @@
         <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6296,7 +6267,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6309,7 +6280,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B80" s="5">
         <v>46090.646490810184</v>
@@ -6319,7 +6290,7 @@
         <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6346,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q80" s="5">
         <v>46182</v>
@@ -6372,7 +6343,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B81" s="8">
         <v>46090.64689480324</v>
@@ -6382,7 +6353,7 @@
         <v>46200.17552224537</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6409,13 +6380,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="O81" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="P81" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q81" s="8">
         <v>46191</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="300">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -394,6 +394,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Generación OC Rodete,Propuesta compras:</t>
@@ -2737,7 +2740,7 @@
         <v>46101.81417637732</v>
       </c>
       <c r="D22" s="5">
-        <v>46101.814193136575</v>
+        <v>46223.80841302083</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2746,9 +2749,11 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I22" s="5">
         <v>46023</v>
       </c>
@@ -2771,7 +2776,7 @@
         <v>70</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="5">
         <v>46023</v>
@@ -2791,7 +2796,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="8">
         <v>46076.58214225694</v>
@@ -2803,7 +2808,7 @@
         <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2836,7 +2841,7 @@
         <v>74</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q23" s="8">
         <v>46023</v>
@@ -2856,7 +2861,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" s="5">
         <v>46073.79484642361</v>
@@ -2865,18 +2870,20 @@
         <v>46097.54785292824</v>
       </c>
       <c r="D24" s="5">
-        <v>46100.778066307874</v>
+        <v>46223.80840997685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I24" s="5">
         <v>46023</v>
       </c>
@@ -2899,7 +2906,7 @@
         <v>74</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q24" s="5">
         <v>46023</v>
@@ -2919,7 +2926,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B25" s="8">
         <v>46073.79484674768</v>
@@ -2931,7 +2938,7 @@
         <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2955,7 +2962,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2972,7 +2979,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="5">
         <v>46073.79484700231</v>
@@ -2984,16 +2991,16 @@
         <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I26" s="5">
         <v>46027</v>
@@ -3011,13 +3018,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="5">
         <v>46027</v>
@@ -3037,7 +3044,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="8">
         <v>46073.794847268524</v>
@@ -3049,16 +3056,16 @@
         <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I27" s="8">
         <v>46027</v>
@@ -3076,13 +3083,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q27" s="8">
         <v>46027</v>
@@ -3102,7 +3109,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5">
         <v>46073.79484752315</v>
@@ -3114,16 +3121,16 @@
         <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I28" s="5">
         <v>46029</v>
@@ -3141,13 +3148,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q28" s="5">
         <v>46029</v>
@@ -3167,7 +3174,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" s="8">
         <v>46073.7948477662</v>
@@ -3179,16 +3186,16 @@
         <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3206,13 +3213,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="8">
         <v>46027</v>
@@ -3232,7 +3239,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" s="5">
         <v>46073.79484803241</v>
@@ -3244,16 +3251,16 @@
         <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I30" s="5">
         <v>46027</v>
@@ -3271,13 +3278,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3293,7 +3300,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="8">
         <v>46073.79484828704</v>
@@ -3305,16 +3312,16 @@
         <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I31" s="8">
         <v>46036</v>
@@ -3332,13 +3339,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3354,7 +3361,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46073.79484853009</v>
@@ -3366,16 +3373,16 @@
         <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I32" s="5">
         <v>46027</v>
@@ -3393,13 +3400,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q32" s="5">
         <v>46027</v>
@@ -3419,7 +3426,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="8">
         <v>46073.79484878472</v>
@@ -3431,16 +3438,16 @@
         <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I33" s="8">
         <v>46027</v>
@@ -3458,13 +3465,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3480,7 +3487,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46073.79484700231</v>
@@ -3492,16 +3499,16 @@
         <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I34" s="5">
         <v>46029</v>
@@ -3519,13 +3526,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3541,7 +3548,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="8">
         <v>46073.79484739584</v>
@@ -3553,16 +3560,16 @@
         <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I35" s="8">
         <v>46020</v>
@@ -3580,13 +3587,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q35" s="8">
         <v>46020</v>
@@ -3606,7 +3613,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46073.79484769676</v>
@@ -3618,16 +3625,16 @@
         <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I36" s="5">
         <v>46020</v>
@@ -3645,13 +3652,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3667,7 +3674,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="8">
         <v>46073.79484798611</v>
@@ -3679,16 +3686,16 @@
         <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I37" s="8">
         <v>46038</v>
@@ -3706,13 +3713,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3728,7 +3735,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46073.79484826389</v>
@@ -3740,16 +3747,16 @@
         <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I38" s="5">
         <v>46038</v>
@@ -3767,13 +3774,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3789,7 +3796,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="8">
         <v>46073.794848564816</v>
@@ -3801,16 +3808,16 @@
         <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I39" s="8">
         <v>46024</v>
@@ -3828,13 +3835,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q39" s="8">
         <v>46024</v>
@@ -3854,7 +3861,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B40" s="5">
         <v>46073.79484883102</v>
@@ -3866,16 +3873,16 @@
         <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I40" s="5">
         <v>46024</v>
@@ -3893,13 +3900,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3915,7 +3922,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B41" s="8">
         <v>46073.79484913194</v>
@@ -3927,16 +3934,16 @@
         <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46044</v>
@@ -3954,13 +3961,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3976,7 +3983,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46076.58266418982</v>
@@ -3988,16 +3995,16 @@
         <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46027</v>
@@ -4015,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q42" s="5">
         <v>46027</v>
@@ -4041,7 +4048,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B43" s="8">
         <v>46076.58280495371</v>
@@ -4053,16 +4060,16 @@
         <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46027</v>
@@ -4080,13 +4087,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4102,7 +4109,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5">
         <v>46076.58302251158</v>
@@ -4114,16 +4121,16 @@
         <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46056</v>
@@ -4141,13 +4148,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4163,7 +4170,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B45" s="8">
         <v>46073.794849467595</v>
@@ -4175,7 +4182,7 @@
         <v>46198.55105587963</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4199,7 +4206,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4216,7 +4223,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B46" s="5">
         <v>46073.79484973379</v>
@@ -4228,16 +4235,16 @@
         <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I46" s="5">
         <v>46023</v>
@@ -4255,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q46" s="5">
         <v>46023</v>
@@ -4281,7 +4288,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B47" s="8">
         <v>46073.79484638889</v>
@@ -4293,16 +4300,16 @@
         <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I47" s="8">
         <v>46078</v>
@@ -4320,13 +4327,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q47" s="8">
         <v>46078</v>
@@ -4346,7 +4353,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B48" s="5">
         <v>46087.80996193287</v>
@@ -4358,16 +4365,16 @@
         <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4383,13 +4390,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q48" s="5">
         <v>46085</v>
@@ -4409,7 +4416,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B49" s="8">
         <v>46087.810021701385</v>
@@ -4421,16 +4428,16 @@
         <v>46198.551042928244</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4446,13 +4453,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q49" s="8">
         <v>46171</v>
@@ -4472,7 +4479,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B50" s="5">
         <v>46073.79484671296</v>
@@ -4484,7 +4491,7 @@
         <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4508,7 +4515,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4525,7 +4532,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B51" s="8">
         <v>46073.79484696759</v>
@@ -4537,16 +4544,16 @@
         <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I51" s="8">
         <v>46073</v>
@@ -4564,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q51" s="8">
         <v>46073</v>
@@ -4590,7 +4597,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B52" s="5">
         <v>46073.794847233796</v>
@@ -4602,16 +4609,16 @@
         <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I52" s="5">
         <v>46077</v>
@@ -4629,13 +4636,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q52" s="5">
         <v>46077</v>
@@ -4655,7 +4662,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B53" s="8">
         <v>46073.794847488425</v>
@@ -4667,7 +4674,7 @@
         <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4691,7 +4698,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4708,7 +4715,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B54" s="5">
         <v>46073.79484775463</v>
@@ -4720,16 +4727,16 @@
         <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I54" s="5">
         <v>46079</v>
@@ -4747,13 +4754,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q54" s="5">
         <v>46079</v>
@@ -4773,7 +4780,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B55" s="8">
         <v>46073.79484800926</v>
@@ -4785,16 +4792,16 @@
         <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I55" s="8">
         <v>46090</v>
@@ -4812,13 +4819,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q55" s="8">
         <v>46090</v>
@@ -4838,7 +4845,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B56" s="5">
         <v>46073.79484829861</v>
@@ -4850,16 +4857,16 @@
         <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I56" s="5">
         <v>46119</v>
@@ -4877,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q56" s="5">
         <v>46119</v>
@@ -4903,7 +4910,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B57" s="8">
         <v>46073.79484855324</v>
@@ -4915,7 +4922,7 @@
         <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4939,7 +4946,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4952,7 +4959,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B58" s="5">
         <v>46073.79484880787</v>
@@ -4964,16 +4971,16 @@
         <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46078</v>
@@ -4991,13 +4998,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q58" s="5">
         <v>46078</v>
@@ -5017,7 +5024,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B59" s="8">
         <v>46073.79484665509</v>
@@ -5035,10 +5042,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I59" s="8">
         <v>46142</v>
@@ -5056,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q59" s="8">
         <v>46142</v>
@@ -5082,7 +5089,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B60" s="5">
         <v>46073.794847129626</v>
@@ -5094,16 +5101,16 @@
         <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46142</v>
@@ -5121,13 +5128,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q60" s="5">
         <v>46142</v>
@@ -5147,7 +5154,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B61" s="8">
         <v>46073.794847418976</v>
@@ -5159,16 +5166,16 @@
         <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I61" s="8">
         <v>46164</v>
@@ -5186,13 +5193,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q61" s="8">
         <v>46167</v>
@@ -5212,7 +5219,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B62" s="5">
         <v>46076.583608553236</v>
@@ -5224,16 +5231,16 @@
         <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I62" s="5">
         <v>46134</v>
@@ -5251,13 +5258,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q62" s="5">
         <v>46134</v>
@@ -5277,7 +5284,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B63" s="8">
         <v>46073.79484768519</v>
@@ -5289,7 +5296,7 @@
         <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5313,7 +5320,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5330,7 +5337,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B64" s="5">
         <v>46073.79484796296</v>
@@ -5339,18 +5346,20 @@
         <v>46195.68823886574</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.688256319445</v>
+        <v>46223.808554351854</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I64" s="5">
         <v>46121</v>
       </c>
@@ -5367,13 +5376,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q64" s="5">
         <v>46121</v>
@@ -5393,7 +5402,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B65" s="8">
         <v>46073.79484829861</v>
@@ -5402,18 +5411,20 @@
         <v>46197.50917609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50919467593</v>
+        <v>46223.80854966435</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I65" s="8">
         <v>46168</v>
       </c>
@@ -5430,13 +5441,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q65" s="8">
         <v>46169</v>
@@ -5456,7 +5467,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B66" s="5">
         <v>46073.79484857639</v>
@@ -5465,18 +5476,20 @@
         <v>46197.50918461806</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50920605324</v>
+        <v>46223.8085455324</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I66" s="5">
         <v>46147</v>
       </c>
@@ -5493,13 +5506,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q66" s="5">
         <v>46147</v>
@@ -5519,7 +5532,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B67" s="8">
         <v>46073.79484884259</v>
@@ -5528,18 +5541,20 @@
         <v>46197.50919322917</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.509207361116</v>
+        <v>46223.808541516206</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I67" s="8">
         <v>46149</v>
       </c>
@@ -5556,13 +5571,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q67" s="8">
         <v>46149</v>
@@ -5582,7 +5597,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B68" s="5">
         <v>46076.6229305787</v>
@@ -5591,18 +5606,20 @@
         <v>46197.50920206019</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.50921739583</v>
+        <v>46223.80853726852</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I68" s="5">
         <v>46136</v>
       </c>
@@ -5619,13 +5636,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q68" s="5">
         <v>46136</v>
@@ -5645,7 +5662,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B69" s="8">
         <v>46073.79484912037</v>
@@ -5654,18 +5671,20 @@
         <v>46197.5092531713</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.50926989583</v>
+        <v>46223.80853359954</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
         <v>46170</v>
@@ -5680,13 +5699,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q69" s="8">
         <v>46170</v>
@@ -5706,7 +5725,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B70" s="5">
         <v>46073.794849432874</v>
@@ -5715,18 +5734,20 @@
         <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46198.55104168982</v>
+        <v>46223.808527870366</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46172</v>
@@ -5741,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q70" s="5">
         <v>46172</v>
@@ -5767,7 +5788,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B71" s="8">
         <v>46073.794846979166</v>
@@ -5777,7 +5798,7 @@
         <v>46197.90012883102</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5801,7 +5822,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5814,7 +5835,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B72" s="5">
         <v>46073.794847384255</v>
@@ -5824,16 +5845,16 @@
         <v>46211.69907109954</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5849,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q72" s="5">
         <v>46175</v>
@@ -5875,7 +5896,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B73" s="8">
         <v>46073.79484767361</v>
@@ -5885,7 +5906,7 @@
         <v>46218.60318394676</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5910,13 +5931,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q73" s="8">
         <v>46176</v>
@@ -5936,7 +5957,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B74" s="5">
         <v>46073.79484796296</v>
@@ -5948,16 +5969,16 @@
         <v>46205.63226972222</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5967,19 +5988,19 @@
         <v>26</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q74" s="5">
         <v>46181</v>
@@ -5999,7 +6020,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B75" s="8">
         <v>46073.79484825231</v>
@@ -6009,16 +6030,16 @@
         <v>46197.90013631944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -6034,13 +6055,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q75" s="8">
         <v>46182</v>
@@ -6060,7 +6081,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B76" s="5">
         <v>46073.79484855324</v>
@@ -6070,7 +6091,7 @@
         <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6094,7 +6115,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6107,7 +6128,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B77" s="8">
         <v>46073.79484886574</v>
@@ -6117,16 +6138,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I77" s="8">
         <v>46182</v>
@@ -6144,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q77" s="8">
         <v>46183</v>
@@ -6170,7 +6191,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B78" s="5">
         <v>46073.79484915509</v>
@@ -6180,16 +6201,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I78" s="5">
         <v>46182</v>
@@ -6207,13 +6228,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q78" s="5">
         <v>46183</v>
@@ -6233,7 +6254,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B79" s="8">
         <v>46090.64638520833</v>
@@ -6243,7 +6264,7 @@
         <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6267,7 +6288,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6280,7 +6301,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B80" s="5">
         <v>46090.646490810184</v>
@@ -6290,7 +6311,7 @@
         <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6317,13 +6338,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q80" s="5">
         <v>46182</v>
@@ -6343,7 +6364,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B81" s="8">
         <v>46090.64689480324</v>
@@ -6353,7 +6374,7 @@
         <v>46200.17552224537</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6380,13 +6401,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q81" s="8">
         <v>46191</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="300">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46218.60318394676</v>
+        <v>46223.83377060185</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>272</v>
@@ -5912,9 +5912,11 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="I73" s="8">
         <v>46175</v>
       </c>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="301">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -394,6 +394,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2752,7 +2755,7 @@
         <v>99</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I22" s="5">
         <v>46023</v>
@@ -2776,7 +2779,7 @@
         <v>70</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q22" s="5">
         <v>46023</v>
@@ -2796,7 +2799,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" s="8">
         <v>46076.58214225694</v>
@@ -2808,7 +2811,7 @@
         <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2841,7 +2844,7 @@
         <v>74</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q23" s="8">
         <v>46023</v>
@@ -2861,7 +2864,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B24" s="5">
         <v>46073.79484642361</v>
@@ -2873,7 +2876,7 @@
         <v>46223.80840997685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2882,7 +2885,7 @@
         <v>99</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I24" s="5">
         <v>46023</v>
@@ -2906,7 +2909,7 @@
         <v>74</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q24" s="5">
         <v>46023</v>
@@ -2926,7 +2929,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8">
         <v>46073.79484674768</v>
@@ -2938,7 +2941,7 @@
         <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2962,7 +2965,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2979,7 +2982,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5">
         <v>46073.79484700231</v>
@@ -2991,16 +2994,16 @@
         <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I26" s="5">
         <v>46027</v>
@@ -3018,13 +3021,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="5">
         <v>46027</v>
@@ -3044,7 +3047,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" s="8">
         <v>46073.794847268524</v>
@@ -3056,16 +3059,16 @@
         <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I27" s="8">
         <v>46027</v>
@@ -3083,13 +3086,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q27" s="8">
         <v>46027</v>
@@ -3109,7 +3112,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28" s="5">
         <v>46073.79484752315</v>
@@ -3121,16 +3124,16 @@
         <v>46097.54734099537</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I28" s="5">
         <v>46029</v>
@@ -3148,13 +3151,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q28" s="5">
         <v>46029</v>
@@ -3174,7 +3177,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B29" s="8">
         <v>46073.7948477662</v>
@@ -3186,16 +3189,16 @@
         <v>46134.20558681713</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3213,13 +3216,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="8">
         <v>46027</v>
@@ -3239,7 +3242,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="5">
         <v>46073.79484803241</v>
@@ -3251,16 +3254,16 @@
         <v>46104.58750311343</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I30" s="5">
         <v>46027</v>
@@ -3278,13 +3281,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3300,7 +3303,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B31" s="8">
         <v>46073.79484828704</v>
@@ -3312,16 +3315,16 @@
         <v>46104.58755618056</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I31" s="8">
         <v>46036</v>
@@ -3339,13 +3342,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" s="5">
         <v>46073.79484853009</v>
@@ -3373,16 +3376,16 @@
         <v>46104.58367331019</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I32" s="5">
         <v>46027</v>
@@ -3400,13 +3403,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q32" s="5">
         <v>46027</v>
@@ -3426,7 +3429,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B33" s="8">
         <v>46073.79484878472</v>
@@ -3438,16 +3441,16 @@
         <v>46104.583577881946</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I33" s="8">
         <v>46027</v>
@@ -3465,13 +3468,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3487,7 +3490,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B34" s="5">
         <v>46073.79484700231</v>
@@ -3499,16 +3502,16 @@
         <v>46104.58364686342</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I34" s="5">
         <v>46029</v>
@@ -3526,13 +3529,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3548,7 +3551,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B35" s="8">
         <v>46073.79484739584</v>
@@ -3560,16 +3563,16 @@
         <v>46165.2060525</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I35" s="8">
         <v>46020</v>
@@ -3587,13 +3590,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q35" s="8">
         <v>46020</v>
@@ -3613,7 +3616,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" s="5">
         <v>46073.79484769676</v>
@@ -3625,16 +3628,16 @@
         <v>46104.58417674768</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I36" s="5">
         <v>46020</v>
@@ -3652,13 +3655,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3674,7 +3677,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B37" s="8">
         <v>46073.79484798611</v>
@@ -3686,16 +3689,16 @@
         <v>46104.58422371528</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I37" s="8">
         <v>46038</v>
@@ -3713,13 +3716,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3735,7 +3738,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="5">
         <v>46073.79484826389</v>
@@ -3747,16 +3750,16 @@
         <v>46104.58427320602</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I38" s="5">
         <v>46038</v>
@@ -3774,13 +3777,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3796,7 +3799,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="8">
         <v>46073.794848564816</v>
@@ -3808,16 +3811,16 @@
         <v>46114.801124247686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I39" s="8">
         <v>46024</v>
@@ -3835,13 +3838,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q39" s="8">
         <v>46024</v>
@@ -3861,7 +3864,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B40" s="5">
         <v>46073.79484883102</v>
@@ -3873,16 +3876,16 @@
         <v>46112.59143256945</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I40" s="5">
         <v>46024</v>
@@ -3900,13 +3903,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3922,7 +3925,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B41" s="8">
         <v>46073.79484913194</v>
@@ -3934,16 +3937,16 @@
         <v>46114.80110109954</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I41" s="8">
         <v>46044</v>
@@ -3961,13 +3964,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3983,7 +3986,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B42" s="5">
         <v>46076.58266418982</v>
@@ -3995,16 +3998,16 @@
         <v>46134.19208922454</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46027</v>
@@ -4022,13 +4025,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q42" s="5">
         <v>46027</v>
@@ -4048,7 +4051,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B43" s="8">
         <v>46076.58280495371</v>
@@ -4060,16 +4063,16 @@
         <v>46129.714587407405</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" s="8">
         <v>46027</v>
@@ -4087,13 +4090,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4109,7 +4112,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5">
         <v>46076.58302251158</v>
@@ -4121,16 +4124,16 @@
         <v>46129.714633553245</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46056</v>
@@ -4148,13 +4151,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4170,7 +4173,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B45" s="8">
         <v>46073.794849467595</v>
@@ -4182,7 +4185,7 @@
         <v>46198.55105587963</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4206,7 +4209,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4223,7 +4226,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B46" s="5">
         <v>46073.79484973379</v>
@@ -4235,16 +4238,16 @@
         <v>46197.70688251157</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I46" s="5">
         <v>46023</v>
@@ -4262,13 +4265,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q46" s="5">
         <v>46023</v>
@@ -4288,7 +4291,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B47" s="8">
         <v>46073.79484638889</v>
@@ -4300,16 +4303,16 @@
         <v>46197.70691572917</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="8">
         <v>46078</v>
@@ -4327,13 +4330,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q47" s="8">
         <v>46078</v>
@@ -4353,7 +4356,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B48" s="5">
         <v>46087.80996193287</v>
@@ -4365,16 +4368,16 @@
         <v>46114.798815428236</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4390,13 +4393,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q48" s="5">
         <v>46085</v>
@@ -4416,7 +4419,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B49" s="8">
         <v>46087.810021701385</v>
@@ -4428,16 +4431,16 @@
         <v>46198.551042928244</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4453,13 +4456,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q49" s="8">
         <v>46171</v>
@@ -4479,7 +4482,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B50" s="5">
         <v>46073.79484671296</v>
@@ -4491,7 +4494,7 @@
         <v>46121.67335355324</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4515,7 +4518,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4532,7 +4535,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B51" s="8">
         <v>46073.79484696759</v>
@@ -4544,16 +4547,16 @@
         <v>46120.79946753472</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I51" s="8">
         <v>46073</v>
@@ -4571,13 +4574,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q51" s="8">
         <v>46073</v>
@@ -4597,7 +4600,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B52" s="5">
         <v>46073.794847233796</v>
@@ -4609,16 +4612,16 @@
         <v>46121.67355936342</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I52" s="5">
         <v>46077</v>
@@ -4636,13 +4639,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q52" s="5">
         <v>46077</v>
@@ -4662,7 +4665,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B53" s="8">
         <v>46073.794847488425</v>
@@ -4674,7 +4677,7 @@
         <v>46132.76738453704</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4698,7 +4701,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4715,7 +4718,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B54" s="5">
         <v>46073.79484775463</v>
@@ -4727,16 +4730,16 @@
         <v>46132.92421190972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I54" s="5">
         <v>46079</v>
@@ -4754,13 +4757,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q54" s="5">
         <v>46079</v>
@@ -4780,7 +4783,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B55" s="8">
         <v>46073.79484800926</v>
@@ -4792,16 +4795,16 @@
         <v>46132.561408657406</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I55" s="8">
         <v>46090</v>
@@ -4819,13 +4822,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q55" s="8">
         <v>46090</v>
@@ -4845,7 +4848,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B56" s="5">
         <v>46073.79484829861</v>
@@ -4857,16 +4860,16 @@
         <v>46132.76737177084</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I56" s="5">
         <v>46119</v>
@@ -4884,13 +4887,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q56" s="5">
         <v>46119</v>
@@ -4910,7 +4913,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B57" s="8">
         <v>46073.79484855324</v>
@@ -4922,7 +4925,7 @@
         <v>46129.71634960648</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4946,7 +4949,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4959,7 +4962,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B58" s="5">
         <v>46073.79484880787</v>
@@ -4971,16 +4974,16 @@
         <v>46122.61765378472</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46078</v>
@@ -4998,13 +5001,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q58" s="5">
         <v>46078</v>
@@ -5024,7 +5027,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B59" s="8">
         <v>46073.79484665509</v>
@@ -5042,10 +5045,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I59" s="8">
         <v>46142</v>
@@ -5063,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q59" s="8">
         <v>46142</v>
@@ -5089,7 +5092,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B60" s="5">
         <v>46073.794847129626</v>
@@ -5101,16 +5104,16 @@
         <v>46147.17597951389</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46142</v>
@@ -5128,13 +5131,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q60" s="5">
         <v>46142</v>
@@ -5154,7 +5157,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B61" s="8">
         <v>46073.794847418976</v>
@@ -5166,16 +5169,16 @@
         <v>46169.174760891205</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I61" s="8">
         <v>46164</v>
@@ -5193,13 +5196,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q61" s="8">
         <v>46167</v>
@@ -5219,7 +5222,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B62" s="5">
         <v>46076.583608553236</v>
@@ -5231,16 +5234,16 @@
         <v>46136.200935636574</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I62" s="5">
         <v>46134</v>
@@ -5258,13 +5261,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q62" s="5">
         <v>46134</v>
@@ -5284,7 +5287,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B63" s="8">
         <v>46073.79484768519</v>
@@ -5296,7 +5299,7 @@
         <v>46197.50933475695</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5320,7 +5323,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5337,7 +5340,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B64" s="5">
         <v>46073.79484796296</v>
@@ -5349,7 +5352,7 @@
         <v>46223.808554351854</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5358,7 +5361,7 @@
         <v>99</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I64" s="5">
         <v>46121</v>
@@ -5376,13 +5379,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q64" s="5">
         <v>46121</v>
@@ -5402,7 +5405,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B65" s="8">
         <v>46073.79484829861</v>
@@ -5414,7 +5417,7 @@
         <v>46223.80854966435</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5423,7 +5426,7 @@
         <v>99</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I65" s="8">
         <v>46168</v>
@@ -5441,13 +5444,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q65" s="8">
         <v>46169</v>
@@ -5467,7 +5470,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B66" s="5">
         <v>46073.79484857639</v>
@@ -5479,7 +5482,7 @@
         <v>46223.8085455324</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5488,7 +5491,7 @@
         <v>99</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I66" s="5">
         <v>46147</v>
@@ -5506,13 +5509,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q66" s="5">
         <v>46147</v>
@@ -5532,7 +5535,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B67" s="8">
         <v>46073.79484884259</v>
@@ -5544,7 +5547,7 @@
         <v>46223.808541516206</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5553,7 +5556,7 @@
         <v>99</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I67" s="8">
         <v>46149</v>
@@ -5571,13 +5574,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q67" s="8">
         <v>46149</v>
@@ -5597,7 +5600,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B68" s="5">
         <v>46076.6229305787</v>
@@ -5609,7 +5612,7 @@
         <v>46223.80853726852</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5618,7 +5621,7 @@
         <v>99</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I68" s="5">
         <v>46136</v>
@@ -5636,13 +5639,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q68" s="5">
         <v>46136</v>
@@ -5662,7 +5665,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B69" s="8">
         <v>46073.79484912037</v>
@@ -5674,7 +5677,7 @@
         <v>46223.80853359954</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5683,7 +5686,7 @@
         <v>99</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5699,13 +5702,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q69" s="8">
         <v>46170</v>
@@ -5725,7 +5728,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B70" s="5">
         <v>46073.794849432874</v>
@@ -5737,7 +5740,7 @@
         <v>46223.808527870366</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5746,7 +5749,7 @@
         <v>99</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5762,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q70" s="5">
         <v>46172</v>
@@ -5788,7 +5791,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B71" s="8">
         <v>46073.794846979166</v>
@@ -5798,7 +5801,7 @@
         <v>46197.90012883102</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5822,7 +5825,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5835,7 +5838,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B72" s="5">
         <v>46073.794847384255</v>
@@ -5845,16 +5848,16 @@
         <v>46211.69907109954</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5870,13 +5873,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q72" s="5">
         <v>46175</v>
@@ -5896,7 +5899,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B73" s="8">
         <v>46073.79484767361</v>
@@ -5906,7 +5909,7 @@
         <v>46223.83377060185</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5915,7 +5918,7 @@
         <v>99</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I73" s="8">
         <v>46175</v>
@@ -5933,13 +5936,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q73" s="8">
         <v>46176</v>
@@ -5959,7 +5962,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B74" s="5">
         <v>46073.79484796296</v>
@@ -5971,16 +5974,16 @@
         <v>46205.63226972222</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5990,19 +5993,19 @@
         <v>26</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q74" s="5">
         <v>46181</v>
@@ -6022,7 +6025,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B75" s="8">
         <v>46073.79484825231</v>
@@ -6032,16 +6035,16 @@
         <v>46197.90013631944</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -6057,13 +6060,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q75" s="8">
         <v>46182</v>
@@ -6083,7 +6086,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B76" s="5">
         <v>46073.79484855324</v>
@@ -6093,7 +6096,7 @@
         <v>46090.66953237269</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6117,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6130,7 +6133,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B77" s="8">
         <v>46073.79484886574</v>
@@ -6140,16 +6143,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I77" s="8">
         <v>46182</v>
@@ -6167,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q77" s="8">
         <v>46183</v>
@@ -6193,7 +6196,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B78" s="5">
         <v>46073.79484915509</v>
@@ -6203,16 +6206,16 @@
         <v>46192.175525451385</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I78" s="5">
         <v>46182</v>
@@ -6230,13 +6233,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q78" s="5">
         <v>46183</v>
@@ -6256,7 +6259,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B79" s="8">
         <v>46090.64638520833</v>
@@ -6266,7 +6269,7 @@
         <v>46090.66956530092</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6290,7 +6293,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6303,7 +6306,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B80" s="5">
         <v>46090.646490810184</v>
@@ -6313,7 +6316,7 @@
         <v>46191.18765634259</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6340,13 +6343,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q80" s="5">
         <v>46182</v>
@@ -6366,7 +6369,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B81" s="8">
         <v>46090.64689480324</v>
@@ -6376,7 +6379,7 @@
         <v>46200.17552224537</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6403,13 +6406,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q81" s="8">
         <v>46191</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5971,7 +5971,7 @@
         <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46205.63226972222</v>
+        <v>46234.93003905093</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>277</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5737,7 +5737,7 @@
         <v>46197.50929818287</v>
       </c>
       <c r="D70" s="5">
-        <v>46223.808527870366</v>
+        <v>46237.512055740735</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>194</v>
@@ -5785,8 +5785,8 @@
       <c r="T70" s="6">
         <v>1</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>81</v>
+      <c r="U70" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="293">
   <si>
     <t>50001446-MINERA FRESNILLO</t>
   </si>
@@ -946,7 +946,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Logistica:,Costos,Instalación de componentes ,Gestion</t>
+    <t>Logistica:,Costos,Gestion</t>
   </si>
   <si>
     <t>1213381525410807</t>
@@ -977,30 +977,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>1213575386156271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta en marcha Servicios </t>
-  </si>
-  <si>
-    <t>Instalación de componentes ,Pruebas de instalación componentes</t>
-  </si>
-  <si>
-    <t>1213575386156273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalación de componentes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de instalación componentes,Puesta en marcha Servicios </t>
-  </si>
-  <si>
-    <t>1213575386156275</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación componentes</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -6032,7 +6008,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46197.90013631944</v>
+        <v>46240.72403283565</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>281</v>
@@ -6254,179 +6230,6 @@
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46090.64638520833</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
-        <v>46090.66956530092</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B80" s="5">
-        <v>46090.646490810184</v>
-      </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="5">
-        <v>46191.18765634259</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46182</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46190</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46182</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46190</v>
-      </c>
-      <c r="S80" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46090.64689480324</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46200.17552224537</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46191</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46199</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>46191</v>
-      </c>
-      <c r="R81" s="8">
-        <v>46199</v>
-      </c>
-      <c r="S81" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="T81" s="9">
-        <v>0</v>
-      </c>
-      <c r="U81" s="10" t="s">
         <v>61</v>
       </c>
     </row>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5947,7 +5947,7 @@
         <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46234.93003905093</v>
+        <v>46241.909162951386</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>277</v>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -213,12 +213,6 @@
   </si>
   <si>
     <t>Embalaje,Ingenieria Servicios:</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
   </si>
   <si>
     <t>1213330955220903</t>
@@ -447,6 +441,9 @@
     <t>Generación OC Alabe,Fabricación Alabe</t>
   </si>
   <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>1213330955220917</t>
   </si>
   <si>
@@ -454,6 +451,9 @@
   </si>
   <si>
     <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
   </si>
   <si>
     <t>1213330955220918</t>
@@ -2097,7 +2097,7 @@
         <v>46129.60127643518</v>
       </c>
       <c r="D12" s="5">
-        <v>46154.171658692125</v>
+        <v>46246.80198226852</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2141,19 +2141,19 @@
       <c r="R12" s="5">
         <v>46153</v>
       </c>
-      <c r="S12" s="11" t="s">
-        <v>60</v>
+      <c r="S12" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
       </c>
-      <c r="U12" s="10" t="s">
-        <v>61</v>
+      <c r="U12" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8">
         <v>46073.794849513884</v>
@@ -2165,7 +2165,7 @@
         <v>46129.71444074074</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2189,7 +2189,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46073.79484703703</v>
@@ -2214,7 +2214,7 @@
         <v>46104.554936064815</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2235,19 +2235,19 @@
         <v>26</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="5">
         <v>46014</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B15" s="8">
         <v>46073.794847592595</v>
@@ -2279,7 +2279,7 @@
         <v>46104.55553096065</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2300,19 +2300,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>42</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="8">
         <v>46014</v>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46073.79484783565</v>
@@ -2344,7 +2344,7 @@
         <v>46104.56897644676</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2365,19 +2365,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46014</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8">
         <v>46073.79484809028</v>
@@ -2409,7 +2409,7 @@
         <v>46100.77890356482</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2436,13 +2436,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="8">
         <v>46014</v>
@@ -2457,12 +2457,12 @@
         <v>1</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46073.79484833333</v>
@@ -2474,7 +2474,7 @@
         <v>46114.50370078704</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2498,7 +2498,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B19" s="8">
         <v>46073.79484857639</v>
@@ -2527,7 +2527,7 @@
         <v>46104.56950603009</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2548,19 +2548,19 @@
         <v>26</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="8">
         <v>46023</v>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46073.79484880787</v>
@@ -2592,7 +2592,7 @@
         <v>46104.56972186343</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2613,19 +2613,19 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q20" s="5">
         <v>46016</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B21" s="8">
         <v>46073.79484905093</v>
@@ -2657,7 +2657,7 @@
         <v>46104.570394375</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2678,19 +2678,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>52</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q21" s="8">
         <v>46017</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B22" s="5">
         <v>46073.79484929398</v>
@@ -2722,16 +2722,16 @@
         <v>46223.80841302083</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I22" s="5">
         <v>46023</v>
@@ -2749,13 +2749,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q22" s="5">
         <v>46023</v>
@@ -2775,7 +2775,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8">
         <v>46076.58214225694</v>
@@ -2787,7 +2787,7 @@
         <v>46114.503793055555</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2814,13 +2814,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q23" s="8">
         <v>46023</v>
@@ -2840,7 +2840,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>46073.79484642361</v>
@@ -2852,16 +2852,16 @@
         <v>46223.80840997685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I24" s="5">
         <v>46023</v>
@@ -2879,13 +2879,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q24" s="5">
         <v>46023</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B25" s="8">
         <v>46073.79484674768</v>
@@ -2917,7 +2917,7 @@
         <v>46129.71472099537</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2941,7 +2941,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46073.79484700231</v>
@@ -2970,16 +2970,16 @@
         <v>46134.20558688657</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="I26" s="5">
         <v>46027</v>
@@ -2997,13 +2997,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q26" s="5">
         <v>46027</v>
@@ -3012,18 +3012,18 @@
         <v>46141</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B27" s="8">
         <v>46073.794847268524</v>
@@ -3035,16 +3035,16 @@
         <v>46101.813124513894</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I27" s="8">
         <v>46027</v>
@@ -3062,13 +3062,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q27" s="8">
         <v>46027</v>
@@ -3077,13 +3077,13 @@
         <v>46028</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3106,10 +3106,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I28" s="5">
         <v>46029</v>
@@ -3127,10 +3127,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>121</v>
@@ -3142,13 +3142,13 @@
         <v>46141</v>
       </c>
       <c r="S28" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3171,10 +3171,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3192,13 +3192,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>124</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="8">
         <v>46027</v>
@@ -3207,13 +3207,13 @@
         <v>46141</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3236,10 +3236,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I30" s="5">
         <v>46027</v>
@@ -3260,7 +3260,7 @@
         <v>123</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>127</v>
@@ -3268,13 +3268,13 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3297,10 +3297,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I31" s="8">
         <v>46036</v>
@@ -3329,13 +3329,13 @@
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3358,10 +3358,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I32" s="5">
         <v>46027</v>
@@ -3379,13 +3379,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q32" s="5">
         <v>46027</v>
@@ -3423,10 +3423,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I33" s="8">
         <v>46027</v>
@@ -3447,7 +3447,7 @@
         <v>132</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>136</v>
@@ -3455,13 +3455,13 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3484,10 +3484,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I34" s="5">
         <v>46029</v>
@@ -3516,13 +3516,13 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3545,10 +3545,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I35" s="8">
         <v>46020</v>
@@ -3566,13 +3566,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>142</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q35" s="8">
         <v>46020</v>
@@ -3581,13 +3581,13 @@
         <v>46164</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T35" s="9">
         <v>1</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3610,10 +3610,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I36" s="5">
         <v>46020</v>
@@ -3634,7 +3634,7 @@
         <v>141</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>145</v>
@@ -3642,13 +3642,13 @@
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3671,10 +3671,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I37" s="8">
         <v>46038</v>
@@ -3703,13 +3703,13 @@
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3732,10 +3732,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I38" s="5">
         <v>46038</v>
@@ -3764,13 +3764,13 @@
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3814,13 +3814,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>156</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q39" s="8">
         <v>46024</v>
@@ -3882,7 +3882,7 @@
         <v>153</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>159</v>
@@ -3890,13 +3890,13 @@
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3951,13 +3951,13 @@
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4001,13 +4001,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q42" s="5">
         <v>46027</v>
@@ -4016,13 +4016,13 @@
         <v>46133</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4069,7 +4069,7 @@
         <v>164</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>168</v>
@@ -4077,13 +4077,13 @@
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4138,13 +4138,13 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4244,7 +4244,7 @@
         <v>173</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>179</v>
@@ -4447,7 +4447,7 @@
         <v>46171</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4565,7 +4565,7 @@
         <v>46076</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T51" s="9">
         <v>1</v>
@@ -4630,7 +4630,7 @@
         <v>46078</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -4748,7 +4748,7 @@
         <v>46087</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         <v>46118</v>
       </c>
       <c r="S55" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T55" s="9">
         <v>1</v>
@@ -4878,7 +4878,7 @@
         <v>46120</v>
       </c>
       <c r="S56" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5057,13 +5057,13 @@
         <v>46146</v>
       </c>
       <c r="S59" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T59" s="9">
         <v>1</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5122,13 +5122,13 @@
         <v>46146</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5187,13 +5187,13 @@
         <v>46168</v>
       </c>
       <c r="S61" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
       </c>
       <c r="U61" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5252,13 +5252,13 @@
         <v>46135</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
       </c>
       <c r="U62" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5334,10 +5334,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I64" s="5">
         <v>46121</v>
@@ -5370,7 +5370,7 @@
         <v>46129</v>
       </c>
       <c r="S64" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>
@@ -5399,10 +5399,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I65" s="8">
         <v>46168</v>
@@ -5435,7 +5435,7 @@
         <v>46170</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T65" s="9">
         <v>1</v>
@@ -5464,10 +5464,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I66" s="5">
         <v>46147</v>
@@ -5500,7 +5500,7 @@
         <v>46148</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5529,10 +5529,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I67" s="8">
         <v>46149</v>
@@ -5565,7 +5565,7 @@
         <v>46120</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -5594,10 +5594,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I68" s="5">
         <v>46136</v>
@@ -5630,7 +5630,7 @@
         <v>46140</v>
       </c>
       <c r="S68" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5659,10 +5659,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5693,7 +5693,7 @@
         <v>46170</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T69" s="9">
         <v>1</v>
@@ -5722,10 +5722,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5756,7 +5756,7 @@
         <v>46172</v>
       </c>
       <c r="S70" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46211.69907109954</v>
+        <v>46246.80485579861</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>268</v>
@@ -5863,14 +5863,14 @@
       <c r="R72" s="5">
         <v>46175</v>
       </c>
-      <c r="S72" s="11" t="s">
-        <v>60</v>
+      <c r="S72" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46223.83377060185</v>
+        <v>46246.80485609954</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>273</v>
@@ -5891,10 +5891,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I73" s="8">
         <v>46175</v>
@@ -5926,14 +5926,14 @@
       <c r="R73" s="8">
         <v>46178</v>
       </c>
-      <c r="S73" s="11" t="s">
-        <v>60</v>
+      <c r="S73" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T73" s="9">
         <v>0.7</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5947,7 +5947,7 @@
         <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46241.909162951386</v>
+        <v>46246.804856400464</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>277</v>
@@ -5989,8 +5989,8 @@
       <c r="R74" s="5">
         <v>46181</v>
       </c>
-      <c r="S74" s="11" t="s">
-        <v>60</v>
+      <c r="S74" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46240.72403283565</v>
+        <v>46246.80485667824</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>281</v>
@@ -6050,14 +6050,14 @@
       <c r="R75" s="8">
         <v>46182</v>
       </c>
-      <c r="S75" s="11" t="s">
-        <v>60</v>
+      <c r="S75" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6161,13 +6161,13 @@
         <v>46191</v>
       </c>
       <c r="S77" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T77" s="9">
         <v>0</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6224,13 +6224,13 @@
         <v>46191</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001446 - MINERA FRESNILLO.xlsx
+++ b/data/50001446 - MINERA FRESNILLO.xlsx
@@ -5774,7 +5774,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.90012883102</v>
+        <v>46260.59887969907</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>265</v>
@@ -5880,9 +5880,11 @@
       <c r="B73" s="8">
         <v>46073.79484767361</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46260.59887023148</v>
+      </c>
       <c r="D73" s="8">
-        <v>46246.80485609954</v>
+        <v>46260.59888653935</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>273</v>
@@ -5930,10 +5932,10 @@
         <v>32</v>
       </c>
       <c r="T73" s="9">
-        <v>0.7</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5947,7 +5949,7 @@
         <v>46197.90011859954</v>
       </c>
       <c r="D74" s="5">
-        <v>46246.804856400464</v>
+        <v>46260.598887314816</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>277</v>
@@ -5995,8 +5997,8 @@
       <c r="T74" s="6">
         <v>1</v>
       </c>
-      <c r="U74" s="11" t="s">
-        <v>33</v>
+      <c r="U74" s="12" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6008,7 +6010,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46246.80485667824</v>
+        <v>46260.594010381945</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>281</v>
@@ -6056,8 +6058,8 @@
       <c r="T75" s="9">
         <v>0</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>79</v>
+      <c r="U75" s="10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
